--- a/03_Private_Equity/instances/public_home_depot_2023.xlsx
+++ b/03_Private_Equity/instances/public_home_depot_2023.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="312">
   <si>
     <t xml:space="preserve">[TARGET] — LBO Underwriting Model</t>
   </si>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">Target / transaction:</t>
   </si>
   <si>
-    <t xml:space="preserve">The Home Depot FY2023 public-company operating case</t>
+    <t xml:space="preserve">[Name]</t>
   </si>
   <si>
     <t xml:space="preserve">Sponsor / principal:</t>
   </si>
   <si>
-    <t xml:space="preserve">Benchmark Sponsor</t>
+    <t xml:space="preserve">[Fund / merchant bank]</t>
   </si>
   <si>
     <t xml:space="preserve">Entry / close date:</t>
@@ -942,15 +942,6 @@
   </si>
   <si>
     <t xml:space="preserve">Immutable curated observation package with SHA-256 digest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retained modeler assumption from pe-reference-buyout.json</t>
-  </si>
-  <si>
-    <t xml:space="preserve">repo://standards/benchmark_cases/pe-reference-buyout.json</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not an external observation; retained for sensitivity and transaction-structure completeness</t>
   </si>
   <si>
     <t xml:space="preserve">Refresh Log</t>
@@ -1114,14 +1105,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFCE4D6"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -1198,7 +1189,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1227,7 +1218,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1267,11 +1258,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1279,11 +1270,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1291,7 +1282,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1303,15 +1294,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1446,34 +1433,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1619,7 +1606,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:F17"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36"/>
@@ -1656,7 +1643,7 @@
       <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1664,7 +1651,7 @@
       <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1672,7 +1659,7 @@
       <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1680,7 +1667,7 @@
       <c r="B9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1688,7 +1675,7 @@
       <c r="B10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1760,7 +1747,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:E9"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
@@ -1827,7 +1814,7 @@
       </c>
       <c r="C7" s="19" t="n">
         <f aca="false">'Sources &amp; Uses'!F8</f>
-        <v>121817.03997</v>
+        <v>109904.2779</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>127</v>
@@ -1842,7 +1829,7 @@
       </c>
       <c r="C8" s="19" t="n">
         <f aca="false">C7*(1+Assumptions!E31)^Assumptions!E29</f>
-        <v>178989.197060589</v>
+        <v>161485.4412789</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>127</v>
@@ -1886,7 +1873,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:J15"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
@@ -1976,35 +1963,35 @@
       <c r="B6" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="26" t="n">
         <f aca="false">Assumptions!$E$28</f>
         <v>10</v>
       </c>
-      <c r="D6" s="27" t="n">
+      <c r="D6" s="26" t="n">
         <f aca="false">Assumptions!$E$28</f>
         <v>10</v>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="26" t="n">
         <f aca="false">Assumptions!$E$28</f>
         <v>10</v>
       </c>
-      <c r="F6" s="27" t="n">
+      <c r="F6" s="26" t="n">
         <f aca="false">Assumptions!$E$28</f>
         <v>10</v>
       </c>
-      <c r="G6" s="27" t="n">
+      <c r="G6" s="26" t="n">
         <f aca="false">Assumptions!$E$28</f>
         <v>10</v>
       </c>
-      <c r="H6" s="27" t="n">
+      <c r="H6" s="26" t="n">
         <f aca="false">Assumptions!$E$28</f>
         <v>10</v>
       </c>
-      <c r="I6" s="27" t="n">
+      <c r="I6" s="26" t="n">
         <f aca="false">Assumptions!$E$28</f>
         <v>10</v>
       </c>
-      <c r="J6" s="27" t="n">
+      <c r="J6" s="26" t="n">
         <f aca="false">INDEX(C6:I6,1,Assumptions!E29)</f>
         <v>10</v>
       </c>
@@ -2052,35 +2039,35 @@
       </c>
       <c r="C8" s="19" t="n">
         <f aca="false">'Debt Schedule'!D28</f>
-        <v>124407.000235313</v>
+        <v>124691.68021125</v>
       </c>
       <c r="D8" s="19" t="n">
         <f aca="false">'Debt Schedule'!E28</f>
-        <v>119998.7349601</v>
+        <v>120595.047125562</v>
       </c>
       <c r="E8" s="19" t="n">
         <f aca="false">'Debt Schedule'!F28</f>
-        <v>115204.363395756</v>
+        <v>116141.578836387</v>
       </c>
       <c r="F8" s="19" t="n">
         <f aca="false">'Debt Schedule'!G28</f>
-        <v>110013.616979535</v>
+        <v>111323.384621118</v>
       </c>
       <c r="G8" s="19" t="n">
         <f aca="false">'Debt Schedule'!H28</f>
-        <v>104415.190086469</v>
+        <v>106131.715854733</v>
       </c>
       <c r="H8" s="19" t="n">
         <f aca="false">'Debt Schedule'!I28</f>
-        <v>98395.916190782</v>
+        <v>100556.162874162</v>
       </c>
       <c r="I8" s="19" t="n">
         <f aca="false">'Debt Schedule'!J28</f>
-        <v>91940.6238682786</v>
+        <v>94584.5269144406</v>
       </c>
       <c r="J8" s="19" t="n">
         <f aca="false">INDEX(C8:I8,1,Assumptions!E29)</f>
-        <v>104415.190086469</v>
+        <v>106131.715854733</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2089,35 +2076,35 @@
       </c>
       <c r="C9" s="19" t="n">
         <f aca="false">MAX(0,C7-C8)</f>
-        <v>109573.509164687</v>
+        <v>109288.82918875</v>
       </c>
       <c r="D9" s="19" t="n">
         <f aca="false">MAX(0,D7-D8)</f>
-        <v>114144.6722629</v>
+        <v>113548.360097438</v>
       </c>
       <c r="E9" s="19" t="n">
         <f aca="false">MAX(0,E7-E8)</f>
-        <v>118881.585322404</v>
+        <v>117944.369881773</v>
       </c>
       <c r="F9" s="19" t="n">
         <f aca="false">MAX(0,F7-F8)</f>
-        <v>123807.591677574</v>
+        <v>122497.824035991</v>
       </c>
       <c r="G9" s="19" t="n">
         <f aca="false">MAX(0,G7-G8)</f>
-        <v>128946.485559407</v>
+        <v>127229.959791143</v>
       </c>
       <c r="H9" s="19" t="n">
         <f aca="false">MAX(0,H7-H8)</f>
-        <v>134323.359336743</v>
+        <v>132163.112653363</v>
       </c>
       <c r="I9" s="19" t="n">
         <f aca="false">MAX(0,I7-I8)</f>
-        <v>139964.770039915</v>
+        <v>137320.866993753</v>
       </c>
       <c r="J9" s="19" t="n">
         <f aca="false">INDEX(C9:I9,1,Assumptions!E29)</f>
-        <v>128946.485559407</v>
+        <v>127229.959791143</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2126,35 +2113,35 @@
       </c>
       <c r="C10" s="19" t="n">
         <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^1</f>
-        <v>131562.4031676</v>
+        <v>118696.620132</v>
       </c>
       <c r="D10" s="19" t="n">
         <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^2</f>
-        <v>142087.395421008</v>
+        <v>128192.34974256</v>
       </c>
       <c r="E10" s="19" t="n">
         <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^3</f>
-        <v>153454.387054689</v>
+        <v>138447.737721965</v>
       </c>
       <c r="F10" s="19" t="n">
         <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^4</f>
-        <v>165730.738019064</v>
+        <v>149523.556739722</v>
       </c>
       <c r="G10" s="19" t="n">
         <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^5</f>
-        <v>178989.197060589</v>
+        <v>161485.4412789</v>
       </c>
       <c r="H10" s="19" t="n">
         <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^6</f>
-        <v>193308.332825436</v>
+        <v>174404.276581212</v>
       </c>
       <c r="I10" s="19" t="n">
         <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^7</f>
-        <v>208772.999451471</v>
+        <v>188356.618707709</v>
       </c>
       <c r="J10" s="19" t="n">
         <f aca="false">INDEX(C10:I10,1,Assumptions!E29)</f>
-        <v>178989.197060589</v>
+        <v>161485.4412789</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2200,35 +2187,35 @@
       </c>
       <c r="C12" s="19" t="n">
         <f aca="false">MIN(C9,C9*Assumptions!$E$30+C11*Assumptions!$E$32)</f>
-        <v>10957.3509164688</v>
+        <v>10928.882918875</v>
       </c>
       <c r="D12" s="19" t="n">
         <f aca="false">MIN(D9,D9*Assumptions!$E$30+D11*Assumptions!$E$32)</f>
-        <v>11414.46722629</v>
+        <v>11354.8360097438</v>
       </c>
       <c r="E12" s="19" t="n">
         <f aca="false">MIN(E9,E9*Assumptions!$E$30+E11*Assumptions!$E$32)</f>
-        <v>11888.1585322404</v>
+        <v>11794.4369881773</v>
       </c>
       <c r="F12" s="19" t="n">
         <f aca="false">MIN(F9,F9*Assumptions!$E$30+F11*Assumptions!$E$32)</f>
-        <v>12380.7591677574</v>
+        <v>12249.7824035991</v>
       </c>
       <c r="G12" s="19" t="n">
         <f aca="false">MIN(G9,G9*Assumptions!$E$30+G11*Assumptions!$E$32)</f>
-        <v>12894.6485559407</v>
+        <v>12722.9959791143</v>
       </c>
       <c r="H12" s="19" t="n">
         <f aca="false">MIN(H9,H9*Assumptions!$E$30+H11*Assumptions!$E$32)</f>
-        <v>13432.3359336743</v>
+        <v>13216.3112653363</v>
       </c>
       <c r="I12" s="19" t="n">
         <f aca="false">MIN(I9,I9*Assumptions!$E$30+I11*Assumptions!$E$32)</f>
-        <v>13996.4770039915</v>
+        <v>13732.0866993753</v>
       </c>
       <c r="J12" s="19" t="n">
         <f aca="false">INDEX(C12:I12,1,Assumptions!E29)</f>
-        <v>12894.6485559407</v>
+        <v>12722.9959791143</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2237,72 +2224,72 @@
       </c>
       <c r="C13" s="19" t="n">
         <f aca="false">MAX(0,C9-C12)</f>
-        <v>98616.1582482187</v>
+        <v>98359.946269875</v>
       </c>
       <c r="D13" s="19" t="n">
         <f aca="false">MAX(0,D9-D12)</f>
-        <v>102730.20503661</v>
+        <v>102193.524087694</v>
       </c>
       <c r="E13" s="19" t="n">
         <f aca="false">MAX(0,E9-E12)</f>
-        <v>106993.426790163</v>
+        <v>106149.932893595</v>
       </c>
       <c r="F13" s="19" t="n">
         <f aca="false">MAX(0,F9-F12)</f>
-        <v>111426.832509817</v>
+        <v>110248.041632392</v>
       </c>
       <c r="G13" s="19" t="n">
         <f aca="false">MAX(0,G9-G12)</f>
-        <v>116051.837003466</v>
+        <v>114506.963812029</v>
       </c>
       <c r="H13" s="19" t="n">
         <f aca="false">MAX(0,H9-H12)</f>
-        <v>120891.023403069</v>
+        <v>118946.801388027</v>
       </c>
       <c r="I13" s="19" t="n">
         <f aca="false">MAX(0,I9-I12)</f>
-        <v>125968.293035924</v>
+        <v>123588.780294378</v>
       </c>
       <c r="J13" s="19" t="n">
         <f aca="false">INDEX(C13:I13,1,Assumptions!E29)</f>
-        <v>116051.837003466</v>
+        <v>114506.963812029</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C14" s="27" t="n">
+      <c r="C14" s="26" t="n">
         <f aca="false">IFERROR(C13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>0.80954321556742</v>
-      </c>
-      <c r="D14" s="27" t="n">
+        <v>0.894960124840372</v>
+      </c>
+      <c r="D14" s="26" t="n">
         <f aca="false">IFERROR(D13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>0.843315558003296</v>
-      </c>
-      <c r="E14" s="27" t="n">
+        <v>0.929841185806055</v>
+      </c>
+      <c r="E14" s="26" t="n">
         <f aca="false">IFERROR(E13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>0.878312482527179</v>
-      </c>
-      <c r="F14" s="27" t="n">
+        <v>0.965839864670048</v>
+      </c>
+      <c r="F14" s="26" t="n">
         <f aca="false">IFERROR(F13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>0.914706452703645</v>
-      </c>
-      <c r="G14" s="27" t="n">
+        <v>1.00312784669497</v>
+      </c>
+      <c r="G14" s="26" t="n">
         <f aca="false">IFERROR(G13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>0.952673263379626</v>
-      </c>
-      <c r="H14" s="27" t="n">
+        <v>1.04187904238102</v>
+      </c>
+      <c r="H14" s="26" t="n">
         <f aca="false">IFERROR(H13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>0.992398300211864</v>
-      </c>
-      <c r="I14" s="27" t="n">
+        <v>1.0822763559418</v>
+      </c>
+      <c r="I14" s="26" t="n">
         <f aca="false">IFERROR(I13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>1.03407776996507</v>
-      </c>
-      <c r="J14" s="27" t="n">
+        <v>1.12451291847647</v>
+      </c>
+      <c r="J14" s="26" t="n">
         <f aca="false">INDEX(C14:I14,1,Assumptions!E29)</f>
-        <v>0.952673263379626</v>
+        <v>1.04187904238102</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2311,35 +2298,35 @@
       </c>
       <c r="C15" s="24" t="n">
         <f aca="false">IFERROR((C13/'Sources &amp; Uses'!$F$8)^(1/1)-1,0)</f>
-        <v>-0.19045678443258</v>
+        <v>-0.105039875159628</v>
       </c>
       <c r="D15" s="24" t="n">
         <f aca="false">IFERROR((D13/'Sources &amp; Uses'!$F$8)^(1/2)-1,0)</f>
-        <v>-0.0816778571746756</v>
+        <v>-0.0357172687400985</v>
       </c>
       <c r="E15" s="24" t="n">
         <f aca="false">IFERROR((E13/'Sources &amp; Uses'!$F$8)^(1/3)-1,0)</f>
-        <v>-0.0423289663639923</v>
+        <v>-0.0115188870758636</v>
       </c>
       <c r="F15" s="24" t="n">
         <f aca="false">IFERROR((F13/'Sources &amp; Uses'!$F$8)^(1/4)-1,0)</f>
-        <v>-0.0220414775936785</v>
+        <v>0.000781046147557918</v>
       </c>
       <c r="G15" s="24" t="n">
         <f aca="false">IFERROR((G13/'Sources &amp; Uses'!$F$8)^(1/5)-1,0)</f>
-        <v>-0.00964979595199322</v>
+        <v>0.00823892555745531</v>
       </c>
       <c r="H15" s="24" t="n">
         <f aca="false">IFERROR((H13/'Sources &amp; Uses'!$F$8)^(1/6)-1,0)</f>
-        <v>-0.0012709816130736</v>
+        <v>0.013264969325727</v>
       </c>
       <c r="I15" s="24" t="n">
         <f aca="false">IFERROR((I13/'Sources &amp; Uses'!$F$8)^(1/7)-1,0)</f>
-        <v>0.00479861752067445</v>
+        <v>0.0169055920708845</v>
       </c>
       <c r="J15" s="24" t="n">
         <f aca="false">INDEX(C15:I15,1,Assumptions!E29)</f>
-        <v>-0.00964979595199322</v>
+        <v>0.00823892555745531</v>
       </c>
     </row>
   </sheetData>
@@ -2362,7 +2349,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:G9"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
@@ -2383,145 +2370,145 @@
       <c r="B4" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="C4" s="32" t="n">
+      <c r="C4" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="D4" s="32" t="n">
+      <c r="D4" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="32" t="n">
+      <c r="E4" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="F4" s="32" t="n">
+      <c r="F4" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="G4" s="32" t="n">
+      <c r="G4" s="31" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="27" t="n">
+      <c r="B5" s="26" t="n">
         <v>8</v>
       </c>
       <c r="C5" s="22" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0541733166544571</v>
+        <v>-0.0581698451093956</v>
       </c>
       <c r="D5" s="22" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0170288187806811</v>
+        <v>0.0142785049827239</v>
       </c>
       <c r="E5" s="22" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0725363268430281</v>
+        <v>0.0705019893213061</v>
       </c>
       <c r="F5" s="22" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.11847980385338</v>
+        <v>0.116918290461881</v>
       </c>
       <c r="G5" s="22" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.157919494431067</v>
+        <v>0.156697512238684</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="27" t="n">
+      <c r="B6" s="26" t="n">
         <v>9</v>
       </c>
       <c r="C6" s="22" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.111668734051856</v>
+        <v>-0.115598250497523</v>
       </c>
       <c r="D6" s="22" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0447948720398664</v>
+        <v>-0.0475674625286657</v>
       </c>
       <c r="E6" s="22" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.00733841598732021</v>
+        <v>0.00522777624550885</v>
       </c>
       <c r="F6" s="22" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.050489056388269</v>
+        <v>0.0488138280628094</v>
       </c>
       <c r="G6" s="22" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0875312659985466</v>
+        <v>0.0861674986270506</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="27" t="n">
+      <c r="B7" s="26" t="n">
         <v>10</v>
       </c>
       <c r="C7" s="22" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.153024099676384</v>
+        <v>-0.156867181583465</v>
       </c>
       <c r="D7" s="22" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0892634828244395</v>
+        <v>-0.0920109213696565</v>
       </c>
       <c r="E7" s="22" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0395572074109225</v>
+        <v>-0.0416792723292913</v>
       </c>
       <c r="F7" s="22" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.00158459847173531</v>
+        <v>-0.000127080994252737</v>
       </c>
       <c r="G7" s="22" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0369023453948436</v>
+        <v>0.0354835513442162</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="27" t="n">
+      <c r="B8" s="26" t="n">
         <v>11</v>
       </c>
       <c r="C8" s="22" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.184986901879388</v>
+        <v>-0.188745283917349</v>
       </c>
       <c r="D8" s="22" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.123632455007017</v>
+        <v>-0.126341181246135</v>
       </c>
       <c r="E8" s="22" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.075801973047225</v>
+        <v>-0.0779125271120233</v>
       </c>
       <c r="F8" s="22" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0362127584522289</v>
+        <v>-0.0379313871921857</v>
       </c>
       <c r="G8" s="22" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0022278170537261</v>
+        <v>-0.00366716120520005</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="27" t="n">
+      <c r="B9" s="26" t="n">
         <v>12</v>
       </c>
       <c r="C9" s="22" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.210851123106239</v>
+        <v>-0.214531234724911</v>
       </c>
       <c r="D9" s="22" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.151443743085698</v>
+        <v>-0.154110663353755</v>
       </c>
       <c r="E9" s="22" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.105131148592559</v>
+        <v>-0.107221327103931</v>
       </c>
       <c r="F9" s="22" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0667982870633519</v>
+        <v>-0.0685109985418146</v>
       </c>
       <c r="G9" s="22" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0338918486296963</v>
+        <v>-0.0353358702552724</v>
       </c>
     </row>
   </sheetData>
@@ -2556,7 +2543,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:C13"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46"/>
@@ -2691,8 +2678,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:E12"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="B2:E11"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
@@ -2724,115 +2711,101 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="32" t="s">
         <v>279</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C5" s="32" t="s">
         <v>280</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="32" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="32" t="s">
         <v>283</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="32" t="s">
         <v>284</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="D6" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="32" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="32" t="s">
         <v>286</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="32" t="s">
         <v>287</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="D7" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="E7" s="32" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="32" t="s">
         <v>289</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="C8" s="32" t="s">
         <v>290</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="D8" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="33" t="s">
+      <c r="E8" s="32" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="32" t="s">
         <v>292</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="32" t="s">
         <v>293</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="32" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="33" t="s">
         <v>295</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="33" t="s">
         <v>296</v>
       </c>
-      <c r="D10" s="34" t="s">
+      <c r="D10" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="34" t="s">
+      <c r="E10" s="33" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="34" t="s">
+      <c r="B11" s="33" t="s">
         <v>298</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" s="33" t="s">
         <v>299</v>
       </c>
-      <c r="D11" s="34" t="s">
+      <c r="D11" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="34" t="s">
+      <c r="E11" s="33" t="s">
         <v>300</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="34" t="s">
-        <v>301</v>
-      </c>
-      <c r="C12" s="34" t="s">
-        <v>302</v>
-      </c>
-      <c r="D12" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="34" t="s">
-        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -2855,7 +2828,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:G29"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
@@ -2868,7 +2841,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -2881,232 +2854,232 @@
         <v>94</v>
       </c>
       <c r="C4" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="F4" s="16" t="s">
         <v>305</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="G4" s="16" t="s">
         <v>306</v>
       </c>
-      <c r="E4" s="16" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="34" t="s">
         <v>307</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="C5" s="34" t="s">
         <v>308</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="D5" s="34" t="s">
+        <v>299</v>
+      </c>
+      <c r="E5" s="34" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="35" t="s">
+      <c r="F5" s="34" t="s">
         <v>310</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="G5" s="34" t="s">
         <v>311</v>
       </c>
-      <c r="D5" s="35" t="s">
-        <v>299</v>
-      </c>
-      <c r="E5" s="35" t="s">
-        <v>312</v>
-      </c>
-      <c r="F5" s="35" t="s">
-        <v>313</v>
-      </c>
-      <c r="G5" s="35" t="s">
-        <v>314</v>
-      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="35"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="35"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="34"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="35"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="35"/>
+      <c r="B26" s="34"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="35"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="35"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="35"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="35"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
+      <c r="B29" s="34"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3128,7 +3101,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:F63"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="48"/>
@@ -3885,7 +3858,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:I9"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
@@ -4035,7 +4008,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:J8"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
@@ -4192,7 +4165,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:F32"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46"/>
@@ -4375,14 +4348,14 @@
         <v>137</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="D13" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="E13" s="27" t="n">
+      <c r="E13" s="26" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D13,C13)</f>
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>138</v>
@@ -4483,14 +4456,14 @@
         <v>144</v>
       </c>
       <c r="C19" s="25" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="D19" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" s="25" t="n">
         <v>3.5</v>
       </c>
-      <c r="E19" s="27" t="n">
+      <c r="E19" s="26" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D19,C19)</f>
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>145</v>
@@ -4537,14 +4510,14 @@
         <v>149</v>
       </c>
       <c r="C22" s="25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="D22" s="26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D22" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="27" t="n">
+      <c r="E22" s="26" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D22,C22)</f>
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>145</v>
@@ -4608,13 +4581,13 @@
       <c r="B26" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C26" s="26" t="n">
+      <c r="C26" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="D26" s="26" t="n">
+      <c r="D26" s="25" t="n">
         <v>6.5</v>
       </c>
-      <c r="E26" s="27" t="n">
+      <c r="E26" s="26" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D26,C26)</f>
         <v>7</v>
       </c>
@@ -4626,13 +4599,13 @@
       <c r="B27" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C27" s="26" t="n">
+      <c r="C27" s="25" t="n">
         <v>1.75</v>
       </c>
-      <c r="D27" s="26" t="n">
+      <c r="D27" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="E27" s="27" t="n">
+      <c r="E27" s="26" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D27,C27)</f>
         <v>1.75</v>
       </c>
@@ -4647,10 +4620,10 @@
       <c r="C28" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="D28" s="26" t="n">
+      <c r="D28" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="E28" s="27" t="n">
+      <c r="E28" s="26" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D28,C28)</f>
         <v>10</v>
       </c>
@@ -4662,13 +4635,13 @@
       <c r="B29" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C29" s="28" t="n">
+      <c r="C29" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="D29" s="28" t="n">
+      <c r="D29" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="E29" s="29" t="n">
+      <c r="E29" s="28" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D29,C29)</f>
         <v>5</v>
       </c>
@@ -4750,7 +4723,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:G10"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
@@ -4793,7 +4766,7 @@
       </c>
       <c r="C5" s="19" t="n">
         <f aca="false">Assumptions!E5*Assumptions!E6*Assumptions!E13</f>
-        <v>245262.7485</v>
+        <v>233583.57</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>169</v>
@@ -4815,7 +4788,7 @@
       </c>
       <c r="F6" s="19" t="n">
         <f aca="false">Assumptions!E5*Assumptions!E6*Assumptions!E19</f>
-        <v>99273.01725</v>
+        <v>93433.428</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4824,14 +4797,14 @@
       </c>
       <c r="C7" s="19" t="n">
         <f aca="false">C5*Assumptions!E14</f>
-        <v>4905.25497</v>
+        <v>4671.6714</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>173</v>
       </c>
       <c r="F7" s="19" t="n">
         <f aca="false">Assumptions!E5*Assumptions!E6*Assumptions!E22</f>
-        <v>29197.94625</v>
+        <v>35037.5355</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4847,23 +4820,23 @@
       </c>
       <c r="F8" s="19" t="n">
         <f aca="false">C9-SUM(F5:F7)</f>
-        <v>121817.03997</v>
+        <v>109904.2779</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="29" t="s">
         <v>176</v>
       </c>
-      <c r="C9" s="31" t="n">
+      <c r="C9" s="30" t="n">
         <f aca="false">SUM(C5:C8)</f>
-        <v>250288.00347</v>
-      </c>
-      <c r="E9" s="30" t="s">
+        <v>238375.2414</v>
+      </c>
+      <c r="E9" s="29" t="s">
         <v>177</v>
       </c>
-      <c r="F9" s="31" t="n">
+      <c r="F9" s="30" t="n">
         <f aca="false">SUM(F5:F8)</f>
-        <v>250288.00347</v>
+        <v>238375.2414</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4895,7 +4868,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:J19"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36"/>
@@ -5051,38 +5024,38 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="29" t="s">
         <v>192</v>
       </c>
-      <c r="C8" s="31" t="n">
+      <c r="C8" s="30" t="n">
         <f aca="false">C5*C7</f>
         <v>23358.357</v>
       </c>
-      <c r="D8" s="31" t="n">
+      <c r="D8" s="30" t="n">
         <f aca="false">D5*D7</f>
         <v>23398.05094</v>
       </c>
-      <c r="E8" s="31" t="n">
+      <c r="E8" s="30" t="n">
         <f aca="false">E5*E7</f>
         <v>23414.3407223</v>
       </c>
-      <c r="F8" s="31" t="n">
+      <c r="F8" s="30" t="n">
         <f aca="false">F5*F7</f>
         <v>23408.594871816</v>
       </c>
-      <c r="G8" s="31" t="n">
+      <c r="G8" s="30" t="n">
         <f aca="false">G5*G7</f>
         <v>23382.120865711</v>
       </c>
-      <c r="H8" s="31" t="n">
+      <c r="H8" s="30" t="n">
         <f aca="false">H5*H7</f>
         <v>23336.1675645876</v>
       </c>
-      <c r="I8" s="31" t="n">
+      <c r="I8" s="30" t="n">
         <f aca="false">I5*I7</f>
         <v>23271.9275527525</v>
       </c>
-      <c r="J8" s="31" t="n">
+      <c r="J8" s="30" t="n">
         <f aca="false">J5*J7</f>
         <v>23190.5393908194</v>
       </c>
@@ -5167,31 +5140,31 @@
       </c>
       <c r="D11" s="19" t="n">
         <f aca="false">'Debt Schedule'!D7</f>
-        <v>11649.98055375</v>
+        <v>11795.970285</v>
       </c>
       <c r="E11" s="19" t="n">
         <f aca="false">'Debt Schedule'!E7</f>
-        <v>11330.5966181139</v>
+        <v>11505.1319040023</v>
       </c>
       <c r="F11" s="19" t="n">
         <f aca="false">'Debt Schedule'!F7</f>
-        <v>10959.8723196736</v>
+        <v>11165.6387475201</v>
       </c>
       <c r="G11" s="19" t="n">
         <f aca="false">'Debt Schedule'!G7</f>
-        <v>10553.3547778563</v>
+        <v>10793.1016843274</v>
       </c>
       <c r="H11" s="19" t="n">
         <f aca="false">'Debt Schedule'!H7</f>
-        <v>10111.1115087954</v>
+        <v>10387.7988438072</v>
       </c>
       <c r="I11" s="19" t="n">
         <f aca="false">'Debt Schedule'!I7</f>
-        <v>9632.14718477652</v>
+        <v>9948.97027364607</v>
       </c>
       <c r="J11" s="19" t="n">
         <f aca="false">'Debt Schedule'!J7</f>
-        <v>9115.24027114113</v>
+        <v>9475.64867775454</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5200,31 +5173,31 @@
       </c>
       <c r="D12" s="19" t="n">
         <f aca="false">D10-D11</f>
-        <v>8045.84713625</v>
+        <v>7899.857405</v>
       </c>
       <c r="E12" s="19" t="n">
         <f aca="false">E10-E11</f>
-        <v>8492.58755168613</v>
+        <v>8318.05226579765</v>
       </c>
       <c r="F12" s="19" t="n">
         <f aca="false">F10-F11</f>
-        <v>8965.30069621743</v>
+        <v>8759.5342683709</v>
       </c>
       <c r="G12" s="19" t="n">
         <f aca="false">G10-G11</f>
-        <v>9449.84688760741</v>
+        <v>9210.09998113632</v>
       </c>
       <c r="H12" s="19" t="n">
         <f aca="false">H10-H11</f>
-        <v>9947.50443155237</v>
+        <v>9670.81709654059</v>
       </c>
       <c r="I12" s="19" t="n">
         <f aca="false">I10-I11</f>
-        <v>10460.5552924634</v>
+        <v>10143.7322035938</v>
       </c>
       <c r="J12" s="19" t="n">
         <f aca="false">J10-J11</f>
-        <v>10991.450796431</v>
+        <v>10631.0423898176</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5233,31 +5206,31 @@
       </c>
       <c r="D13" s="19" t="n">
         <f aca="false">MAX(0,D12*Assumptions!$E$12)</f>
-        <v>2011.4617840625</v>
+        <v>1974.96435125</v>
       </c>
       <c r="E13" s="19" t="n">
         <f aca="false">MAX(0,E12*Assumptions!$E$12)</f>
-        <v>2123.14688792153</v>
+        <v>2079.51306644941</v>
       </c>
       <c r="F13" s="19" t="n">
         <f aca="false">MAX(0,F12*Assumptions!$E$12)</f>
-        <v>2241.32517405436</v>
+        <v>2189.88356709272</v>
       </c>
       <c r="G13" s="19" t="n">
         <f aca="false">MAX(0,G12*Assumptions!$E$12)</f>
-        <v>2362.46172190185</v>
+        <v>2302.52499528408</v>
       </c>
       <c r="H13" s="19" t="n">
         <f aca="false">MAX(0,H12*Assumptions!$E$12)</f>
-        <v>2486.87610788809</v>
+        <v>2417.70427413515</v>
       </c>
       <c r="I13" s="19" t="n">
         <f aca="false">MAX(0,I12*Assumptions!$E$12)</f>
-        <v>2615.13882311584</v>
+        <v>2535.93305089845</v>
       </c>
       <c r="J13" s="19" t="n">
         <f aca="false">MAX(0,J12*Assumptions!$E$12)</f>
-        <v>2747.86269910775</v>
+        <v>2657.7605974544</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5266,31 +5239,31 @@
       </c>
       <c r="D14" s="19" t="n">
         <f aca="false">D12-D13</f>
-        <v>6034.3853521875</v>
+        <v>5924.89305375</v>
       </c>
       <c r="E14" s="19" t="n">
         <f aca="false">E12-E13</f>
-        <v>6369.4406637646</v>
+        <v>6238.53919934824</v>
       </c>
       <c r="F14" s="19" t="n">
         <f aca="false">F12-F13</f>
-        <v>6723.97552216307</v>
+        <v>6569.65070127817</v>
       </c>
       <c r="G14" s="19" t="n">
         <f aca="false">G12-G13</f>
-        <v>7087.38516570556</v>
+        <v>6907.57498585224</v>
       </c>
       <c r="H14" s="19" t="n">
         <f aca="false">H12-H13</f>
-        <v>7460.62832366428</v>
+        <v>7253.11282240544</v>
       </c>
       <c r="I14" s="19" t="n">
         <f aca="false">I12-I13</f>
-        <v>7845.41646934752</v>
+        <v>7607.79915269535</v>
       </c>
       <c r="J14" s="19" t="n">
         <f aca="false">J12-J13</f>
-        <v>8243.58809732325</v>
+        <v>7973.28179236319</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5397,71 +5370,71 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="29" t="s">
         <v>202</v>
       </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31" t="n">
+      <c r="C18" s="30"/>
+      <c r="D18" s="30" t="n">
         <f aca="false">D14+D9-D15-D17</f>
-        <v>4919.9016521875</v>
-      </c>
-      <c r="E18" s="31" t="n">
+        <v>4810.40935375</v>
+      </c>
+      <c r="E18" s="30" t="n">
         <f aca="false">E14+E9-E15-E17</f>
-        <v>5288.3914747646</v>
-      </c>
-      <c r="F18" s="31" t="n">
+        <v>5157.49001034824</v>
+      </c>
+      <c r="F18" s="30" t="n">
         <f aca="false">F14+F9-F15-F17</f>
-        <v>5675.35780883307</v>
-      </c>
-      <c r="G18" s="31" t="n">
+        <v>5521.03298794817</v>
+      </c>
+      <c r="G18" s="30" t="n">
         <f aca="false">G14+G9-G15-G17</f>
-        <v>6070.22598377546</v>
-      </c>
-      <c r="H18" s="31" t="n">
+        <v>5890.41580392214</v>
+      </c>
+      <c r="H18" s="30" t="n">
         <f aca="false">H14+H9-H15-H17</f>
-        <v>6473.98391719208</v>
-      </c>
-      <c r="I18" s="31" t="n">
+        <v>6266.46841593325</v>
+      </c>
+      <c r="I18" s="30" t="n">
         <f aca="false">I14+I9-I15-I17</f>
-        <v>6888.37139506949</v>
-      </c>
-      <c r="J18" s="31" t="n">
+        <v>6650.75407841732</v>
+      </c>
+      <c r="J18" s="30" t="n">
         <f aca="false">J14+J9-J15-J17</f>
-        <v>7315.25437527356</v>
+        <v>7044.9480703135</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="30" t="s">
+      <c r="B19" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31" t="n">
+      <c r="C19" s="30"/>
+      <c r="D19" s="30" t="n">
         <f aca="false">D8-D13-D15-D17</f>
-        <v>16569.8822059375</v>
-      </c>
-      <c r="E19" s="31" t="n">
+        <v>16606.37963875</v>
+      </c>
+      <c r="E19" s="30" t="n">
         <f aca="false">E8-E13-E15-E17</f>
-        <v>16618.9880928785</v>
-      </c>
-      <c r="F19" s="31" t="n">
+        <v>16662.6219143506</v>
+      </c>
+      <c r="F19" s="30" t="n">
         <f aca="false">F8-F13-F15-F17</f>
-        <v>16635.2301285066</v>
-      </c>
-      <c r="G19" s="31" t="n">
+        <v>16686.6717354683</v>
+      </c>
+      <c r="G19" s="30" t="n">
         <f aca="false">G8-G13-G15-G17</f>
-        <v>16623.5807616318</v>
-      </c>
-      <c r="H19" s="31" t="n">
+        <v>16683.5174882495</v>
+      </c>
+      <c r="H19" s="30" t="n">
         <f aca="false">H8-H13-H15-H17</f>
-        <v>16585.0954259875</v>
-      </c>
-      <c r="I19" s="31" t="n">
+        <v>16654.2672597404</v>
+      </c>
+      <c r="I19" s="30" t="n">
         <f aca="false">I8-I13-I15-I17</f>
-        <v>16520.518579846</v>
-      </c>
-      <c r="J19" s="31" t="n">
+        <v>16599.7243520634</v>
+      </c>
+      <c r="J19" s="30" t="n">
         <f aca="false">J8-J13-J15-J17</f>
-        <v>16430.4946464147</v>
+        <v>16520.596748068</v>
       </c>
     </row>
   </sheetData>
@@ -5484,7 +5457,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:J28"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42"/>
@@ -5546,27 +5519,27 @@
       </c>
       <c r="E5" s="19" t="n">
         <f aca="false">D13</f>
-        <v>265.448217480469</v>
+        <v>262.254692109375</v>
       </c>
       <c r="F5" s="19" t="n">
         <f aca="false">E13</f>
-        <v>303.819344984067</v>
+        <v>299.088151403601</v>
       </c>
       <c r="G5" s="19" t="n">
         <f aca="false">F13</f>
-        <v>330.402936332321</v>
+        <v>324.111678709486</v>
       </c>
       <c r="H5" s="19" t="n">
         <f aca="false">G13</f>
-        <v>356.743671725486</v>
+        <v>348.762075164477</v>
       </c>
       <c r="I5" s="19" t="n">
         <f aca="false">H13</f>
-        <v>383.624838526098</v>
+        <v>373.806013193608</v>
       </c>
       <c r="J5" s="19" t="n">
         <f aca="false">I13</f>
-        <v>411.204128818474</v>
+        <v>399.389113225683</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5575,31 +5548,31 @@
       </c>
       <c r="D6" s="19" t="n">
         <f aca="false">'Operating Model'!D19</f>
-        <v>16569.8822059375</v>
+        <v>16606.37963875</v>
       </c>
       <c r="E6" s="19" t="n">
         <f aca="false">'Operating Model'!E19</f>
-        <v>16618.9880928785</v>
+        <v>16662.6219143506</v>
       </c>
       <c r="F6" s="19" t="n">
         <f aca="false">'Operating Model'!F19</f>
-        <v>16635.2301285066</v>
+        <v>16686.6717354683</v>
       </c>
       <c r="G6" s="19" t="n">
         <f aca="false">'Operating Model'!G19</f>
-        <v>16623.5807616318</v>
+        <v>16683.5174882495</v>
       </c>
       <c r="H6" s="19" t="n">
         <f aca="false">'Operating Model'!H19</f>
-        <v>16585.0954259875</v>
+        <v>16654.2672597404</v>
       </c>
       <c r="I6" s="19" t="n">
         <f aca="false">'Operating Model'!I19</f>
-        <v>16520.518579846</v>
+        <v>16599.7243520634</v>
       </c>
       <c r="J6" s="19" t="n">
         <f aca="false">'Operating Model'!J19</f>
-        <v>16430.4946464147</v>
+        <v>16520.596748068</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5608,31 +5581,31 @@
       </c>
       <c r="D7" s="19" t="n">
         <f aca="false">SUM(D15,D18,D23)</f>
-        <v>11649.98055375</v>
+        <v>11795.970285</v>
       </c>
       <c r="E7" s="19" t="n">
         <f aca="false">SUM(E15,E18,E23)</f>
-        <v>11330.5966181139</v>
+        <v>11505.1319040023</v>
       </c>
       <c r="F7" s="19" t="n">
         <f aca="false">SUM(F15,F18,F23)</f>
-        <v>10959.8723196736</v>
+        <v>11165.6387475201</v>
       </c>
       <c r="G7" s="19" t="n">
         <f aca="false">SUM(G15,G18,G23)</f>
-        <v>10553.3547778563</v>
+        <v>10793.1016843274</v>
       </c>
       <c r="H7" s="19" t="n">
         <f aca="false">SUM(H15,H18,H23)</f>
-        <v>10111.1115087954</v>
+        <v>10387.7988438072</v>
       </c>
       <c r="I7" s="19" t="n">
         <f aca="false">SUM(I15,I18,I23)</f>
-        <v>9632.14718477652</v>
+        <v>9948.97027364607</v>
       </c>
       <c r="J7" s="19" t="n">
         <f aca="false">SUM(J15,J18,J23)</f>
-        <v>9115.24027114113</v>
+        <v>9475.64867775454</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5641,31 +5614,31 @@
       </c>
       <c r="D8" s="19" t="n">
         <f aca="false">D19</f>
-        <v>992.7301725</v>
+        <v>934.33428</v>
       </c>
       <c r="E8" s="19" t="n">
         <f aca="false">E19</f>
-        <v>992.7301725</v>
+        <v>934.33428</v>
       </c>
       <c r="F8" s="19" t="n">
         <f aca="false">F19</f>
-        <v>992.7301725</v>
+        <v>934.33428</v>
       </c>
       <c r="G8" s="19" t="n">
         <f aca="false">G19</f>
-        <v>992.7301725</v>
+        <v>934.33428</v>
       </c>
       <c r="H8" s="19" t="n">
         <f aca="false">H19</f>
-        <v>992.7301725</v>
+        <v>934.33428</v>
       </c>
       <c r="I8" s="19" t="n">
         <f aca="false">I19</f>
-        <v>992.7301725</v>
+        <v>934.33428</v>
       </c>
       <c r="J8" s="19" t="n">
         <f aca="false">J19</f>
-        <v>992.7301725</v>
+        <v>934.33428</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5674,31 +5647,31 @@
       </c>
       <c r="D9" s="19" t="n">
         <f aca="false">D5+D6-D7-D8</f>
-        <v>3947.1714796875</v>
+        <v>3896.07507375</v>
       </c>
       <c r="E9" s="19" t="n">
         <f aca="false">E5+E6-E7-E8</f>
-        <v>4561.10951974507</v>
+        <v>4485.41042245762</v>
       </c>
       <c r="F9" s="19" t="n">
         <f aca="false">F5+F6-F7-F8</f>
-        <v>4986.44698131714</v>
+        <v>4885.78685935178</v>
       </c>
       <c r="G9" s="19" t="n">
         <f aca="false">G5+G6-G7-G8</f>
-        <v>5407.89874760778</v>
+        <v>5280.19320263163</v>
       </c>
       <c r="H9" s="19" t="n">
         <f aca="false">H5+H6-H7-H8</f>
-        <v>5837.99741641757</v>
+        <v>5680.89621109773</v>
       </c>
       <c r="I9" s="19" t="n">
         <f aca="false">I5+I6-I7-I8</f>
-        <v>6279.26606109558</v>
+        <v>6090.22581161093</v>
       </c>
       <c r="J9" s="19" t="n">
         <f aca="false">J5+J6-J7-J8</f>
-        <v>6733.72833159203</v>
+        <v>6510.00290353918</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5740,31 +5713,31 @@
       </c>
       <c r="D11" s="19" t="n">
         <f aca="false">MIN(MAX(0,D17-D19),MAX(0,D9+D10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>2945.37860976562</v>
+        <v>2907.0563053125</v>
       </c>
       <c r="E11" s="19" t="n">
         <f aca="false">MIN(MAX(0,E17-E19),MAX(0,E9+E10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>3405.8321398088</v>
+        <v>3349.05781684321</v>
       </c>
       <c r="F11" s="19" t="n">
         <f aca="false">MIN(MAX(0,F17-F19),MAX(0,F9+F10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>3724.83523598785</v>
+        <v>3649.34014451383</v>
       </c>
       <c r="G11" s="19" t="n">
         <f aca="false">MIN(MAX(0,G17-G19),MAX(0,G9+G10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>4040.92406070584</v>
+        <v>3945.14490197372</v>
       </c>
       <c r="H11" s="19" t="n">
         <f aca="false">MIN(MAX(0,H17-H19),MAX(0,H9+H10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>4363.49806231318</v>
+        <v>4245.67215832329</v>
       </c>
       <c r="I11" s="19" t="n">
         <f aca="false">MIN(MAX(0,I17-I19),MAX(0,I9+I10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>4694.44954582169</v>
+        <v>4552.6693587082</v>
       </c>
       <c r="J11" s="19" t="n">
         <f aca="false">MIN(MAX(0,J17-J19),MAX(0,J9+J10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>5035.29624869402</v>
+        <v>4867.50217765439</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5773,68 +5746,68 @@
       </c>
       <c r="D12" s="19" t="n">
         <f aca="false">MIN(MAX(0,D22+D24),MAX(0,D9+D10-D11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>736.344652441406</v>
+        <v>726.764076328124</v>
       </c>
       <c r="E12" s="19" t="n">
         <f aca="false">MIN(MAX(0,E22+E24),MAX(0,E9+E10-E11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>851.458034952201</v>
+        <v>837.264454210804</v>
       </c>
       <c r="F12" s="19" t="n">
         <f aca="false">MIN(MAX(0,F22+F24),MAX(0,F9+F10-F11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>931.208808996963</v>
+        <v>912.335036128458</v>
       </c>
       <c r="G12" s="19" t="n">
         <f aca="false">MIN(MAX(0,G22+G24),MAX(0,G9+G10-G11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>1010.23101517646</v>
+        <v>986.28622549343</v>
       </c>
       <c r="H12" s="19" t="n">
         <f aca="false">MIN(MAX(0,H22+H24),MAX(0,H9+H10-H11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>1090.87451557829</v>
+        <v>1061.41803958082</v>
       </c>
       <c r="I12" s="19" t="n">
         <f aca="false">MIN(MAX(0,I22+I24),MAX(0,I9+I10-I11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>1173.61238645542</v>
+        <v>1138.16733967705</v>
       </c>
       <c r="J12" s="19" t="n">
         <f aca="false">MIN(MAX(0,J22+J24),MAX(0,J9+J10-J11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>1258.82406217351</v>
+        <v>1216.8755444136</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="C13" s="31" t="n">
+      <c r="C13" s="30" t="n">
         <f aca="false">C5</f>
         <v>20</v>
       </c>
-      <c r="D13" s="31" t="n">
+      <c r="D13" s="30" t="n">
         <f aca="false">D9+D10-D11-D12</f>
-        <v>265.448217480469</v>
-      </c>
-      <c r="E13" s="31" t="n">
+        <v>262.254692109375</v>
+      </c>
+      <c r="E13" s="30" t="n">
         <f aca="false">E9+E10-E11-E12</f>
-        <v>303.819344984067</v>
-      </c>
-      <c r="F13" s="31" t="n">
+        <v>299.088151403601</v>
+      </c>
+      <c r="F13" s="30" t="n">
         <f aca="false">F9+F10-F11-F12</f>
-        <v>330.402936332321</v>
-      </c>
-      <c r="G13" s="31" t="n">
+        <v>324.111678709486</v>
+      </c>
+      <c r="G13" s="30" t="n">
         <f aca="false">G9+G10-G11-G12</f>
-        <v>356.743671725486</v>
-      </c>
-      <c r="H13" s="31" t="n">
+        <v>348.762075164477</v>
+      </c>
+      <c r="H13" s="30" t="n">
         <f aca="false">H9+H10-H11-H12</f>
-        <v>383.624838526098</v>
-      </c>
-      <c r="I13" s="31" t="n">
+        <v>373.806013193608</v>
+      </c>
+      <c r="I13" s="30" t="n">
         <f aca="false">I9+I10-I11-I12</f>
-        <v>411.204128818474</v>
-      </c>
-      <c r="J13" s="31" t="n">
+        <v>399.389113225683</v>
+      </c>
+      <c r="J13" s="30" t="n">
         <f aca="false">J9+J10-J11-J12</f>
-        <v>439.608020724502</v>
+        <v>425.625181471199</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5950,35 +5923,35 @@
       </c>
       <c r="C17" s="19" t="n">
         <f aca="false">'Sources &amp; Uses'!F6</f>
-        <v>99273.01725</v>
+        <v>93433.428</v>
       </c>
       <c r="D17" s="19" t="n">
         <f aca="false">C21</f>
-        <v>99273.01725</v>
+        <v>93433.428</v>
       </c>
       <c r="E17" s="19" t="n">
         <f aca="false">D21</f>
-        <v>95334.9084677344</v>
+        <v>89592.0374146875</v>
       </c>
       <c r="F17" s="19" t="n">
         <f aca="false">E21</f>
-        <v>90936.3461554256</v>
+        <v>85308.6453178443</v>
       </c>
       <c r="G17" s="19" t="n">
         <f aca="false">F21</f>
-        <v>86218.7807469377</v>
+        <v>80724.9708933305</v>
       </c>
       <c r="H17" s="19" t="n">
         <f aca="false">G21</f>
-        <v>81185.1265137319</v>
+        <v>75845.4917113568</v>
       </c>
       <c r="I17" s="19" t="n">
         <f aca="false">H21</f>
-        <v>75828.8982789187</v>
+        <v>70665.4852730335</v>
       </c>
       <c r="J17" s="19" t="n">
         <f aca="false">I21</f>
-        <v>70141.718560597</v>
+        <v>65178.4816343253</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5987,31 +5960,31 @@
       </c>
       <c r="D18" s="19" t="n">
         <f aca="false">D17*Assumptions!$E$20</f>
-        <v>8438.20646625</v>
+        <v>7941.84138</v>
       </c>
       <c r="E18" s="19" t="n">
         <f aca="false">E17*Assumptions!$E$20</f>
-        <v>8103.46721975742</v>
+        <v>7615.32318024844</v>
       </c>
       <c r="F18" s="19" t="n">
         <f aca="false">F17*Assumptions!$E$20</f>
-        <v>7729.58942321118</v>
+        <v>7251.23485201677</v>
       </c>
       <c r="G18" s="19" t="n">
         <f aca="false">G17*Assumptions!$E$20</f>
-        <v>7328.59636348971</v>
+        <v>6861.62252593309</v>
       </c>
       <c r="H18" s="19" t="n">
         <f aca="false">H17*Assumptions!$E$20</f>
-        <v>6900.73575366721</v>
+        <v>6446.86679546533</v>
       </c>
       <c r="I18" s="19" t="n">
         <f aca="false">I17*Assumptions!$E$20</f>
-        <v>6445.45635370809</v>
+        <v>6006.56624820785</v>
       </c>
       <c r="J18" s="19" t="n">
         <f aca="false">J17*Assumptions!$E$20</f>
-        <v>5962.04607765075</v>
+        <v>5540.17093891765</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6020,68 +5993,68 @@
       </c>
       <c r="D19" s="19" t="n">
         <f aca="false">MIN(D17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
-        <v>992.7301725</v>
+        <v>934.33428</v>
       </c>
       <c r="E19" s="19" t="n">
         <f aca="false">MIN(E17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
-        <v>992.7301725</v>
+        <v>934.33428</v>
       </c>
       <c r="F19" s="19" t="n">
         <f aca="false">MIN(F17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
-        <v>992.7301725</v>
+        <v>934.33428</v>
       </c>
       <c r="G19" s="19" t="n">
         <f aca="false">MIN(G17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
-        <v>992.7301725</v>
+        <v>934.33428</v>
       </c>
       <c r="H19" s="19" t="n">
         <f aca="false">MIN(H17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
-        <v>992.7301725</v>
+        <v>934.33428</v>
       </c>
       <c r="I19" s="19" t="n">
         <f aca="false">MIN(I17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
-        <v>992.7301725</v>
+        <v>934.33428</v>
       </c>
       <c r="J19" s="19" t="n">
         <f aca="false">MIN(J17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
-        <v>992.7301725</v>
+        <v>934.33428</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="29" t="s">
         <v>219</v>
       </c>
-      <c r="C20" s="31" t="n">
+      <c r="C20" s="30" t="n">
         <f aca="false">'Sources &amp; Uses'!F7</f>
-        <v>29197.94625</v>
-      </c>
-      <c r="D20" s="31" t="n">
+        <v>35037.5355</v>
+      </c>
+      <c r="D20" s="30" t="n">
         <f aca="false">D11</f>
-        <v>2945.37860976562</v>
-      </c>
-      <c r="E20" s="31" t="n">
+        <v>2907.0563053125</v>
+      </c>
+      <c r="E20" s="30" t="n">
         <f aca="false">E11</f>
-        <v>3405.8321398088</v>
-      </c>
-      <c r="F20" s="31" t="n">
+        <v>3349.05781684321</v>
+      </c>
+      <c r="F20" s="30" t="n">
         <f aca="false">F11</f>
-        <v>3724.83523598785</v>
-      </c>
-      <c r="G20" s="31" t="n">
+        <v>3649.34014451383</v>
+      </c>
+      <c r="G20" s="30" t="n">
         <f aca="false">G11</f>
-        <v>4040.92406070584</v>
-      </c>
-      <c r="H20" s="31" t="n">
+        <v>3945.14490197372</v>
+      </c>
+      <c r="H20" s="30" t="n">
         <f aca="false">H11</f>
-        <v>4363.49806231318</v>
-      </c>
-      <c r="I20" s="31" t="n">
+        <v>4245.67215832329</v>
+      </c>
+      <c r="I20" s="30" t="n">
         <f aca="false">I11</f>
-        <v>4694.44954582169</v>
-      </c>
-      <c r="J20" s="31" t="n">
+        <v>4552.6693587082</v>
+      </c>
+      <c r="J20" s="30" t="n">
         <f aca="false">J11</f>
-        <v>5035.29624869402</v>
+        <v>4867.50217765439</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6090,35 +6063,35 @@
       </c>
       <c r="C21" s="19" t="n">
         <f aca="false">C17</f>
-        <v>99273.01725</v>
+        <v>93433.428</v>
       </c>
       <c r="D21" s="19" t="n">
         <f aca="false">MAX(0,D17-D19-D20)</f>
-        <v>95334.9084677344</v>
+        <v>89592.0374146875</v>
       </c>
       <c r="E21" s="19" t="n">
         <f aca="false">MAX(0,E17-E19-E20)</f>
-        <v>90936.3461554256</v>
+        <v>85308.6453178443</v>
       </c>
       <c r="F21" s="19" t="n">
         <f aca="false">MAX(0,F17-F19-F20)</f>
-        <v>86218.7807469377</v>
+        <v>80724.9708933305</v>
       </c>
       <c r="G21" s="19" t="n">
         <f aca="false">MAX(0,G17-G19-G20)</f>
-        <v>81185.1265137319</v>
+        <v>75845.4917113568</v>
       </c>
       <c r="H21" s="19" t="n">
         <f aca="false">MAX(0,H17-H19-H20)</f>
-        <v>75828.8982789187</v>
+        <v>70665.4852730335</v>
       </c>
       <c r="I21" s="19" t="n">
         <f aca="false">MAX(0,I17-I19-I20)</f>
-        <v>70141.718560597</v>
+        <v>65178.4816343253</v>
       </c>
       <c r="J21" s="19" t="n">
         <f aca="false">MAX(0,J17-J19-J20)</f>
-        <v>64113.692139403</v>
+        <v>59376.6451766709</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6127,35 +6100,35 @@
       </c>
       <c r="C22" s="19" t="n">
         <f aca="false">'Sources &amp; Uses'!F7</f>
-        <v>29197.94625</v>
+        <v>35037.5355</v>
       </c>
       <c r="D22" s="19" t="n">
         <f aca="false">C26</f>
-        <v>29197.94625</v>
+        <v>35037.5355</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">D26</f>
-        <v>29337.5399850586</v>
+        <v>35361.8974886719</v>
       </c>
       <c r="F22" s="19" t="n">
         <f aca="false">E26</f>
-        <v>29366.2081496582</v>
+        <v>35585.4899591212</v>
       </c>
       <c r="G22" s="19" t="n">
         <f aca="false">F26</f>
-        <v>29315.9855851509</v>
+        <v>35740.7196217664</v>
       </c>
       <c r="H22" s="19" t="n">
         <f aca="false">G26</f>
-        <v>29185.234137529</v>
+        <v>35826.654984926</v>
       </c>
       <c r="I22" s="19" t="n">
         <f aca="false">H26</f>
-        <v>28969.9166460766</v>
+        <v>35840.0365948929</v>
       </c>
       <c r="J22" s="19" t="n">
         <f aca="false">I26</f>
-        <v>28665.4017590035</v>
+        <v>35777.0703530627</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6164,139 +6137,139 @@
       </c>
       <c r="D23" s="19" t="n">
         <f aca="false">D22*Assumptions!$E$23</f>
-        <v>3211.7740875</v>
+        <v>3854.128905</v>
       </c>
       <c r="E23" s="19" t="n">
         <f aca="false">E22*Assumptions!$E$23</f>
-        <v>3227.12939835645</v>
+        <v>3889.80872375391</v>
       </c>
       <c r="F23" s="19" t="n">
         <f aca="false">F22*Assumptions!$E$23</f>
-        <v>3230.2828964624</v>
+        <v>3914.40389550333</v>
       </c>
       <c r="G23" s="19" t="n">
         <f aca="false">G22*Assumptions!$E$23</f>
-        <v>3224.7584143666</v>
+        <v>3931.4791583943</v>
       </c>
       <c r="H23" s="19" t="n">
         <f aca="false">H22*Assumptions!$E$23</f>
-        <v>3210.37575512819</v>
+        <v>3940.93204834186</v>
       </c>
       <c r="I23" s="19" t="n">
         <f aca="false">I22*Assumptions!$E$23</f>
-        <v>3186.69083106842</v>
+        <v>3942.40402543822</v>
       </c>
       <c r="J23" s="19" t="n">
         <f aca="false">J22*Assumptions!$E$23</f>
-        <v>3153.19419349038</v>
+        <v>3935.47773883689</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="30" t="s">
+      <c r="B24" s="29" t="s">
         <v>223</v>
       </c>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31" t="n">
+      <c r="C24" s="30"/>
+      <c r="D24" s="30" t="n">
         <f aca="false">D22*Assumptions!$E$24</f>
-        <v>875.9383875</v>
-      </c>
-      <c r="E24" s="31" t="n">
+        <v>1051.126065</v>
+      </c>
+      <c r="E24" s="30" t="n">
         <f aca="false">E22*Assumptions!$E$24</f>
-        <v>880.126199551758</v>
-      </c>
-      <c r="F24" s="31" t="n">
+        <v>1060.85692466016</v>
+      </c>
+      <c r="F24" s="30" t="n">
         <f aca="false">F22*Assumptions!$E$24</f>
-        <v>880.986244489744</v>
-      </c>
-      <c r="G24" s="31" t="n">
+        <v>1067.56469877364</v>
+      </c>
+      <c r="G24" s="30" t="n">
         <f aca="false">G22*Assumptions!$E$24</f>
-        <v>879.479567554528</v>
-      </c>
-      <c r="H24" s="31" t="n">
+        <v>1072.22158865299</v>
+      </c>
+      <c r="H24" s="30" t="n">
         <f aca="false">H22*Assumptions!$E$24</f>
-        <v>875.55702412587</v>
-      </c>
-      <c r="I24" s="31" t="n">
+        <v>1074.79964954778</v>
+      </c>
+      <c r="I24" s="30" t="n">
         <f aca="false">I22*Assumptions!$E$24</f>
-        <v>869.097499382297</v>
-      </c>
-      <c r="J24" s="31" t="n">
+        <v>1075.20109784679</v>
+      </c>
+      <c r="J24" s="30" t="n">
         <f aca="false">J22*Assumptions!$E$24</f>
-        <v>859.962052770104</v>
+        <v>1073.31211059188</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="30" t="s">
+      <c r="B25" s="29" t="s">
         <v>224</v>
       </c>
-      <c r="C25" s="31" t="n">
+      <c r="C25" s="30" t="n">
         <f aca="false">SUM(C16,C20,C13)</f>
-        <v>29217.94625</v>
-      </c>
-      <c r="D25" s="31" t="n">
+        <v>35057.5355</v>
+      </c>
+      <c r="D25" s="30" t="n">
         <f aca="false">D12</f>
-        <v>736.344652441406</v>
-      </c>
-      <c r="E25" s="31" t="n">
+        <v>726.764076328124</v>
+      </c>
+      <c r="E25" s="30" t="n">
         <f aca="false">E12</f>
-        <v>851.458034952201</v>
-      </c>
-      <c r="F25" s="31" t="n">
+        <v>837.264454210804</v>
+      </c>
+      <c r="F25" s="30" t="n">
         <f aca="false">F12</f>
-        <v>931.208808996963</v>
-      </c>
-      <c r="G25" s="31" t="n">
+        <v>912.335036128458</v>
+      </c>
+      <c r="G25" s="30" t="n">
         <f aca="false">G12</f>
-        <v>1010.23101517646</v>
-      </c>
-      <c r="H25" s="31" t="n">
+        <v>986.28622549343</v>
+      </c>
+      <c r="H25" s="30" t="n">
         <f aca="false">H12</f>
-        <v>1090.87451557829</v>
-      </c>
-      <c r="I25" s="31" t="n">
+        <v>1061.41803958082</v>
+      </c>
+      <c r="I25" s="30" t="n">
         <f aca="false">I12</f>
-        <v>1173.61238645542</v>
-      </c>
-      <c r="J25" s="31" t="n">
+        <v>1138.16733967705</v>
+      </c>
+      <c r="J25" s="30" t="n">
         <f aca="false">J12</f>
-        <v>1258.82406217351</v>
+        <v>1216.8755444136</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="30" t="s">
+      <c r="B26" s="29" t="s">
         <v>225</v>
       </c>
-      <c r="C26" s="31" t="n">
+      <c r="C26" s="30" t="n">
         <f aca="false">C22</f>
-        <v>29197.94625</v>
-      </c>
-      <c r="D26" s="31" t="n">
+        <v>35037.5355</v>
+      </c>
+      <c r="D26" s="30" t="n">
         <f aca="false">MAX(0,D22+D24-D25)</f>
-        <v>29337.5399850586</v>
-      </c>
-      <c r="E26" s="31" t="n">
+        <v>35361.8974886719</v>
+      </c>
+      <c r="E26" s="30" t="n">
         <f aca="false">MAX(0,E22+E24-E25)</f>
-        <v>29366.2081496582</v>
-      </c>
-      <c r="F26" s="31" t="n">
+        <v>35585.4899591212</v>
+      </c>
+      <c r="F26" s="30" t="n">
         <f aca="false">MAX(0,F22+F24-F25)</f>
-        <v>29315.9855851509</v>
-      </c>
-      <c r="G26" s="31" t="n">
+        <v>35740.7196217664</v>
+      </c>
+      <c r="G26" s="30" t="n">
         <f aca="false">MAX(0,G22+G24-G25)</f>
-        <v>29185.234137529</v>
-      </c>
-      <c r="H26" s="31" t="n">
+        <v>35826.654984926</v>
+      </c>
+      <c r="H26" s="30" t="n">
         <f aca="false">MAX(0,H22+H24-H25)</f>
-        <v>28969.9166460766</v>
-      </c>
-      <c r="I26" s="31" t="n">
+        <v>35840.0365948929</v>
+      </c>
+      <c r="I26" s="30" t="n">
         <f aca="false">MAX(0,I22+I24-I25)</f>
-        <v>28665.4017590035</v>
-      </c>
-      <c r="J26" s="31" t="n">
+        <v>35777.0703530627</v>
+      </c>
+      <c r="J26" s="30" t="n">
         <f aca="false">MAX(0,J22+J24-J25)</f>
-        <v>28266.5397496001</v>
+        <v>35633.5069192409</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6309,31 +6282,31 @@
       </c>
       <c r="D27" s="19" t="n">
         <f aca="false">SUM(D16,D21,D26)</f>
-        <v>124672.448452793</v>
+        <v>124953.934903359</v>
       </c>
       <c r="E27" s="19" t="n">
         <f aca="false">SUM(E16,E21,E26)</f>
-        <v>120302.554305084</v>
+        <v>120894.135276966</v>
       </c>
       <c r="F27" s="19" t="n">
         <f aca="false">SUM(F16,F21,F26)</f>
-        <v>115534.766332089</v>
+        <v>116465.690515097</v>
       </c>
       <c r="G27" s="19" t="n">
         <f aca="false">SUM(G16,G21,G26)</f>
-        <v>110370.360651261</v>
+        <v>111672.146696283</v>
       </c>
       <c r="H27" s="19" t="n">
         <f aca="false">SUM(H16,H21,H26)</f>
-        <v>104798.814924995</v>
+        <v>106505.521867926</v>
       </c>
       <c r="I27" s="19" t="n">
         <f aca="false">SUM(I16,I21,I26)</f>
-        <v>98807.1203196005</v>
+        <v>100955.551987388</v>
       </c>
       <c r="J27" s="19" t="n">
         <f aca="false">SUM(J16,J21,J26)</f>
-        <v>92380.2318890031</v>
+        <v>95010.1520959118</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6346,31 +6319,31 @@
       </c>
       <c r="D28" s="19" t="n">
         <f aca="false">D27-D13</f>
-        <v>124407.000235313</v>
+        <v>124691.68021125</v>
       </c>
       <c r="E28" s="19" t="n">
         <f aca="false">E27-E13</f>
-        <v>119998.7349601</v>
+        <v>120595.047125562</v>
       </c>
       <c r="F28" s="19" t="n">
         <f aca="false">F27-F13</f>
-        <v>115204.363395756</v>
+        <v>116141.578836387</v>
       </c>
       <c r="G28" s="19" t="n">
         <f aca="false">G27-G13</f>
-        <v>110013.616979535</v>
+        <v>111323.384621118</v>
       </c>
       <c r="H28" s="19" t="n">
         <f aca="false">H27-H13</f>
-        <v>104415.190086469</v>
+        <v>106131.715854733</v>
       </c>
       <c r="I28" s="19" t="n">
         <f aca="false">I27-I13</f>
-        <v>98395.916190782</v>
+        <v>100556.162874162</v>
       </c>
       <c r="J28" s="19" t="n">
         <f aca="false">J27-J13</f>
-        <v>91940.6238682786</v>
+        <v>94584.5269144406</v>
       </c>
     </row>
   </sheetData>
@@ -6393,7 +6366,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:I13"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
@@ -6442,64 +6415,64 @@
       <c r="B5" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="26" t="n">
         <f aca="false">IFERROR('Debt Schedule'!D25/'Operating Model'!D8,0)</f>
-        <v>0.031470341454065</v>
-      </c>
-      <c r="D5" s="27" t="n">
+        <v>0.0310608810191831</v>
+      </c>
+      <c r="D5" s="26" t="n">
         <f aca="false">IFERROR('Debt Schedule'!E25/'Operating Model'!E8,0)</f>
-        <v>0.0363648092872103</v>
-      </c>
-      <c r="E5" s="27" t="n">
+        <v>0.0357586175131289</v>
+      </c>
+      <c r="E5" s="26" t="n">
         <f aca="false">IFERROR('Debt Schedule'!F25/'Operating Model'!F8,0)</f>
-        <v>0.0397806367317733</v>
-      </c>
-      <c r="F5" s="27" t="n">
+        <v>0.0389743613883853</v>
+      </c>
+      <c r="F5" s="26" t="n">
         <f aca="false">IFERROR('Debt Schedule'!G25/'Operating Model'!G8,0)</f>
-        <v>0.0432052772705459</v>
-      </c>
-      <c r="G5" s="27" t="n">
+        <v>0.0421812132080706</v>
+      </c>
+      <c r="G5" s="26" t="n">
         <f aca="false">IFERROR('Debt Schedule'!H25/'Operating Model'!H8,0)</f>
-        <v>0.046746086843912</v>
-      </c>
-      <c r="H5" s="27" t="n">
+        <v>0.0454838197678832</v>
+      </c>
+      <c r="H5" s="26" t="n">
         <f aca="false">IFERROR('Debt Schedule'!I25/'Operating Model'!I8,0)</f>
-        <v>0.0504303901683732</v>
-      </c>
-      <c r="I5" s="27" t="n">
+        <v>0.048907308477008</v>
+      </c>
+      <c r="I5" s="26" t="n">
         <f aca="false">IFERROR('Debt Schedule'!J25/'Operating Model'!J8,0)</f>
-        <v>0.054281793146728</v>
+        <v>0.052472929754076</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="26" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
-      <c r="D6" s="27" t="n">
+      <c r="D6" s="26" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="26" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
-      <c r="F6" s="27" t="n">
+      <c r="F6" s="26" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
-      <c r="G6" s="27" t="n">
+      <c r="G6" s="26" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
-      <c r="H6" s="27" t="n">
+      <c r="H6" s="26" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
-      <c r="I6" s="27" t="n">
+      <c r="I6" s="26" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
@@ -6508,97 +6481,97 @@
       <c r="B7" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="26" t="n">
         <f aca="false">C6-C5</f>
-        <v>6.96852965854594</v>
-      </c>
-      <c r="D7" s="27" t="n">
+        <v>6.96893911898082</v>
+      </c>
+      <c r="D7" s="26" t="n">
         <f aca="false">D6-D5</f>
-        <v>6.96363519071279</v>
-      </c>
-      <c r="E7" s="27" t="n">
+        <v>6.96424138248687</v>
+      </c>
+      <c r="E7" s="26" t="n">
         <f aca="false">E6-E5</f>
-        <v>6.96021936326823</v>
-      </c>
-      <c r="F7" s="27" t="n">
+        <v>6.96102563861161</v>
+      </c>
+      <c r="F7" s="26" t="n">
         <f aca="false">F6-F5</f>
-        <v>6.95679472272945</v>
-      </c>
-      <c r="G7" s="27" t="n">
+        <v>6.95781878679193</v>
+      </c>
+      <c r="G7" s="26" t="n">
         <f aca="false">G6-G5</f>
-        <v>6.95325391315609</v>
-      </c>
-      <c r="H7" s="27" t="n">
+        <v>6.95451618023212</v>
+      </c>
+      <c r="H7" s="26" t="n">
         <f aca="false">H6-H5</f>
-        <v>6.94956960983163</v>
-      </c>
-      <c r="I7" s="27" t="n">
+        <v>6.95109269152299</v>
+      </c>
+      <c r="I7" s="26" t="n">
         <f aca="false">I6-I5</f>
-        <v>6.94571820685327</v>
+        <v>6.94752707024592</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="26" t="n">
         <f aca="false">IFERROR('Operating Model'!D8/'Debt Schedule'!D7,0)</f>
-        <v>2.00841974216587</v>
-      </c>
-      <c r="D8" s="27" t="n">
+        <v>1.98356306218857</v>
+      </c>
+      <c r="D8" s="26" t="n">
         <f aca="false">IFERROR('Operating Model'!E8/'Debt Schedule'!E7,0)</f>
-        <v>2.06647024084047</v>
-      </c>
-      <c r="E8" s="27" t="n">
+        <v>2.03512144994659</v>
+      </c>
+      <c r="E8" s="26" t="n">
         <f aca="false">IFERROR('Operating Model'!F8/'Debt Schedule'!F7,0)</f>
-        <v>2.13584558186835</v>
-      </c>
-      <c r="F8" s="27" t="n">
+        <v>2.09648506468249</v>
+      </c>
+      <c r="F8" s="26" t="n">
         <f aca="false">IFERROR('Operating Model'!G8/'Debt Schedule'!G7,0)</f>
-        <v>2.21561023559757</v>
-      </c>
-      <c r="G8" s="27" t="n">
+        <v>2.16639493906224</v>
+      </c>
+      <c r="G8" s="26" t="n">
         <f aca="false">IFERROR('Operating Model'!H8/'Debt Schedule'!H7,0)</f>
-        <v>2.30797252550207</v>
-      </c>
-      <c r="H8" s="27" t="n">
+        <v>2.24649783033677</v>
+      </c>
+      <c r="H8" s="26" t="n">
         <f aca="false">IFERROR('Operating Model'!I8/'Debt Schedule'!I7,0)</f>
-        <v>2.41606851580647</v>
-      </c>
-      <c r="I8" s="27" t="n">
+        <v>2.3391292679201</v>
+      </c>
+      <c r="I8" s="26" t="n">
         <f aca="false">IFERROR('Operating Model'!J8/'Debt Schedule'!J7,0)</f>
-        <v>2.54415009379848</v>
+        <v>2.44738277868644</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="26" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
-      <c r="D9" s="27" t="n">
+      <c r="D9" s="26" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="26" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
-      <c r="F9" s="27" t="n">
+      <c r="F9" s="26" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
-      <c r="G9" s="27" t="n">
+      <c r="G9" s="26" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
-      <c r="H9" s="27" t="n">
+      <c r="H9" s="26" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
-      <c r="I9" s="27" t="n">
+      <c r="I9" s="26" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
@@ -6607,33 +6580,33 @@
       <c r="B10" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C10" s="27" t="n">
+      <c r="C10" s="26" t="n">
         <f aca="false">C8-C9</f>
-        <v>0.258419742165872</v>
-      </c>
-      <c r="D10" s="27" t="n">
+        <v>0.233563062188571</v>
+      </c>
+      <c r="D10" s="26" t="n">
         <f aca="false">D8-D9</f>
-        <v>0.316470240840472</v>
-      </c>
-      <c r="E10" s="27" t="n">
+        <v>0.285121449946588</v>
+      </c>
+      <c r="E10" s="26" t="n">
         <f aca="false">E8-E9</f>
-        <v>0.385845581868348</v>
-      </c>
-      <c r="F10" s="27" t="n">
+        <v>0.34648506468249</v>
+      </c>
+      <c r="F10" s="26" t="n">
         <f aca="false">F8-F9</f>
-        <v>0.465610235597571</v>
-      </c>
-      <c r="G10" s="27" t="n">
+        <v>0.416394939062236</v>
+      </c>
+      <c r="G10" s="26" t="n">
         <f aca="false">G8-G9</f>
-        <v>0.557972525502074</v>
-      </c>
-      <c r="H10" s="27" t="n">
+        <v>0.496497830336767</v>
+      </c>
+      <c r="H10" s="26" t="n">
         <f aca="false">H8-H9</f>
-        <v>0.666068515806475</v>
-      </c>
-      <c r="I10" s="27" t="n">
+        <v>0.589129267920095</v>
+      </c>
+      <c r="I10" s="26" t="n">
         <f aca="false">I8-I9</f>
-        <v>0.79415009379848</v>
+        <v>0.697382778686439</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6675,31 +6648,31 @@
       </c>
       <c r="C12" s="19" t="n">
         <f aca="false">'Debt Schedule'!D13-C11</f>
-        <v>245.448217480469</v>
+        <v>242.254692109375</v>
       </c>
       <c r="D12" s="19" t="n">
         <f aca="false">'Debt Schedule'!E13-D11</f>
-        <v>283.819344984067</v>
+        <v>279.088151403601</v>
       </c>
       <c r="E12" s="19" t="n">
         <f aca="false">'Debt Schedule'!F13-E11</f>
-        <v>310.402936332321</v>
+        <v>304.111678709486</v>
       </c>
       <c r="F12" s="19" t="n">
         <f aca="false">'Debt Schedule'!G13-F11</f>
-        <v>336.743671725486</v>
+        <v>328.762075164477</v>
       </c>
       <c r="G12" s="19" t="n">
         <f aca="false">'Debt Schedule'!H13-G11</f>
-        <v>363.624838526098</v>
+        <v>353.806013193608</v>
       </c>
       <c r="H12" s="19" t="n">
         <f aca="false">'Debt Schedule'!I13-H11</f>
-        <v>391.204128818474</v>
+        <v>379.389113225683</v>
       </c>
       <c r="I12" s="19" t="n">
         <f aca="false">'Debt Schedule'!J13-I11</f>
-        <v>419.608020724502</v>
+        <v>405.625181471199</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/03_Private_Equity/instances/public_home_depot_2023.xlsx
+++ b/03_Private_Equity/instances/public_home_depot_2023.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Target / transaction:</t>
   </si>
   <si>
-    <t xml:space="preserve">[Name]</t>
+    <t xml:space="preserve">The Home Depot, Inc. -- FY2023 public-company operating case</t>
   </si>
   <si>
     <t xml:space="preserve">Sponsor / principal:</t>
@@ -1105,14 +1105,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFCE4D6"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -1218,7 +1218,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1258,11 +1258,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1270,11 +1270,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1282,7 +1282,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1290,7 +1290,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1298,7 +1298,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1433,34 +1433,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1606,7 +1606,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:F17"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36"/>
@@ -1635,7 +1635,7 @@
       <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       <c r="B9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1747,7 +1747,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:E9"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
@@ -1873,7 +1873,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:J15"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
@@ -2349,7 +2349,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:G9"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
@@ -2543,7 +2543,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:C13"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46"/>
@@ -2679,7 +2679,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:E11"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
@@ -2828,7 +2828,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:G29"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
@@ -3101,7 +3101,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:F63"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="48"/>
@@ -3858,7 +3858,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:I9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
@@ -4008,7 +4008,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:J8"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
@@ -4165,7 +4165,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:F32"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46"/>
@@ -4723,7 +4723,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:G10"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
@@ -4868,7 +4868,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:J19"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36"/>
@@ -5457,7 +5457,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:J28"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42"/>
@@ -6366,7 +6366,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:I13"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>

--- a/03_Private_Equity/instances/public_home_depot_2023.xlsx
+++ b/03_Private_Equity/instances/public_home_depot_2023.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="314">
   <si>
     <t xml:space="preserve">[TARGET] — LBO Underwriting Model</t>
   </si>
@@ -531,6 +531,12 @@
   </si>
   <si>
     <t xml:space="preserve">% incremental</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revolver commitment fee (undrawn balance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% p.a.</t>
   </si>
   <si>
     <t xml:space="preserve">Transaction Sources &amp; Uses</t>
@@ -1189,12 +1195,8 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1202,31 +1204,31 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1250,7 +1252,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1258,59 +1260,59 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1318,7 +1320,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1326,7 +1328,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1608,115 +1610,115 @@
   <dimension ref="B2:F17"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="12"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="3" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="3" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="3" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="3" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="3" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="6" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="3" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="9" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="3" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1749,108 +1751,108 @@
   <dimension ref="B2:E9"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="42"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>238</v>
-      </c>
-      <c r="D4" s="16" t="s">
+      <c r="B2" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+      <c r="D4" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="C5" s="22" t="n">
+      <c r="E4" s="15" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="C5" s="21" t="n">
         <f aca="false">Assumptions!E30</f>
         <v>0.1</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C6" s="22" t="n">
+      <c r="E5" s="14" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
+        <v>245</v>
+      </c>
+      <c r="C6" s="21" t="n">
         <f aca="false">1-C5</f>
         <v>0.9</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="C7" s="19" t="n">
+      <c r="E6" s="14" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
+        <v>247</v>
+      </c>
+      <c r="C7" s="18" t="n">
         <f aca="false">'Sources &amp; Uses'!F8</f>
         <v>109904.2779</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="C8" s="19" t="n">
+      <c r="E7" s="14" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="C8" s="18" t="n">
         <f aca="false">C7*(1+Assumptions!E31)^Assumptions!E29</f>
         <v>161485.4412789</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="C9" s="22" t="n">
+      <c r="E8" s="14" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="s">
+        <v>251</v>
+      </c>
+      <c r="C9" s="21" t="n">
         <f aca="false">Assumptions!E32</f>
         <v>0.2</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>250</v>
+      <c r="E9" s="14" t="s">
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -1875,458 +1877,458 @@
   <dimension ref="B2:J15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="3" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="3" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="E4" s="16" t="s">
+      <c r="B2" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="E4" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="F4" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="G4" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="J4" s="16" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="C5" s="19" t="n">
+      <c r="H4" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
+        <v>255</v>
+      </c>
+      <c r="C5" s="18" t="n">
         <f aca="false">'Operating Model'!D8</f>
         <v>23398.05094</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="18" t="n">
         <f aca="false">'Operating Model'!E8</f>
         <v>23414.3407223</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="18" t="n">
         <f aca="false">'Operating Model'!F8</f>
         <v>23408.594871816</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="18" t="n">
         <f aca="false">'Operating Model'!G8</f>
         <v>23382.120865711</v>
       </c>
-      <c r="G5" s="19" t="n">
+      <c r="G5" s="18" t="n">
         <f aca="false">'Operating Model'!H8</f>
         <v>23336.1675645876</v>
       </c>
-      <c r="H5" s="19" t="n">
+      <c r="H5" s="18" t="n">
         <f aca="false">'Operating Model'!I8</f>
         <v>23271.9275527525</v>
       </c>
-      <c r="I5" s="19" t="n">
+      <c r="I5" s="18" t="n">
         <f aca="false">'Operating Model'!J8</f>
         <v>23190.5393908194</v>
       </c>
-      <c r="J5" s="19" t="n">
+      <c r="J5" s="18" t="n">
         <f aca="false">INDEX(C5:I5,1,Assumptions!E29)</f>
         <v>23336.1675645876</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C6" s="26" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
+        <v>256</v>
+      </c>
+      <c r="C6" s="25" t="n">
         <f aca="false">Assumptions!$E$28</f>
         <v>10</v>
       </c>
-      <c r="D6" s="26" t="n">
+      <c r="D6" s="25" t="n">
         <f aca="false">Assumptions!$E$28</f>
         <v>10</v>
       </c>
-      <c r="E6" s="26" t="n">
+      <c r="E6" s="25" t="n">
         <f aca="false">Assumptions!$E$28</f>
         <v>10</v>
       </c>
-      <c r="F6" s="26" t="n">
+      <c r="F6" s="25" t="n">
         <f aca="false">Assumptions!$E$28</f>
         <v>10</v>
       </c>
-      <c r="G6" s="26" t="n">
+      <c r="G6" s="25" t="n">
         <f aca="false">Assumptions!$E$28</f>
         <v>10</v>
       </c>
-      <c r="H6" s="26" t="n">
+      <c r="H6" s="25" t="n">
         <f aca="false">Assumptions!$E$28</f>
         <v>10</v>
       </c>
-      <c r="I6" s="26" t="n">
+      <c r="I6" s="25" t="n">
         <f aca="false">Assumptions!$E$28</f>
         <v>10</v>
       </c>
-      <c r="J6" s="26" t="n">
+      <c r="J6" s="25" t="n">
         <f aca="false">INDEX(C6:I6,1,Assumptions!E29)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C7" s="19" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
+        <v>257</v>
+      </c>
+      <c r="C7" s="18" t="n">
         <f aca="false">C5*C6</f>
         <v>233980.5094</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="18" t="n">
         <f aca="false">D5*D6</f>
         <v>234143.407223</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="18" t="n">
         <f aca="false">E5*E6</f>
         <v>234085.94871816</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="18" t="n">
         <f aca="false">F5*F6</f>
         <v>233821.20865711</v>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G7" s="18" t="n">
         <f aca="false">G5*G6</f>
         <v>233361.675645876</v>
       </c>
-      <c r="H7" s="19" t="n">
+      <c r="H7" s="18" t="n">
         <f aca="false">H5*H6</f>
         <v>232719.275527525</v>
       </c>
-      <c r="I7" s="19" t="n">
+      <c r="I7" s="18" t="n">
         <f aca="false">I5*I6</f>
         <v>231905.393908194</v>
       </c>
-      <c r="J7" s="19" t="n">
+      <c r="J7" s="18" t="n">
         <f aca="false">INDEX(C7:I7,1,Assumptions!E29)</f>
         <v>233361.675645876</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="C8" s="19" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
+        <v>229</v>
+      </c>
+      <c r="C8" s="18" t="n">
         <f aca="false">'Debt Schedule'!D28</f>
-        <v>124691.68021125</v>
-      </c>
-      <c r="D8" s="19" t="n">
+        <v>124691.89114875</v>
+      </c>
+      <c r="D8" s="18" t="n">
         <f aca="false">'Debt Schedule'!E28</f>
-        <v>120595.047125562</v>
-      </c>
-      <c r="E8" s="19" t="n">
+        <v>120595.483535474</v>
+      </c>
+      <c r="E8" s="18" t="n">
         <f aca="false">'Debt Schedule'!F28</f>
-        <v>116141.578836387</v>
-      </c>
-      <c r="F8" s="19" t="n">
+        <v>116142.257215327</v>
+      </c>
+      <c r="F8" s="18" t="n">
         <f aca="false">'Debt Schedule'!G28</f>
-        <v>111323.384621118</v>
-      </c>
-      <c r="G8" s="19" t="n">
+        <v>111324.322776467</v>
+      </c>
+      <c r="G8" s="18" t="n">
         <f aca="false">'Debt Schedule'!H28</f>
-        <v>106131.715854733</v>
-      </c>
-      <c r="H8" s="19" t="n">
+        <v>106132.932958885</v>
+      </c>
+      <c r="H8" s="18" t="n">
         <f aca="false">'Debt Schedule'!I28</f>
-        <v>100556.162874162</v>
-      </c>
-      <c r="I8" s="19" t="n">
+        <v>100557.679567245</v>
+      </c>
+      <c r="I8" s="18" t="n">
         <f aca="false">'Debt Schedule'!J28</f>
-        <v>94584.5269144406</v>
-      </c>
-      <c r="J8" s="19" t="n">
+        <v>94586.3654175843</v>
+      </c>
+      <c r="J8" s="18" t="n">
         <f aca="false">INDEX(C8:I8,1,Assumptions!E29)</f>
-        <v>106131.715854733</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C9" s="19" t="n">
+        <v>106132.932958885</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="C9" s="18" t="n">
         <f aca="false">MAX(0,C7-C8)</f>
-        <v>109288.82918875</v>
-      </c>
-      <c r="D9" s="19" t="n">
+        <v>109288.61825125</v>
+      </c>
+      <c r="D9" s="18" t="n">
         <f aca="false">MAX(0,D7-D8)</f>
-        <v>113548.360097438</v>
-      </c>
-      <c r="E9" s="19" t="n">
+        <v>113547.923687526</v>
+      </c>
+      <c r="E9" s="18" t="n">
         <f aca="false">MAX(0,E7-E8)</f>
-        <v>117944.369881773</v>
-      </c>
-      <c r="F9" s="19" t="n">
+        <v>117943.691502833</v>
+      </c>
+      <c r="F9" s="18" t="n">
         <f aca="false">MAX(0,F7-F8)</f>
-        <v>122497.824035991</v>
-      </c>
-      <c r="G9" s="19" t="n">
+        <v>122496.885880643</v>
+      </c>
+      <c r="G9" s="18" t="n">
         <f aca="false">MAX(0,G7-G8)</f>
-        <v>127229.959791143</v>
-      </c>
-      <c r="H9" s="19" t="n">
+        <v>127228.742686991</v>
+      </c>
+      <c r="H9" s="18" t="n">
         <f aca="false">MAX(0,H7-H8)</f>
-        <v>132163.112653363</v>
-      </c>
-      <c r="I9" s="19" t="n">
+        <v>132161.59596028</v>
+      </c>
+      <c r="I9" s="18" t="n">
         <f aca="false">MAX(0,I7-I8)</f>
-        <v>137320.866993753</v>
-      </c>
-      <c r="J9" s="19" t="n">
+        <v>137319.02849061</v>
+      </c>
+      <c r="J9" s="18" t="n">
         <f aca="false">INDEX(C9:I9,1,Assumptions!E29)</f>
-        <v>127229.959791143</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
+        <v>127228.742686991</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="0" t="s">
         <v>161</v>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="18" t="n">
         <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^1</f>
         <v>118696.620132</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="18" t="n">
         <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^2</f>
         <v>128192.34974256</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="18" t="n">
         <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^3</f>
         <v>138447.737721965</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="18" t="n">
         <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^4</f>
         <v>149523.556739722</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="18" t="n">
         <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^5</f>
         <v>161485.4412789</v>
       </c>
-      <c r="H10" s="19" t="n">
+      <c r="H10" s="18" t="n">
         <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^6</f>
         <v>174404.276581212</v>
       </c>
-      <c r="I10" s="19" t="n">
+      <c r="I10" s="18" t="n">
         <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^7</f>
         <v>188356.618707709</v>
       </c>
-      <c r="J10" s="19" t="n">
+      <c r="J10" s="18" t="n">
         <f aca="false">INDEX(C10:I10,1,Assumptions!E29)</f>
         <v>161485.4412789</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C11" s="19" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="0" t="s">
+        <v>259</v>
+      </c>
+      <c r="C11" s="18" t="n">
         <f aca="false">MAX(0,C9-C10)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="18" t="n">
         <f aca="false">MAX(0,D9-D10)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="18" t="n">
         <f aca="false">MAX(0,E9-E10)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="18" t="n">
         <f aca="false">MAX(0,F9-F10)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="G11" s="18" t="n">
         <f aca="false">MAX(0,G9-G10)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="19" t="n">
+      <c r="H11" s="18" t="n">
         <f aca="false">MAX(0,H9-H10)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="19" t="n">
+      <c r="I11" s="18" t="n">
         <f aca="false">MAX(0,I9-I10)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="19" t="n">
+      <c r="J11" s="18" t="n">
         <f aca="false">INDEX(C11:I11,1,Assumptions!E29)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C12" s="19" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="0" t="s">
+        <v>260</v>
+      </c>
+      <c r="C12" s="18" t="n">
         <f aca="false">MIN(C9,C9*Assumptions!$E$30+C11*Assumptions!$E$32)</f>
-        <v>10928.882918875</v>
-      </c>
-      <c r="D12" s="19" t="n">
+        <v>10928.861825125</v>
+      </c>
+      <c r="D12" s="18" t="n">
         <f aca="false">MIN(D9,D9*Assumptions!$E$30+D11*Assumptions!$E$32)</f>
-        <v>11354.8360097438</v>
-      </c>
-      <c r="E12" s="19" t="n">
+        <v>11354.7923687526</v>
+      </c>
+      <c r="E12" s="18" t="n">
         <f aca="false">MIN(E9,E9*Assumptions!$E$30+E11*Assumptions!$E$32)</f>
-        <v>11794.4369881773</v>
-      </c>
-      <c r="F12" s="19" t="n">
+        <v>11794.3691502833</v>
+      </c>
+      <c r="F12" s="18" t="n">
         <f aca="false">MIN(F9,F9*Assumptions!$E$30+F11*Assumptions!$E$32)</f>
-        <v>12249.7824035991</v>
-      </c>
-      <c r="G12" s="19" t="n">
+        <v>12249.6885880643</v>
+      </c>
+      <c r="G12" s="18" t="n">
         <f aca="false">MIN(G9,G9*Assumptions!$E$30+G11*Assumptions!$E$32)</f>
-        <v>12722.9959791143</v>
-      </c>
-      <c r="H12" s="19" t="n">
+        <v>12722.8742686991</v>
+      </c>
+      <c r="H12" s="18" t="n">
         <f aca="false">MIN(H9,H9*Assumptions!$E$30+H11*Assumptions!$E$32)</f>
-        <v>13216.3112653363</v>
-      </c>
-      <c r="I12" s="19" t="n">
+        <v>13216.159596028</v>
+      </c>
+      <c r="I12" s="18" t="n">
         <f aca="false">MIN(I9,I9*Assumptions!$E$30+I11*Assumptions!$E$32)</f>
-        <v>13732.0866993753</v>
-      </c>
-      <c r="J12" s="19" t="n">
+        <v>13731.9028490609</v>
+      </c>
+      <c r="J12" s="18" t="n">
         <f aca="false">INDEX(C12:I12,1,Assumptions!E29)</f>
-        <v>12722.9959791143</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C13" s="19" t="n">
+        <v>12722.8742686991</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="C13" s="18" t="n">
         <f aca="false">MAX(0,C9-C12)</f>
-        <v>98359.946269875</v>
-      </c>
-      <c r="D13" s="19" t="n">
+        <v>98359.756426125</v>
+      </c>
+      <c r="D13" s="18" t="n">
         <f aca="false">MAX(0,D9-D12)</f>
-        <v>102193.524087694</v>
-      </c>
-      <c r="E13" s="19" t="n">
+        <v>102193.131318773</v>
+      </c>
+      <c r="E13" s="18" t="n">
         <f aca="false">MAX(0,E9-E12)</f>
-        <v>106149.932893595</v>
-      </c>
-      <c r="F13" s="19" t="n">
+        <v>106149.32235255</v>
+      </c>
+      <c r="F13" s="18" t="n">
         <f aca="false">MAX(0,F9-F12)</f>
-        <v>110248.041632392</v>
-      </c>
-      <c r="G13" s="19" t="n">
+        <v>110247.197292578</v>
+      </c>
+      <c r="G13" s="18" t="n">
         <f aca="false">MAX(0,G9-G12)</f>
-        <v>114506.963812029</v>
-      </c>
-      <c r="H13" s="19" t="n">
+        <v>114505.868418292</v>
+      </c>
+      <c r="H13" s="18" t="n">
         <f aca="false">MAX(0,H9-H12)</f>
-        <v>118946.801388027</v>
-      </c>
-      <c r="I13" s="19" t="n">
+        <v>118945.436364252</v>
+      </c>
+      <c r="I13" s="18" t="n">
         <f aca="false">MAX(0,I9-I12)</f>
-        <v>123588.780294378</v>
-      </c>
-      <c r="J13" s="19" t="n">
+        <v>123587.125641549</v>
+      </c>
+      <c r="J13" s="18" t="n">
         <f aca="false">INDEX(C13:I13,1,Assumptions!E29)</f>
-        <v>114506.963812029</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C14" s="26" t="n">
+        <v>114505.868418292</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0" t="s">
+        <v>262</v>
+      </c>
+      <c r="C14" s="25" t="n">
         <f aca="false">IFERROR(C13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>0.894960124840372</v>
-      </c>
-      <c r="D14" s="26" t="n">
+        <v>0.894958397484953</v>
+      </c>
+      <c r="D14" s="25" t="n">
         <f aca="false">IFERROR(D13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>0.929841185806055</v>
-      </c>
-      <c r="E14" s="26" t="n">
+        <v>0.929837612069633</v>
+      </c>
+      <c r="E14" s="25" t="n">
         <f aca="false">IFERROR(E13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>0.965839864670048</v>
-      </c>
-      <c r="F14" s="26" t="n">
+        <v>0.965834309462759</v>
+      </c>
+      <c r="F14" s="25" t="n">
         <f aca="false">IFERROR(F13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>1.00312784669497</v>
-      </c>
-      <c r="G14" s="26" t="n">
+        <v>1.00312016419316</v>
+      </c>
+      <c r="G14" s="25" t="n">
         <f aca="false">IFERROR(G13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>1.04187904238102</v>
-      </c>
-      <c r="H14" s="26" t="n">
+        <v>1.04186907558302</v>
+      </c>
+      <c r="H14" s="25" t="n">
         <f aca="false">IFERROR(H13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>1.0822763559418</v>
-      </c>
-      <c r="I14" s="26" t="n">
+        <v>1.08226393582676</v>
+      </c>
+      <c r="I14" s="25" t="n">
         <f aca="false">IFERROR(I13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>1.12451291847647</v>
-      </c>
-      <c r="J14" s="26" t="n">
+        <v>1.1244978630768</v>
+      </c>
+      <c r="J14" s="25" t="n">
         <f aca="false">INDEX(C14:I14,1,Assumptions!E29)</f>
-        <v>1.04187904238102</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C15" s="24" t="n">
+        <v>1.04186907558302</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="0" t="s">
+        <v>263</v>
+      </c>
+      <c r="C15" s="23" t="n">
         <f aca="false">IFERROR((C13/'Sources &amp; Uses'!$F$8)^(1/1)-1,0)</f>
-        <v>-0.105039875159628</v>
-      </c>
-      <c r="D15" s="24" t="n">
+        <v>-0.105041602515047</v>
+      </c>
+      <c r="D15" s="23" t="n">
         <f aca="false">IFERROR((D13/'Sources &amp; Uses'!$F$8)^(1/2)-1,0)</f>
-        <v>-0.0357172687400985</v>
-      </c>
-      <c r="E15" s="24" t="n">
+        <v>-0.0357191217961267</v>
+      </c>
+      <c r="E15" s="23" t="n">
         <f aca="false">IFERROR((E13/'Sources &amp; Uses'!$F$8)^(1/3)-1,0)</f>
-        <v>-0.0115188870758636</v>
-      </c>
-      <c r="F15" s="24" t="n">
+        <v>-0.0115207822237074</v>
+      </c>
+      <c r="F15" s="23" t="n">
         <f aca="false">IFERROR((F13/'Sources &amp; Uses'!$F$8)^(1/4)-1,0)</f>
-        <v>0.000781046147557918</v>
-      </c>
-      <c r="G15" s="24" t="n">
+        <v>0.000779130009872731</v>
+      </c>
+      <c r="G15" s="23" t="n">
         <f aca="false">IFERROR((G13/'Sources &amp; Uses'!$F$8)^(1/5)-1,0)</f>
-        <v>0.00823892555745531</v>
-      </c>
-      <c r="H15" s="24" t="n">
+        <v>0.00823699655192778</v>
+      </c>
+      <c r="H15" s="23" t="n">
         <f aca="false">IFERROR((H13/'Sources &amp; Uses'!$F$8)^(1/6)-1,0)</f>
-        <v>0.013264969325727</v>
-      </c>
-      <c r="I15" s="24" t="n">
+        <v>0.0132630312921269</v>
+      </c>
+      <c r="I15" s="23" t="n">
         <f aca="false">IFERROR((I13/'Sources &amp; Uses'!$F$8)^(1/7)-1,0)</f>
-        <v>0.0169055920708845</v>
-      </c>
-      <c r="J15" s="24" t="n">
+        <v>0.0169036471007922</v>
+      </c>
+      <c r="J15" s="23" t="n">
         <f aca="false">INDEX(C15:I15,1,Assumptions!E29)</f>
-        <v>0.00823892555745531</v>
+        <v>0.00823699655192778</v>
       </c>
     </row>
   </sheetData>
@@ -2351,164 +2353,164 @@
   <dimension ref="B2:G9"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="16" t="s">
-        <v>263</v>
-      </c>
-      <c r="C4" s="31" t="n">
+      <c r="B2" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="C4" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="D4" s="31" t="n">
+      <c r="D4" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="31" t="n">
+      <c r="E4" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="F4" s="31" t="n">
+      <c r="F4" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="G4" s="31" t="n">
+      <c r="G4" s="30" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="26" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="C5" s="22" t="n">
+      <c r="C5" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0581698451093956</v>
-      </c>
-      <c r="D5" s="22" t="n">
+        <v>-0.058173241584372</v>
+      </c>
+      <c r="D5" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0142785049827239</v>
-      </c>
-      <c r="E5" s="22" t="n">
+        <v>0.0142759798225731</v>
+      </c>
+      <c r="E5" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0705019893213061</v>
-      </c>
-      <c r="F5" s="22" t="n">
+        <v>0.0704999543073663</v>
+      </c>
+      <c r="F5" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.116918290461881</v>
-      </c>
-      <c r="G5" s="22" t="n">
+        <v>0.116916573220379</v>
+      </c>
+      <c r="G5" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.156697512238684</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="26" t="n">
+        <v>0.156696019315141</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.115598250497523</v>
-      </c>
-      <c r="D6" s="22" t="n">
+        <v>-0.115601439871313</v>
+      </c>
+      <c r="D6" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0475674625286657</v>
-      </c>
-      <c r="E6" s="22" t="n">
+        <v>-0.0475698337163406</v>
+      </c>
+      <c r="E6" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.00522777624550885</v>
-      </c>
-      <c r="F6" s="22" t="n">
+        <v>0.00522586531721747</v>
+      </c>
+      <c r="F6" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0488138280628094</v>
-      </c>
-      <c r="G6" s="22" t="n">
+        <v>0.0488122155306767</v>
+      </c>
+      <c r="G6" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0861674986270506</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="26" t="n">
+        <v>0.086166096735014</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.156867181583465</v>
-      </c>
-      <c r="D7" s="22" t="n">
+        <v>-0.156870222131174</v>
+      </c>
+      <c r="D7" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0920109213696565</v>
-      </c>
-      <c r="E7" s="22" t="n">
+        <v>-0.0920131819103536</v>
+      </c>
+      <c r="E7" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0416792723292913</v>
-      </c>
-      <c r="F7" s="22" t="n">
+        <v>-0.0416810940877364</v>
+      </c>
+      <c r="F7" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.000127080994252737</v>
-      </c>
-      <c r="G7" s="22" t="n">
+        <v>-0.000128618280630266</v>
+      </c>
+      <c r="G7" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0354835513442162</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="26" t="n">
+        <v>0.0354822148688141</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.188745283917349</v>
-      </c>
-      <c r="D8" s="22" t="n">
+        <v>-0.188748209504652</v>
+      </c>
+      <c r="D8" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.126341181246135</v>
-      </c>
-      <c r="E8" s="22" t="n">
+        <v>-0.126343356317798</v>
+      </c>
+      <c r="E8" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0779125271120233</v>
-      </c>
-      <c r="F8" s="22" t="n">
+        <v>-0.0779142799914012</v>
+      </c>
+      <c r="F8" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0379313871921857</v>
-      </c>
-      <c r="G8" s="22" t="n">
+        <v>-0.0379328663551319</v>
+      </c>
+      <c r="G8" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.00366716120520005</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="26" t="n">
+        <v>-0.00366844714965531</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C9" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.214531234724911</v>
-      </c>
-      <c r="D9" s="22" t="n">
+        <v>-0.214534067321629</v>
+      </c>
+      <c r="D9" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.154110663353755</v>
-      </c>
-      <c r="E9" s="22" t="n">
+        <v>-0.154112769290176</v>
+      </c>
+      <c r="E9" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.107221327103931</v>
-      </c>
-      <c r="F9" s="22" t="n">
+        <v>-0.107223024267563</v>
+      </c>
+      <c r="F9" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0685109985418146</v>
-      </c>
-      <c r="G9" s="22" t="n">
+        <v>-0.068512430689166</v>
+      </c>
+      <c r="G9" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0353358702552724</v>
+        <v>-0.0353371153256351</v>
       </c>
     </row>
   </sheetData>
@@ -2545,102 +2547,102 @@
   <dimension ref="B2:C13"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="16" t="s">
-        <v>265</v>
-      </c>
-      <c r="C4" s="16" t="s">
+      <c r="B2" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="C5" s="1" t="str">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="C5" s="0" t="str">
         <f aca="false">IF(ABS('Sources &amp; Uses'!F10)&lt;0.000001,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="C6" s="1" t="str">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="C6" s="0" t="str">
         <f aca="false">IF('Sources &amp; Uses'!F8&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="C7" s="1" t="str">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="C7" s="0" t="str">
         <f aca="false">IF(MIN('Debt Schedule'!D15:J25)&gt;=0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C8" s="1" t="str">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="C8" s="0" t="str">
         <f aca="false">IF(MIN('Debt Schedule'!D13:J13)&gt;=Assumptions!E16,"PASS","REVIEW")</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="C9" s="1" t="str">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="s">
+        <v>272</v>
+      </c>
+      <c r="C9" s="0" t="str">
         <f aca="false">IF(COUNTIF(Covenants!C13:I13,"BREACH")=0,"PASS","REVIEW")</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C10" s="1" t="str">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="C10" s="0" t="str">
         <f aca="false">IF(MIN('Returns Waterfall'!C9:I9)&gt;=0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="C11" s="1" t="str">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="0" t="s">
+        <v>274</v>
+      </c>
+      <c r="C11" s="0" t="str">
         <f aca="false">IF(MAX(ABS('Returns Waterfall'!C9:I9-'Returns Waterfall'!C12:I12-'Returns Waterfall'!C13:I13))&lt;0.000001,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="C12" s="1" t="str">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="0" t="s">
+        <v>275</v>
+      </c>
+      <c r="C12" s="0" t="str">
         <f aca="false">IF(AND(Assumptions!E29&gt;=1,Assumptions!E29&lt;=7),"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="C13" s="1" t="str">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="0" t="s">
+        <v>276</v>
+      </c>
+      <c r="C13" s="0" t="str">
         <f aca="false">IF(COUNTIF(C5:C12,"FAIL")=0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
@@ -2681,131 +2683,131 @@
   <dimension ref="B2:E11"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="48"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="16" t="s">
-        <v>276</v>
-      </c>
-      <c r="C4" s="16" t="s">
+      <c r="B2" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="E4" s="16" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="32" t="s">
-        <v>279</v>
-      </c>
-      <c r="C5" s="32" t="s">
+      <c r="E4" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="D5" s="32" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="31" t="s">
         <v>281</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="C5" s="31" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="32" t="s">
+      <c r="D5" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="E5" s="31" t="s">
         <v>284</v>
       </c>
-      <c r="D6" s="32" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>286</v>
+      </c>
+      <c r="D6" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="32" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="32" t="s">
-        <v>286</v>
-      </c>
-      <c r="C7" s="32" t="s">
+      <c r="E6" s="31" t="s">
         <v>287</v>
       </c>
-      <c r="D7" s="32" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>289</v>
+      </c>
+      <c r="D7" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="32" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="32" t="s">
-        <v>289</v>
-      </c>
-      <c r="C8" s="32" t="s">
+      <c r="E7" s="31" t="s">
         <v>290</v>
       </c>
-      <c r="D8" s="32" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="31" t="s">
+        <v>291</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>292</v>
+      </c>
+      <c r="D8" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="32" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="32" t="s">
-        <v>292</v>
-      </c>
-      <c r="C9" s="32" t="s">
+      <c r="E8" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="D9" s="32" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>295</v>
+      </c>
+      <c r="D9" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="32" t="s">
-        <v>294</v>
+      <c r="E9" s="31" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="33" t="s">
-        <v>295</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>296</v>
-      </c>
-      <c r="D10" s="33" t="s">
+      <c r="B10" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>298</v>
+      </c>
+      <c r="D10" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="33" t="s">
-        <v>297</v>
+      <c r="E10" s="32" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="33" t="s">
-        <v>298</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>299</v>
-      </c>
-      <c r="D11" s="33" t="s">
+      <c r="B11" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>301</v>
+      </c>
+      <c r="D11" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="33" t="s">
-        <v>300</v>
+      <c r="E11" s="32" t="s">
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -2830,256 +2832,256 @@
   <dimension ref="B2:G29"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>306</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="33" t="s">
+        <v>309</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="D5" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>302</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>304</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>305</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="34" t="s">
-        <v>307</v>
-      </c>
-      <c r="C5" s="34" t="s">
-        <v>308</v>
-      </c>
-      <c r="D5" s="34" t="s">
-        <v>299</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>309</v>
-      </c>
-      <c r="F5" s="34" t="s">
-        <v>310</v>
-      </c>
-      <c r="G5" s="34" t="s">
+      <c r="E5" s="33" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="34"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="34"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="34"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="34"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="34"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="34"/>
-      <c r="C23" s="34"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="34"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="34"/>
-      <c r="C24" s="34"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="34"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="34"/>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="34"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="34"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="34"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="34"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="34"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="34"/>
+      <c r="F5" s="33" t="s">
+        <v>312</v>
+      </c>
+      <c r="G5" s="33" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="33"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="33"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="33"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="33"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="33"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="33"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="33"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="33"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="33"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="33"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="33"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="33"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="33"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="33"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3111,692 +3113,630 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="13" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="15" t="s">
+      <c r="F14" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="15" t="s">
+      <c r="F16" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="0" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="15" t="s">
+      <c r="F17" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="0" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="15" t="s">
+      <c r="F18" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="13" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="15" t="s">
+      <c r="F22" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="15" t="s">
+      <c r="F23" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="15" t="s">
+      <c r="F24" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="15" t="s">
+      <c r="F25" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="0" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="15" t="s">
+      <c r="F26" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="E29" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" s="13" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="0" t="s">
         <v>57</v>
       </c>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="15" t="s">
+      <c r="F30" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="15" t="s">
+      <c r="F31" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="15" t="s">
+      <c r="F32" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="15" t="s">
+      <c r="F33" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="15" t="s">
+      <c r="F34" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="D37" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E37" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F37" s="14" t="s">
+      <c r="F37" s="13" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="15" t="s">
+      <c r="F38" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="15" t="s">
+      <c r="F39" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="15" t="s">
+      <c r="F40" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="0" t="s">
         <v>66</v>
       </c>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="15" t="s">
+      <c r="F41" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="15" t="s">
+      <c r="F42" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="13" t="s">
+      <c r="B44" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="14" t="s">
+      <c r="B45" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C45" s="14" t="s">
+      <c r="C45" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D45" s="14" t="s">
+      <c r="D45" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="E45" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F45" s="14" t="s">
+      <c r="F45" s="13" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="0" t="s">
         <v>69</v>
       </c>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="15" t="s">
+      <c r="F46" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="15" t="s">
+      <c r="F47" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="15" t="s">
+      <c r="F48" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="15" t="s">
+      <c r="F49" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="0" t="s">
         <v>73</v>
       </c>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="15" t="s">
+      <c r="F50" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="13" t="s">
+      <c r="B52" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="C52" s="13"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="14" t="s">
+      <c r="B53" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C53" s="14" t="s">
+      <c r="C53" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D53" s="14" t="s">
+      <c r="D53" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E53" s="14" t="s">
+      <c r="E53" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F53" s="14" t="s">
+      <c r="F53" s="13" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="0" t="s">
         <v>75</v>
       </c>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="15" t="s">
+      <c r="F54" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="0" t="s">
         <v>76</v>
       </c>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="15" t="s">
+      <c r="F55" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="0" t="s">
         <v>77</v>
       </c>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="15" t="s">
+      <c r="F56" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="0" t="s">
         <v>78</v>
       </c>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="15" t="s">
+      <c r="F57" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="0" t="s">
         <v>79</v>
       </c>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="15" t="s">
+      <c r="F58" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="13" t="s">
+      <c r="B60" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="C60" s="13"/>
-      <c r="D60" s="13"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="14" t="s">
+      <c r="B61" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="C61" s="14" t="s">
+      <c r="C61" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D61" s="14" t="s">
+      <c r="D61" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="E61" s="14" t="s">
+      <c r="E61" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="F61" s="14" t="s">
+      <c r="F61" s="13" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="0" t="s">
         <v>86</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="0" t="s">
         <v>87</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D62" s="0" t="s">
         <v>88</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E62" s="0" t="s">
         <v>89</v>
       </c>
-      <c r="F62" s="1"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="0" t="s">
         <v>90</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="0" t="s">
         <v>91</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D63" s="0" t="s">
         <v>92</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E63" s="0" t="s">
         <v>89</v>
       </c>
-      <c r="F63" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -3857,7 +3797,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:I9"/>
+  <dimension ref="B2:I54"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
@@ -3871,112 +3811,217 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="13" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="0" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="0" t="s">
         <v>73</v>
       </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H10" s="14"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H11" s="14"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H12" s="14"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H13" s="14"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H14" s="14"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H15" s="14"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H16" s="14"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H17" s="14"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H18" s="14"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H19" s="14"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H20" s="14"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H21" s="14"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H22" s="14"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H23" s="14"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H24" s="14"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H25" s="14"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H26" s="14"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H27" s="14"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H28" s="14"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H29" s="14"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H30" s="14"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H31" s="14"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H32" s="14"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H33" s="14"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H34" s="14"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H35" s="14"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H36" s="14"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H37" s="14"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H38" s="14"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H39" s="14"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H40" s="14"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H41" s="14"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H42" s="14"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H43" s="14"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H44" s="14"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H45" s="14"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H46" s="14"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H47" s="14"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H48" s="14"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H49" s="14"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H50" s="14"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H51" s="14"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H52" s="14"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H53" s="14"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H54" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4007,7 +4052,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:J8"/>
+  <dimension ref="B2:J40"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
@@ -4022,122 +4067,198 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="13" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="0" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="0" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="0" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="14" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="0" t="s">
         <v>113</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="0" t="s">
         <v>110</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="0" t="s">
         <v>114</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="14" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="0" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="0" t="s">
         <v>116</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="0" t="s">
         <v>117</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="15" t="s">
+      <c r="J7" s="14" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="0" t="s">
         <v>118</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="0" t="s">
         <v>119</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="0" t="s">
         <v>120</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="15" t="s">
+      <c r="J8" s="14" t="s">
         <v>112</v>
       </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J9" s="14"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J10" s="14"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J11" s="14"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J13" s="14"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J15" s="14"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J17" s="14"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J18" s="14"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J20" s="14"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J21" s="14"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J23" s="14"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J24" s="14"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J27" s="14"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J28" s="14"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J29" s="14"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J30" s="14"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J31" s="14"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J32" s="14"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J33" s="14"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J34" s="14"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J35" s="14"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J36" s="14"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J37" s="14"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J38" s="14"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J39" s="14"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J40" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4164,543 +4285,561 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:F32"/>
+  <dimension ref="B2:F33"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="32"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="16" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="15" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
         <v>126</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="16" t="n">
         <v>152669</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="17" t="n">
         <v>600</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="18" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D5,C5)</f>
         <v>152669</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="14" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
         <v>128</v>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="19" t="n">
         <v>0.153</v>
       </c>
-      <c r="D6" s="21" t="n">
+      <c r="D6" s="20" t="n">
         <v>0.17</v>
       </c>
-      <c r="E6" s="22" t="n">
+      <c r="E6" s="21" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D6,C6)</f>
         <v>0.153</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="14" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
         <v>130</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="19" t="n">
         <v>-0.03</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="20" t="n">
         <v>-0.02</v>
       </c>
-      <c r="E7" s="22" t="n">
+      <c r="E7" s="21" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D7,C7)</f>
         <v>-0.03</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="14" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="23" t="n">
+      <c r="C8" s="22" t="n">
         <v>0.005</v>
       </c>
-      <c r="D8" s="23" t="n">
+      <c r="D8" s="22" t="n">
         <v>-0.003</v>
       </c>
-      <c r="E8" s="24" t="n">
+      <c r="E8" s="23" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D8,C8)</f>
         <v>0.005</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="14" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="s">
         <v>133</v>
       </c>
-      <c r="C9" s="21" t="n">
+      <c r="C9" s="20" t="n">
         <v>0.025</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="20" t="n">
         <v>0.025</v>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="E9" s="21" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D9,C9)</f>
         <v>0.025</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="14" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="0" t="s">
         <v>134</v>
       </c>
-      <c r="C10" s="21" t="n">
+      <c r="C10" s="20" t="n">
         <v>0.035</v>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="20" t="n">
         <v>0.045</v>
       </c>
-      <c r="E10" s="22" t="n">
+      <c r="E10" s="21" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D10,C10)</f>
         <v>0.035</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="14" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="0" t="s">
         <v>135</v>
       </c>
-      <c r="C11" s="21" t="n">
+      <c r="C11" s="20" t="n">
         <v>0.08</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="20" t="n">
         <v>0.1</v>
       </c>
-      <c r="E11" s="22" t="n">
+      <c r="E11" s="21" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D11,C11)</f>
         <v>0.08</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="14" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="0" t="s">
         <v>136</v>
       </c>
-      <c r="C12" s="21" t="n">
+      <c r="C12" s="20" t="n">
         <v>0.25</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="20" t="n">
         <v>0.2</v>
       </c>
-      <c r="E12" s="22" t="n">
+      <c r="E12" s="21" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D12,C12)</f>
         <v>0.25</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="14" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="1" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="0" t="s">
         <v>137</v>
       </c>
-      <c r="C13" s="25" t="n">
+      <c r="C13" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="E13" s="26" t="n">
+      <c r="E13" s="25" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D13,C13)</f>
         <v>10</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="14" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0" t="s">
         <v>139</v>
       </c>
-      <c r="C14" s="21" t="n">
+      <c r="C14" s="20" t="n">
         <v>0.02</v>
       </c>
-      <c r="D14" s="21" t="n">
+      <c r="D14" s="20" t="n">
         <v>0.025</v>
       </c>
-      <c r="E14" s="22" t="n">
+      <c r="E14" s="21" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D14,C14)</f>
         <v>0.02</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="14" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="0" t="s">
         <v>140</v>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C15" s="17" t="n">
         <v>100</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="17" t="n">
         <v>100</v>
       </c>
-      <c r="E15" s="19" t="n">
+      <c r="E15" s="18" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D15,C15)</f>
         <v>100</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="14" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="1" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="0" t="s">
         <v>141</v>
       </c>
-      <c r="C16" s="18" t="n">
+      <c r="C16" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="17" t="n">
         <v>25</v>
       </c>
-      <c r="E16" s="19" t="n">
+      <c r="E16" s="18" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D16,C16)</f>
         <v>20</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="14" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="1" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="0" t="s">
         <v>142</v>
       </c>
-      <c r="C17" s="18" t="n">
+      <c r="C17" s="17" t="n">
         <v>75</v>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D17" s="17" t="n">
         <v>75</v>
       </c>
-      <c r="E17" s="19" t="n">
+      <c r="E17" s="18" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D17,C17)</f>
         <v>75</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="14" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="1" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="0" t="s">
         <v>143</v>
       </c>
-      <c r="C18" s="23" t="n">
+      <c r="C18" s="22" t="n">
         <v>0.09</v>
       </c>
-      <c r="D18" s="23" t="n">
+      <c r="D18" s="22" t="n">
         <v>0.115</v>
       </c>
-      <c r="E18" s="24" t="n">
+      <c r="E18" s="23" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D18,C18)</f>
         <v>0.09</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="14" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="1" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="0" t="s">
         <v>144</v>
       </c>
-      <c r="C19" s="25" t="n">
+      <c r="C19" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="D19" s="25" t="n">
+      <c r="D19" s="24" t="n">
         <v>3.5</v>
       </c>
-      <c r="E19" s="26" t="n">
+      <c r="E19" s="25" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D19,C19)</f>
         <v>4</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="14" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="1" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="0" t="s">
         <v>146</v>
       </c>
-      <c r="C20" s="23" t="n">
+      <c r="C20" s="22" t="n">
         <v>0.085</v>
       </c>
-      <c r="D20" s="23" t="n">
+      <c r="D20" s="22" t="n">
         <v>0.105</v>
       </c>
-      <c r="E20" s="24" t="n">
+      <c r="E20" s="23" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D20,C20)</f>
         <v>0.085</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="14" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="1" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="0" t="s">
         <v>147</v>
       </c>
-      <c r="C21" s="21" t="n">
+      <c r="C21" s="20" t="n">
         <v>0.01</v>
       </c>
-      <c r="D21" s="21" t="n">
+      <c r="D21" s="20" t="n">
         <v>0.01</v>
       </c>
-      <c r="E21" s="22" t="n">
+      <c r="E21" s="21" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D21,C21)</f>
         <v>0.01</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="14" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="1" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="0" t="s">
         <v>149</v>
       </c>
-      <c r="C22" s="25" t="n">
+      <c r="C22" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="D22" s="25" t="n">
+      <c r="D22" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="26" t="n">
+      <c r="E22" s="25" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D22,C22)</f>
         <v>1.5</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="14" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="1" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="0" t="s">
         <v>150</v>
       </c>
-      <c r="C23" s="23" t="n">
+      <c r="C23" s="22" t="n">
         <v>0.11</v>
       </c>
-      <c r="D23" s="23" t="n">
+      <c r="D23" s="22" t="n">
         <v>0.13</v>
       </c>
-      <c r="E23" s="24" t="n">
+      <c r="E23" s="23" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D23,C23)</f>
         <v>0.11</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="14" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="1" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="0" t="s">
         <v>151</v>
       </c>
-      <c r="C24" s="23" t="n">
+      <c r="C24" s="22" t="n">
         <v>0.03</v>
       </c>
-      <c r="D24" s="23" t="n">
+      <c r="D24" s="22" t="n">
         <v>0.05</v>
       </c>
-      <c r="E24" s="24" t="n">
+      <c r="E24" s="23" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D24,C24)</f>
         <v>0.03</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="14" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="1" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="0" t="s">
         <v>152</v>
       </c>
-      <c r="C25" s="21" t="n">
+      <c r="C25" s="20" t="n">
         <v>0.75</v>
       </c>
-      <c r="D25" s="21" t="n">
+      <c r="D25" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="E25" s="22" t="n">
+      <c r="E25" s="21" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D25,C25)</f>
         <v>0.75</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="14" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="1" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="0" t="s">
         <v>154</v>
       </c>
-      <c r="C26" s="25" t="n">
+      <c r="C26" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="D26" s="25" t="n">
+      <c r="D26" s="24" t="n">
         <v>6.5</v>
       </c>
-      <c r="E26" s="26" t="n">
+      <c r="E26" s="25" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D26,C26)</f>
         <v>7</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="14" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="1" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="0" t="s">
         <v>155</v>
       </c>
-      <c r="C27" s="25" t="n">
+      <c r="C27" s="24" t="n">
         <v>1.75</v>
       </c>
-      <c r="D27" s="25" t="n">
+      <c r="D27" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="E27" s="26" t="n">
+      <c r="E27" s="25" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D27,C27)</f>
         <v>1.75</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="14" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="1" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="0" t="s">
         <v>156</v>
       </c>
-      <c r="C28" s="25" t="n">
+      <c r="C28" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="D28" s="25" t="n">
+      <c r="D28" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="E28" s="26" t="n">
+      <c r="E28" s="25" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D28,C28)</f>
         <v>10</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="14" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="1" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="0" t="s">
         <v>157</v>
       </c>
-      <c r="C29" s="27" t="n">
+      <c r="C29" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="D29" s="27" t="n">
+      <c r="D29" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="E29" s="28" t="n">
+      <c r="E29" s="27" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D29,C29)</f>
         <v>5</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="14" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="1" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="0" t="s">
         <v>159</v>
       </c>
-      <c r="C30" s="21" t="n">
+      <c r="C30" s="20" t="n">
         <v>0.1</v>
       </c>
-      <c r="D30" s="21" t="n">
+      <c r="D30" s="20" t="n">
         <v>0.1</v>
       </c>
-      <c r="E30" s="22" t="n">
+      <c r="E30" s="21" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D30,C30)</f>
         <v>0.1</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="14" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="1" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="0" t="s">
         <v>161</v>
       </c>
-      <c r="C31" s="21" t="n">
+      <c r="C31" s="20" t="n">
         <v>0.08</v>
       </c>
-      <c r="D31" s="21" t="n">
+      <c r="D31" s="20" t="n">
         <v>0.08</v>
       </c>
-      <c r="E31" s="22" t="n">
+      <c r="E31" s="21" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D31,C31)</f>
         <v>0.08</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="14" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="1" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="0" t="s">
         <v>162</v>
       </c>
-      <c r="C32" s="21" t="n">
+      <c r="C32" s="20" t="n">
         <v>0.2</v>
       </c>
-      <c r="D32" s="21" t="n">
+      <c r="D32" s="20" t="n">
         <v>0.2</v>
       </c>
-      <c r="E32" s="22" t="n">
+      <c r="E32" s="21" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D32,C32)</f>
         <v>0.2</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="14" t="s">
         <v>163</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="22" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="D33" s="22" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E33" s="23" t="n">
+        <f aca="false">IF(Cover!$C$9="Downside",D33,C33)</f>
+        <v>0.00375</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -4725,125 +4864,125 @@
   <dimension ref="B2:G10"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="5"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="C4" s="16" t="s">
+      <c r="B2" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="F4" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="G4" s="16"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+      <c r="C4" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="D4" s="15"/>
+      <c r="E4" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="G4" s="15"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="C5" s="18" t="n">
         <f aca="false">Assumptions!E5*Assumptions!E6*Assumptions!E13</f>
         <v>233583.57</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F5" s="18" t="n">
+      <c r="E5" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="F5" s="17" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C6" s="19" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="C6" s="18" t="n">
         <f aca="false">Assumptions!E15</f>
         <v>100</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="F6" s="19" t="n">
+      <c r="E6" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="F6" s="18" t="n">
         <f aca="false">Assumptions!E5*Assumptions!E6*Assumptions!E19</f>
         <v>93433.428</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C7" s="19" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
+        <v>174</v>
+      </c>
+      <c r="C7" s="18" t="n">
         <f aca="false">C5*Assumptions!E14</f>
         <v>4671.6714</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="F7" s="19" t="n">
+      <c r="E7" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="F7" s="18" t="n">
         <f aca="false">Assumptions!E5*Assumptions!E6*Assumptions!E22</f>
         <v>35037.5355</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="C8" s="19" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" s="18" t="n">
         <f aca="false">Assumptions!E16</f>
         <v>20</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="F8" s="19" t="n">
+      <c r="E8" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="F8" s="18" t="n">
         <f aca="false">C9-SUM(F5:F7)</f>
         <v>109904.2779</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="29" t="s">
-        <v>176</v>
-      </c>
-      <c r="C9" s="30" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="C9" s="29" t="n">
         <f aca="false">SUM(C5:C8)</f>
         <v>238375.2414</v>
       </c>
-      <c r="E9" s="29" t="s">
-        <v>177</v>
-      </c>
-      <c r="F9" s="30" t="n">
+      <c r="E9" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="F9" s="29" t="n">
         <f aca="false">SUM(F5:F8)</f>
         <v>238375.2414</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E10" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="F10" s="19" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E10" s="0" t="s">
+        <v>180</v>
+      </c>
+      <c r="F10" s="18" t="n">
         <f aca="false">F9-C9</f>
         <v>0</v>
       </c>
@@ -4870,571 +5009,571 @@
   <dimension ref="B2:J19"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="3" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="3" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="C4" s="16" t="s">
+      <c r="B2" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="E4" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="F4" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="G4" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="H4" s="15" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
+      <c r="I4" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="J4" s="15" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="C5" s="18" t="n">
         <f aca="false">Assumptions!E5</f>
         <v>152669</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="18" t="n">
         <f aca="false">C5*(1+Assumptions!$E$7)</f>
         <v>148088.93</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="18" t="n">
         <f aca="false">D5*(1+Assumptions!$E$7)</f>
         <v>143646.2621</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="18" t="n">
         <f aca="false">E5*(1+Assumptions!$E$7)</f>
         <v>139336.874237</v>
       </c>
-      <c r="G5" s="19" t="n">
+      <c r="G5" s="18" t="n">
         <f aca="false">F5*(1+Assumptions!$E$7)</f>
         <v>135156.76800989</v>
       </c>
-      <c r="H5" s="19" t="n">
+      <c r="H5" s="18" t="n">
         <f aca="false">G5*(1+Assumptions!$E$7)</f>
         <v>131102.064969593</v>
       </c>
-      <c r="I5" s="19" t="n">
+      <c r="I5" s="18" t="n">
         <f aca="false">H5*(1+Assumptions!$E$7)</f>
         <v>127169.003020505</v>
       </c>
-      <c r="J5" s="19" t="n">
+      <c r="J5" s="18" t="n">
         <f aca="false">I5*(1+Assumptions!$E$7)</f>
         <v>123353.93292989</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D6" s="22" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="D6" s="21" t="n">
         <f aca="false">IFERROR(D5/C5-1,0)</f>
         <v>-0.03</v>
       </c>
-      <c r="E6" s="22" t="n">
+      <c r="E6" s="21" t="n">
         <f aca="false">IFERROR(E5/D5-1,0)</f>
         <v>-0.03</v>
       </c>
-      <c r="F6" s="22" t="n">
+      <c r="F6" s="21" t="n">
         <f aca="false">IFERROR(F5/E5-1,0)</f>
         <v>-0.03</v>
       </c>
-      <c r="G6" s="22" t="n">
+      <c r="G6" s="21" t="n">
         <f aca="false">IFERROR(G5/F5-1,0)</f>
         <v>-0.0299999999999999</v>
       </c>
-      <c r="H6" s="22" t="n">
+      <c r="H6" s="21" t="n">
         <f aca="false">IFERROR(H5/G5-1,0)</f>
         <v>-0.03</v>
       </c>
-      <c r="I6" s="22" t="n">
+      <c r="I6" s="21" t="n">
         <f aca="false">IFERROR(I5/H5-1,0)</f>
         <v>-0.03</v>
       </c>
-      <c r="J6" s="22" t="n">
+      <c r="J6" s="21" t="n">
         <f aca="false">IFERROR(J5/I5-1,0)</f>
         <v>-0.03</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C7" s="22" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="C7" s="21" t="n">
         <f aca="false">Assumptions!E6</f>
         <v>0.153</v>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="D7" s="21" t="n">
         <f aca="false">MAX(0,MIN(0.6,C7+Assumptions!$E$8))</f>
         <v>0.158</v>
       </c>
-      <c r="E7" s="22" t="n">
+      <c r="E7" s="21" t="n">
         <f aca="false">MAX(0,MIN(0.6,D7+Assumptions!$E$8))</f>
         <v>0.163</v>
       </c>
-      <c r="F7" s="22" t="n">
+      <c r="F7" s="21" t="n">
         <f aca="false">MAX(0,MIN(0.6,E7+Assumptions!$E$8))</f>
         <v>0.168</v>
       </c>
-      <c r="G7" s="22" t="n">
+      <c r="G7" s="21" t="n">
         <f aca="false">MAX(0,MIN(0.6,F7+Assumptions!$E$8))</f>
         <v>0.173</v>
       </c>
-      <c r="H7" s="22" t="n">
+      <c r="H7" s="21" t="n">
         <f aca="false">MAX(0,MIN(0.6,G7+Assumptions!$E$8))</f>
         <v>0.178</v>
       </c>
-      <c r="I7" s="22" t="n">
+      <c r="I7" s="21" t="n">
         <f aca="false">MAX(0,MIN(0.6,H7+Assumptions!$E$8))</f>
         <v>0.183</v>
       </c>
-      <c r="J7" s="22" t="n">
+      <c r="J7" s="21" t="n">
         <f aca="false">MAX(0,MIN(0.6,I7+Assumptions!$E$8))</f>
         <v>0.188</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="29" t="s">
-        <v>192</v>
-      </c>
-      <c r="C8" s="30" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" s="29" t="n">
         <f aca="false">C5*C7</f>
         <v>23358.357</v>
       </c>
-      <c r="D8" s="30" t="n">
+      <c r="D8" s="29" t="n">
         <f aca="false">D5*D7</f>
         <v>23398.05094</v>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E8" s="29" t="n">
         <f aca="false">E5*E7</f>
         <v>23414.3407223</v>
       </c>
-      <c r="F8" s="30" t="n">
+      <c r="F8" s="29" t="n">
         <f aca="false">F5*F7</f>
         <v>23408.594871816</v>
       </c>
-      <c r="G8" s="30" t="n">
+      <c r="G8" s="29" t="n">
         <f aca="false">G5*G7</f>
         <v>23382.120865711</v>
       </c>
-      <c r="H8" s="30" t="n">
+      <c r="H8" s="29" t="n">
         <f aca="false">H5*H7</f>
         <v>23336.1675645876</v>
       </c>
-      <c r="I8" s="30" t="n">
+      <c r="I8" s="29" t="n">
         <f aca="false">I5*I7</f>
         <v>23271.9275527525</v>
       </c>
-      <c r="J8" s="30" t="n">
+      <c r="J8" s="29" t="n">
         <f aca="false">J5*J7</f>
         <v>23190.5393908194</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C9" s="19" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="s">
+        <v>195</v>
+      </c>
+      <c r="C9" s="18" t="n">
         <f aca="false">C5*Assumptions!E9</f>
         <v>3816.725</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="18" t="n">
         <f aca="false">D5*Assumptions!$E$9</f>
         <v>3702.22325</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="18" t="n">
         <f aca="false">E5*Assumptions!$E$9</f>
         <v>3591.1565525</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="18" t="n">
         <f aca="false">F5*Assumptions!$E$9</f>
         <v>3483.421855925</v>
       </c>
-      <c r="G9" s="19" t="n">
+      <c r="G9" s="18" t="n">
         <f aca="false">G5*Assumptions!$E$9</f>
         <v>3378.91920024725</v>
       </c>
-      <c r="H9" s="19" t="n">
+      <c r="H9" s="18" t="n">
         <f aca="false">H5*Assumptions!$E$9</f>
         <v>3277.55162423983</v>
       </c>
-      <c r="I9" s="19" t="n">
+      <c r="I9" s="18" t="n">
         <f aca="false">I5*Assumptions!$E$9</f>
         <v>3179.22507551264</v>
       </c>
-      <c r="J9" s="19" t="n">
+      <c r="J9" s="18" t="n">
         <f aca="false">J5*Assumptions!$E$9</f>
         <v>3083.84832324726</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="C10" s="19" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="C10" s="18" t="n">
         <f aca="false">C8-C9</f>
         <v>19541.632</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="18" t="n">
         <f aca="false">D8-D9</f>
         <v>19695.82769</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="18" t="n">
         <f aca="false">E8-E9</f>
         <v>19823.1841698</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="18" t="n">
         <f aca="false">F8-F9</f>
         <v>19925.173015891</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="18" t="n">
         <f aca="false">G8-G9</f>
         <v>20003.2016654637</v>
       </c>
-      <c r="H10" s="19" t="n">
+      <c r="H10" s="18" t="n">
         <f aca="false">H8-H9</f>
         <v>20058.6159403478</v>
       </c>
-      <c r="I10" s="19" t="n">
+      <c r="I10" s="18" t="n">
         <f aca="false">I8-I9</f>
         <v>20092.7024772399</v>
       </c>
-      <c r="J10" s="19" t="n">
+      <c r="J10" s="18" t="n">
         <f aca="false">J8-J9</f>
         <v>20106.6910675721</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D11" s="19" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="D11" s="18" t="n">
         <f aca="false">'Debt Schedule'!D7</f>
-        <v>11795.970285</v>
-      </c>
-      <c r="E11" s="19" t="n">
+        <v>11796.251535</v>
+      </c>
+      <c r="E11" s="18" t="n">
         <f aca="false">'Debt Schedule'!E7</f>
-        <v>11505.1319040023</v>
-      </c>
-      <c r="F11" s="19" t="n">
+        <v>11505.4309518539</v>
+      </c>
+      <c r="F11" s="18" t="n">
         <f aca="false">'Debt Schedule'!F7</f>
-        <v>11165.6387475201</v>
-      </c>
-      <c r="G11" s="19" t="n">
+        <v>11165.9579623768</v>
+      </c>
+      <c r="G11" s="18" t="n">
         <f aca="false">'Debt Schedule'!G7</f>
-        <v>10793.1016843274</v>
-      </c>
-      <c r="H11" s="19" t="n">
+        <v>10793.4426331471</v>
+      </c>
+      <c r="H11" s="18" t="n">
         <f aca="false">'Debt Schedule'!H7</f>
-        <v>10387.7988438072</v>
-      </c>
-      <c r="I11" s="19" t="n">
+        <v>10388.163156209</v>
+      </c>
+      <c r="I11" s="18" t="n">
         <f aca="false">'Debt Schedule'!I7</f>
-        <v>9948.97027364607</v>
-      </c>
-      <c r="J11" s="19" t="n">
+        <v>9949.35970106571</v>
+      </c>
+      <c r="J11" s="18" t="n">
         <f aca="false">'Debt Schedule'!J7</f>
-        <v>9475.64867775454</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D12" s="19" t="n">
+        <v>9476.06510604968</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="0" t="s">
+        <v>198</v>
+      </c>
+      <c r="D12" s="18" t="n">
         <f aca="false">D10-D11</f>
-        <v>7899.857405</v>
-      </c>
-      <c r="E12" s="19" t="n">
+        <v>7899.576155</v>
+      </c>
+      <c r="E12" s="18" t="n">
         <f aca="false">E10-E11</f>
-        <v>8318.05226579765</v>
-      </c>
-      <c r="F12" s="19" t="n">
+        <v>8317.75321794609</v>
+      </c>
+      <c r="F12" s="18" t="n">
         <f aca="false">F10-F11</f>
-        <v>8759.5342683709</v>
-      </c>
-      <c r="G12" s="19" t="n">
+        <v>8759.21505351418</v>
+      </c>
+      <c r="G12" s="18" t="n">
         <f aca="false">G10-G11</f>
-        <v>9210.09998113632</v>
-      </c>
-      <c r="H12" s="19" t="n">
+        <v>9209.75903231663</v>
+      </c>
+      <c r="H12" s="18" t="n">
         <f aca="false">H10-H11</f>
-        <v>9670.81709654059</v>
-      </c>
-      <c r="I12" s="19" t="n">
+        <v>9670.45278413877</v>
+      </c>
+      <c r="I12" s="18" t="n">
         <f aca="false">I10-I11</f>
-        <v>10143.7322035938</v>
-      </c>
-      <c r="J12" s="19" t="n">
+        <v>10143.3427761742</v>
+      </c>
+      <c r="J12" s="18" t="n">
         <f aca="false">J10-J11</f>
-        <v>10631.0423898176</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="D13" s="19" t="n">
+        <v>10630.6259615224</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="0" t="s">
+        <v>199</v>
+      </c>
+      <c r="D13" s="18" t="n">
         <f aca="false">MAX(0,D12*Assumptions!$E$12)</f>
-        <v>1974.96435125</v>
-      </c>
-      <c r="E13" s="19" t="n">
+        <v>1974.89403875</v>
+      </c>
+      <c r="E13" s="18" t="n">
         <f aca="false">MAX(0,E12*Assumptions!$E$12)</f>
-        <v>2079.51306644941</v>
-      </c>
-      <c r="F13" s="19" t="n">
+        <v>2079.43830448652</v>
+      </c>
+      <c r="F13" s="18" t="n">
         <f aca="false">MAX(0,F12*Assumptions!$E$12)</f>
-        <v>2189.88356709272</v>
-      </c>
-      <c r="G13" s="19" t="n">
+        <v>2189.80376337854</v>
+      </c>
+      <c r="G13" s="18" t="n">
         <f aca="false">MAX(0,G12*Assumptions!$E$12)</f>
-        <v>2302.52499528408</v>
-      </c>
-      <c r="H13" s="19" t="n">
+        <v>2302.43975807916</v>
+      </c>
+      <c r="H13" s="18" t="n">
         <f aca="false">MAX(0,H12*Assumptions!$E$12)</f>
-        <v>2417.70427413515</v>
-      </c>
-      <c r="I13" s="19" t="n">
+        <v>2417.61319603469</v>
+      </c>
+      <c r="I13" s="18" t="n">
         <f aca="false">MAX(0,I12*Assumptions!$E$12)</f>
-        <v>2535.93305089845</v>
-      </c>
-      <c r="J13" s="19" t="n">
+        <v>2535.83569404354</v>
+      </c>
+      <c r="J13" s="18" t="n">
         <f aca="false">MAX(0,J12*Assumptions!$E$12)</f>
-        <v>2657.7605974544</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="D14" s="19" t="n">
+        <v>2657.65649038061</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0" t="s">
+        <v>200</v>
+      </c>
+      <c r="D14" s="18" t="n">
         <f aca="false">D12-D13</f>
-        <v>5924.89305375</v>
-      </c>
-      <c r="E14" s="19" t="n">
+        <v>5924.68211625</v>
+      </c>
+      <c r="E14" s="18" t="n">
         <f aca="false">E12-E13</f>
-        <v>6238.53919934824</v>
-      </c>
-      <c r="F14" s="19" t="n">
+        <v>6238.31491345957</v>
+      </c>
+      <c r="F14" s="18" t="n">
         <f aca="false">F12-F13</f>
-        <v>6569.65070127817</v>
-      </c>
-      <c r="G14" s="19" t="n">
+        <v>6569.41129013564</v>
+      </c>
+      <c r="G14" s="18" t="n">
         <f aca="false">G12-G13</f>
-        <v>6907.57498585224</v>
-      </c>
-      <c r="H14" s="19" t="n">
+        <v>6907.31927423747</v>
+      </c>
+      <c r="H14" s="18" t="n">
         <f aca="false">H12-H13</f>
-        <v>7253.11282240544</v>
-      </c>
-      <c r="I14" s="19" t="n">
+        <v>7252.83958810408</v>
+      </c>
+      <c r="I14" s="18" t="n">
         <f aca="false">I12-I13</f>
-        <v>7607.79915269535</v>
-      </c>
-      <c r="J14" s="19" t="n">
+        <v>7607.50708213062</v>
+      </c>
+      <c r="J14" s="18" t="n">
         <f aca="false">J12-J13</f>
-        <v>7973.28179236319</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D15" s="19" t="n">
+        <v>7972.96947114184</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="D15" s="18" t="n">
         <f aca="false">D5*Assumptions!$E$10</f>
         <v>5183.11255</v>
       </c>
-      <c r="E15" s="19" t="n">
+      <c r="E15" s="18" t="n">
         <f aca="false">E5*Assumptions!$E$10</f>
         <v>5027.6191735</v>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F15" s="18" t="n">
         <f aca="false">F5*Assumptions!$E$10</f>
         <v>4876.790598295</v>
       </c>
-      <c r="G15" s="19" t="n">
+      <c r="G15" s="18" t="n">
         <f aca="false">G5*Assumptions!$E$10</f>
         <v>4730.48688034615</v>
       </c>
-      <c r="H15" s="19" t="n">
+      <c r="H15" s="18" t="n">
         <f aca="false">H5*Assumptions!$E$10</f>
         <v>4588.57227393577</v>
       </c>
-      <c r="I15" s="19" t="n">
+      <c r="I15" s="18" t="n">
         <f aca="false">I5*Assumptions!$E$10</f>
         <v>4450.91510571769</v>
       </c>
-      <c r="J15" s="19" t="n">
+      <c r="J15" s="18" t="n">
         <f aca="false">J5*Assumptions!$E$10</f>
         <v>4317.38765254616</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="C16" s="19" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="C16" s="18" t="n">
         <f aca="false">C5*Assumptions!E11</f>
         <v>12213.52</v>
       </c>
-      <c r="D16" s="19" t="n">
+      <c r="D16" s="18" t="n">
         <f aca="false">D5*Assumptions!$E$11</f>
         <v>11847.1144</v>
       </c>
-      <c r="E16" s="19" t="n">
+      <c r="E16" s="18" t="n">
         <f aca="false">E5*Assumptions!$E$11</f>
         <v>11491.700968</v>
       </c>
-      <c r="F16" s="19" t="n">
+      <c r="F16" s="18" t="n">
         <f aca="false">F5*Assumptions!$E$11</f>
         <v>11146.94993896</v>
       </c>
-      <c r="G16" s="19" t="n">
+      <c r="G16" s="18" t="n">
         <f aca="false">G5*Assumptions!$E$11</f>
         <v>10812.5414407912</v>
       </c>
-      <c r="H16" s="19" t="n">
+      <c r="H16" s="18" t="n">
         <f aca="false">H5*Assumptions!$E$11</f>
         <v>10488.1651975675</v>
       </c>
-      <c r="I16" s="19" t="n">
+      <c r="I16" s="18" t="n">
         <f aca="false">I5*Assumptions!$E$11</f>
         <v>10173.5202416404</v>
       </c>
-      <c r="J16" s="19" t="n">
+      <c r="J16" s="18" t="n">
         <f aca="false">J5*Assumptions!$E$11</f>
         <v>9868.31463439123</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="D17" s="19" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="D17" s="18" t="n">
         <f aca="false">D16-C16</f>
         <v>-366.4056</v>
       </c>
-      <c r="E17" s="19" t="n">
+      <c r="E17" s="18" t="n">
         <f aca="false">E16-D16</f>
         <v>-355.413432000001</v>
       </c>
-      <c r="F17" s="19" t="n">
+      <c r="F17" s="18" t="n">
         <f aca="false">F16-E16</f>
         <v>-344.751029040001</v>
       </c>
-      <c r="G17" s="19" t="n">
+      <c r="G17" s="18" t="n">
         <f aca="false">G16-F16</f>
         <v>-334.408498168799</v>
       </c>
-      <c r="H17" s="19" t="n">
+      <c r="H17" s="18" t="n">
         <f aca="false">H16-G16</f>
         <v>-324.376243223736</v>
       </c>
-      <c r="I17" s="19" t="n">
+      <c r="I17" s="18" t="n">
         <f aca="false">I16-H16</f>
         <v>-314.644955927024</v>
       </c>
-      <c r="J17" s="19" t="n">
+      <c r="J17" s="18" t="n">
         <f aca="false">J16-I16</f>
         <v>-305.205607249214</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="29" t="s">
-        <v>202</v>
-      </c>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29" t="n">
         <f aca="false">D14+D9-D15-D17</f>
-        <v>4810.40935375</v>
-      </c>
-      <c r="E18" s="30" t="n">
+        <v>4810.19841625</v>
+      </c>
+      <c r="E18" s="29" t="n">
         <f aca="false">E14+E9-E15-E17</f>
-        <v>5157.49001034824</v>
-      </c>
-      <c r="F18" s="30" t="n">
+        <v>5157.26572445957</v>
+      </c>
+      <c r="F18" s="29" t="n">
         <f aca="false">F14+F9-F15-F17</f>
-        <v>5521.03298794817</v>
-      </c>
-      <c r="G18" s="30" t="n">
+        <v>5520.79357680564</v>
+      </c>
+      <c r="G18" s="29" t="n">
         <f aca="false">G14+G9-G15-G17</f>
-        <v>5890.41580392214</v>
-      </c>
-      <c r="H18" s="30" t="n">
+        <v>5890.16009230737</v>
+      </c>
+      <c r="H18" s="29" t="n">
         <f aca="false">H14+H9-H15-H17</f>
-        <v>6266.46841593325</v>
-      </c>
-      <c r="I18" s="30" t="n">
+        <v>6266.19518163188</v>
+      </c>
+      <c r="I18" s="29" t="n">
         <f aca="false">I14+I9-I15-I17</f>
-        <v>6650.75407841732</v>
-      </c>
-      <c r="J18" s="30" t="n">
+        <v>6650.46200785259</v>
+      </c>
+      <c r="J18" s="29" t="n">
         <f aca="false">J14+J9-J15-J17</f>
-        <v>7044.9480703135</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="29" t="s">
-        <v>203</v>
-      </c>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30" t="n">
+        <v>7044.63574909215</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29" t="n">
         <f aca="false">D8-D13-D15-D17</f>
-        <v>16606.37963875</v>
-      </c>
-      <c r="E19" s="30" t="n">
+        <v>16606.44995125</v>
+      </c>
+      <c r="E19" s="29" t="n">
         <f aca="false">E8-E13-E15-E17</f>
-        <v>16662.6219143506</v>
-      </c>
-      <c r="F19" s="30" t="n">
+        <v>16662.6966763135</v>
+      </c>
+      <c r="F19" s="29" t="n">
         <f aca="false">F8-F13-F15-F17</f>
-        <v>16686.6717354683</v>
-      </c>
-      <c r="G19" s="30" t="n">
+        <v>16686.7515391825</v>
+      </c>
+      <c r="G19" s="29" t="n">
         <f aca="false">G8-G13-G15-G17</f>
-        <v>16683.5174882495</v>
-      </c>
-      <c r="H19" s="30" t="n">
+        <v>16683.6027254545</v>
+      </c>
+      <c r="H19" s="29" t="n">
         <f aca="false">H8-H13-H15-H17</f>
-        <v>16654.2672597404</v>
-      </c>
-      <c r="I19" s="30" t="n">
+        <v>16654.3583378409</v>
+      </c>
+      <c r="I19" s="29" t="n">
         <f aca="false">I8-I13-I15-I17</f>
-        <v>16599.7243520634</v>
-      </c>
-      <c r="J19" s="30" t="n">
+        <v>16599.8217089183</v>
+      </c>
+      <c r="J19" s="29" t="n">
         <f aca="false">J8-J13-J15-J17</f>
-        <v>16520.596748068</v>
+        <v>16520.7008551418</v>
       </c>
     </row>
   </sheetData>
@@ -5456,894 +5595,927 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:J28"/>
+  <dimension ref="B2:J29"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="3" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="3" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="D4" s="16" t="s">
+      <c r="B2" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="E4" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="F4" s="16" t="s">
+      <c r="C4" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="E4" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="F4" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="G4" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="H4" s="15" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C5" s="19" t="n">
+      <c r="I4" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="C5" s="18" t="n">
         <f aca="false">Assumptions!E16</f>
         <v>20</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="18" t="n">
         <f aca="false">C13</f>
         <v>20</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="18" t="n">
         <f aca="false">D13</f>
-        <v>262.254692109375</v>
-      </c>
-      <c r="F5" s="19" t="n">
+        <v>262.241508515625</v>
+      </c>
+      <c r="F5" s="18" t="n">
         <f aca="false">E13</f>
-        <v>299.088151403601</v>
-      </c>
-      <c r="G5" s="19" t="n">
+        <v>299.07330956095</v>
+      </c>
+      <c r="G5" s="18" t="n">
         <f aca="false">F13</f>
-        <v>324.111678709486</v>
-      </c>
-      <c r="H5" s="19" t="n">
+        <v>324.095787897912</v>
+      </c>
+      <c r="H5" s="18" t="n">
         <f aca="false">G13</f>
-        <v>348.762075164477</v>
-      </c>
-      <c r="I5" s="19" t="n">
+        <v>348.74510001283</v>
+      </c>
+      <c r="I5" s="18" t="n">
         <f aca="false">H13</f>
-        <v>373.806013193608</v>
-      </c>
-      <c r="J5" s="19" t="n">
+        <v>373.787875102795</v>
+      </c>
+      <c r="J5" s="18" t="n">
         <f aca="false">I13</f>
-        <v>399.389113225683</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D6" s="19" t="n">
+        <v>399.369725184711</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
+        <v>205</v>
+      </c>
+      <c r="D6" s="18" t="n">
         <f aca="false">'Operating Model'!D19</f>
-        <v>16606.37963875</v>
-      </c>
-      <c r="E6" s="19" t="n">
+        <v>16606.44995125</v>
+      </c>
+      <c r="E6" s="18" t="n">
         <f aca="false">'Operating Model'!E19</f>
-        <v>16662.6219143506</v>
-      </c>
-      <c r="F6" s="19" t="n">
+        <v>16662.6966763135</v>
+      </c>
+      <c r="F6" s="18" t="n">
         <f aca="false">'Operating Model'!F19</f>
-        <v>16686.6717354683</v>
-      </c>
-      <c r="G6" s="19" t="n">
+        <v>16686.7515391825</v>
+      </c>
+      <c r="G6" s="18" t="n">
         <f aca="false">'Operating Model'!G19</f>
-        <v>16683.5174882495</v>
-      </c>
-      <c r="H6" s="19" t="n">
+        <v>16683.6027254545</v>
+      </c>
+      <c r="H6" s="18" t="n">
         <f aca="false">'Operating Model'!H19</f>
-        <v>16654.2672597404</v>
-      </c>
-      <c r="I6" s="19" t="n">
+        <v>16654.3583378409</v>
+      </c>
+      <c r="I6" s="18" t="n">
         <f aca="false">'Operating Model'!I19</f>
-        <v>16599.7243520634</v>
-      </c>
-      <c r="J6" s="19" t="n">
+        <v>16599.8217089183</v>
+      </c>
+      <c r="J6" s="18" t="n">
         <f aca="false">'Operating Model'!J19</f>
-        <v>16520.596748068</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D7" s="19" t="n">
-        <f aca="false">SUM(D15,D18,D23)</f>
-        <v>11795.970285</v>
-      </c>
-      <c r="E7" s="19" t="n">
-        <f aca="false">SUM(E15,E18,E23)</f>
-        <v>11505.1319040023</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <f aca="false">SUM(F15,F18,F23)</f>
-        <v>11165.6387475201</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <f aca="false">SUM(G15,G18,G23)</f>
-        <v>10793.1016843274</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <f aca="false">SUM(H15,H18,H23)</f>
-        <v>10387.7988438072</v>
-      </c>
-      <c r="I7" s="19" t="n">
-        <f aca="false">SUM(I15,I18,I23)</f>
-        <v>9948.97027364607</v>
-      </c>
-      <c r="J7" s="19" t="n">
-        <f aca="false">SUM(J15,J18,J23)</f>
-        <v>9475.64867775454</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D8" s="19" t="n">
+        <v>16520.7008551418</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="D7" s="18" t="n">
+        <f aca="false">SUM(D15,D18,D23,D29)</f>
+        <v>11796.251535</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <f aca="false">SUM(E15,E18,E23,E29)</f>
+        <v>11505.4309518539</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <f aca="false">SUM(F15,F18,F23,F29)</f>
+        <v>11165.9579623768</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <f aca="false">SUM(G15,G18,G23,G29)</f>
+        <v>10793.4426331471</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <f aca="false">SUM(H15,H18,H23,H29)</f>
+        <v>10388.163156209</v>
+      </c>
+      <c r="I7" s="18" t="n">
+        <f aca="false">SUM(I15,I18,I23,I29)</f>
+        <v>9949.35970106571</v>
+      </c>
+      <c r="J7" s="18" t="n">
+        <f aca="false">SUM(J15,J18,J23,J29)</f>
+        <v>9476.06510604968</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="D8" s="18" t="n">
         <f aca="false">D19</f>
         <v>934.33428</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="18" t="n">
         <f aca="false">E19</f>
         <v>934.33428</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="18" t="n">
         <f aca="false">F19</f>
         <v>934.33428</v>
       </c>
-      <c r="G8" s="19" t="n">
+      <c r="G8" s="18" t="n">
         <f aca="false">G19</f>
         <v>934.33428</v>
       </c>
-      <c r="H8" s="19" t="n">
+      <c r="H8" s="18" t="n">
         <f aca="false">H19</f>
         <v>934.33428</v>
       </c>
-      <c r="I8" s="19" t="n">
+      <c r="I8" s="18" t="n">
         <f aca="false">I19</f>
         <v>934.33428</v>
       </c>
-      <c r="J8" s="19" t="n">
+      <c r="J8" s="18" t="n">
         <f aca="false">J19</f>
         <v>934.33428</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="D9" s="19" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="D9" s="18" t="n">
         <f aca="false">D5+D6-D7-D8</f>
-        <v>3896.07507375</v>
-      </c>
-      <c r="E9" s="19" t="n">
+        <v>3895.86413625</v>
+      </c>
+      <c r="E9" s="18" t="n">
         <f aca="false">E5+E6-E7-E8</f>
-        <v>4485.41042245762</v>
-      </c>
-      <c r="F9" s="19" t="n">
+        <v>4485.1729529752</v>
+      </c>
+      <c r="F9" s="18" t="n">
         <f aca="false">F5+F6-F7-F8</f>
-        <v>4885.78685935178</v>
-      </c>
-      <c r="G9" s="19" t="n">
+        <v>4885.53260636659</v>
+      </c>
+      <c r="G9" s="18" t="n">
         <f aca="false">G5+G6-G7-G8</f>
-        <v>5280.19320263163</v>
-      </c>
-      <c r="H9" s="19" t="n">
+        <v>5279.92160020528</v>
+      </c>
+      <c r="H9" s="18" t="n">
         <f aca="false">H5+H6-H7-H8</f>
-        <v>5680.89621109773</v>
-      </c>
-      <c r="I9" s="19" t="n">
+        <v>5680.60600164471</v>
+      </c>
+      <c r="I9" s="18" t="n">
         <f aca="false">I5+I6-I7-I8</f>
-        <v>6090.22581161093</v>
-      </c>
-      <c r="J9" s="19" t="n">
+        <v>6089.91560295538</v>
+      </c>
+      <c r="J9" s="18" t="n">
         <f aca="false">J5+J6-J7-J8</f>
-        <v>6510.00290353918</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="D10" s="19" t="n">
+        <v>6509.67119427686</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="D10" s="18" t="n">
         <f aca="false">IF(D9&lt;Assumptions!$E$16,MIN(Assumptions!$E$17-D14,Assumptions!$E$16-D9),-MIN(D14,MAX(0,D9-Assumptions!$E$16)))</f>
         <v>-0</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="18" t="n">
         <f aca="false">IF(E9&lt;Assumptions!$E$16,MIN(Assumptions!$E$17-E14,Assumptions!$E$16-E9),-MIN(E14,MAX(0,E9-Assumptions!$E$16)))</f>
         <v>-0</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="18" t="n">
         <f aca="false">IF(F9&lt;Assumptions!$E$16,MIN(Assumptions!$E$17-F14,Assumptions!$E$16-F9),-MIN(F14,MAX(0,F9-Assumptions!$E$16)))</f>
         <v>-0</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="18" t="n">
         <f aca="false">IF(G9&lt;Assumptions!$E$16,MIN(Assumptions!$E$17-G14,Assumptions!$E$16-G9),-MIN(G14,MAX(0,G9-Assumptions!$E$16)))</f>
         <v>-0</v>
       </c>
-      <c r="H10" s="19" t="n">
+      <c r="H10" s="18" t="n">
         <f aca="false">IF(H9&lt;Assumptions!$E$16,MIN(Assumptions!$E$17-H14,Assumptions!$E$16-H9),-MIN(H14,MAX(0,H9-Assumptions!$E$16)))</f>
         <v>-0</v>
       </c>
-      <c r="I10" s="19" t="n">
+      <c r="I10" s="18" t="n">
         <f aca="false">IF(I9&lt;Assumptions!$E$16,MIN(Assumptions!$E$17-I14,Assumptions!$E$16-I9),-MIN(I14,MAX(0,I9-Assumptions!$E$16)))</f>
         <v>-0</v>
       </c>
-      <c r="J10" s="19" t="n">
+      <c r="J10" s="18" t="n">
         <f aca="false">IF(J9&lt;Assumptions!$E$16,MIN(Assumptions!$E$17-J14,Assumptions!$E$16-J9),-MIN(J14,MAX(0,J9-Assumptions!$E$16)))</f>
         <v>-0</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D11" s="19" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="0" t="s">
+        <v>212</v>
+      </c>
+      <c r="D11" s="18" t="n">
         <f aca="false">MIN(MAX(0,D17-D19),MAX(0,D9+D10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>2907.0563053125</v>
-      </c>
-      <c r="E11" s="19" t="n">
+        <v>2906.8981021875</v>
+      </c>
+      <c r="E11" s="18" t="n">
         <f aca="false">MIN(MAX(0,E17-E19),MAX(0,E9+E10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>3349.05781684321</v>
-      </c>
-      <c r="F11" s="19" t="n">
+        <v>3348.8797147314</v>
+      </c>
+      <c r="F11" s="18" t="n">
         <f aca="false">MIN(MAX(0,F17-F19),MAX(0,F9+F10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>3649.34014451383</v>
-      </c>
-      <c r="G11" s="19" t="n">
+        <v>3649.14945477494</v>
+      </c>
+      <c r="G11" s="18" t="n">
         <f aca="false">MIN(MAX(0,G17-G19),MAX(0,G9+G10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>3945.14490197372</v>
-      </c>
-      <c r="H11" s="19" t="n">
+        <v>3944.94120015396</v>
+      </c>
+      <c r="H11" s="18" t="n">
         <f aca="false">MIN(MAX(0,H17-H19),MAX(0,H9+H10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>4245.67215832329</v>
-      </c>
-      <c r="I11" s="19" t="n">
+        <v>4245.45450123354</v>
+      </c>
+      <c r="I11" s="18" t="n">
         <f aca="false">MIN(MAX(0,I17-I19),MAX(0,I9+I10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>4552.6693587082</v>
-      </c>
-      <c r="J11" s="19" t="n">
+        <v>4552.43670221653</v>
+      </c>
+      <c r="J11" s="18" t="n">
         <f aca="false">MIN(MAX(0,J17-J19),MAX(0,J9+J10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>4867.50217765439</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="D12" s="19" t="n">
+        <v>4867.25339570764</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="D12" s="18" t="n">
         <f aca="false">MIN(MAX(0,D22+D24),MAX(0,D9+D10-D11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>726.764076328124</v>
-      </c>
-      <c r="E12" s="19" t="n">
+        <v>726.724525546874</v>
+      </c>
+      <c r="E12" s="18" t="n">
         <f aca="false">MIN(MAX(0,E22+E24),MAX(0,E9+E10-E11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>837.264454210804</v>
-      </c>
-      <c r="F12" s="19" t="n">
+        <v>837.21992868285</v>
+      </c>
+      <c r="F12" s="18" t="n">
         <f aca="false">MIN(MAX(0,F22+F24),MAX(0,F9+F10-F11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>912.335036128458</v>
-      </c>
-      <c r="G12" s="19" t="n">
+        <v>912.287363693735</v>
+      </c>
+      <c r="G12" s="18" t="n">
         <f aca="false">MIN(MAX(0,G22+G24),MAX(0,G9+G10-G11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>986.28622549343</v>
-      </c>
-      <c r="H12" s="19" t="n">
+        <v>986.23530003849</v>
+      </c>
+      <c r="H12" s="18" t="n">
         <f aca="false">MIN(MAX(0,H22+H24),MAX(0,H9+H10-H11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>1061.41803958082</v>
-      </c>
-      <c r="I12" s="19" t="n">
+        <v>1061.36362530838</v>
+      </c>
+      <c r="I12" s="18" t="n">
         <f aca="false">MIN(MAX(0,I22+I24),MAX(0,I9+I10-I11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>1138.16733967705</v>
-      </c>
-      <c r="J12" s="19" t="n">
+        <v>1138.10917555413</v>
+      </c>
+      <c r="J12" s="18" t="n">
         <f aca="false">MIN(MAX(0,J22+J24),MAX(0,J9+J10-J11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>1216.8755444136</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="29" t="s">
-        <v>212</v>
-      </c>
-      <c r="C13" s="30" t="n">
+        <v>1216.81334892691</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="C13" s="29" t="n">
         <f aca="false">C5</f>
         <v>20</v>
       </c>
-      <c r="D13" s="30" t="n">
+      <c r="D13" s="29" t="n">
         <f aca="false">D9+D10-D11-D12</f>
-        <v>262.254692109375</v>
-      </c>
-      <c r="E13" s="30" t="n">
+        <v>262.241508515625</v>
+      </c>
+      <c r="E13" s="29" t="n">
         <f aca="false">E9+E10-E11-E12</f>
-        <v>299.088151403601</v>
-      </c>
-      <c r="F13" s="30" t="n">
+        <v>299.07330956095</v>
+      </c>
+      <c r="F13" s="29" t="n">
         <f aca="false">F9+F10-F11-F12</f>
-        <v>324.111678709486</v>
-      </c>
-      <c r="G13" s="30" t="n">
+        <v>324.095787897912</v>
+      </c>
+      <c r="G13" s="29" t="n">
         <f aca="false">G9+G10-G11-G12</f>
-        <v>348.762075164477</v>
-      </c>
-      <c r="H13" s="30" t="n">
+        <v>348.74510001283</v>
+      </c>
+      <c r="H13" s="29" t="n">
         <f aca="false">H9+H10-H11-H12</f>
-        <v>373.806013193608</v>
-      </c>
-      <c r="I13" s="30" t="n">
+        <v>373.787875102795</v>
+      </c>
+      <c r="I13" s="29" t="n">
         <f aca="false">I9+I10-I11-I12</f>
-        <v>399.389113225683</v>
-      </c>
-      <c r="J13" s="30" t="n">
+        <v>399.369725184711</v>
+      </c>
+      <c r="J13" s="29" t="n">
         <f aca="false">J9+J10-J11-J12</f>
-        <v>425.625181471199</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C14" s="19" t="n">
+        <v>425.604449642304</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="C14" s="18" t="n">
         <f aca="false">'Sources &amp; Uses'!F5</f>
         <v>0</v>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="18" t="n">
         <f aca="false">C16</f>
         <v>0</v>
       </c>
-      <c r="E14" s="19" t="n">
+      <c r="E14" s="18" t="n">
         <f aca="false">D16</f>
         <v>0</v>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F14" s="18" t="n">
         <f aca="false">E16</f>
         <v>0</v>
       </c>
-      <c r="G14" s="19" t="n">
+      <c r="G14" s="18" t="n">
         <f aca="false">F16</f>
         <v>0</v>
       </c>
-      <c r="H14" s="19" t="n">
+      <c r="H14" s="18" t="n">
         <f aca="false">G16</f>
         <v>0</v>
       </c>
-      <c r="I14" s="19" t="n">
+      <c r="I14" s="18" t="n">
         <f aca="false">H16</f>
         <v>0</v>
       </c>
-      <c r="J14" s="19" t="n">
+      <c r="J14" s="18" t="n">
         <f aca="false">I16</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="D15" s="19" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="D15" s="18" t="n">
         <f aca="false">D14*Assumptions!$E$18</f>
         <v>0</v>
       </c>
-      <c r="E15" s="19" t="n">
+      <c r="E15" s="18" t="n">
         <f aca="false">E14*Assumptions!$E$18</f>
         <v>0</v>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F15" s="18" t="n">
         <f aca="false">F14*Assumptions!$E$18</f>
         <v>0</v>
       </c>
-      <c r="G15" s="19" t="n">
+      <c r="G15" s="18" t="n">
         <f aca="false">G14*Assumptions!$E$18</f>
         <v>0</v>
       </c>
-      <c r="H15" s="19" t="n">
+      <c r="H15" s="18" t="n">
         <f aca="false">H14*Assumptions!$E$18</f>
         <v>0</v>
       </c>
-      <c r="I15" s="19" t="n">
+      <c r="I15" s="18" t="n">
         <f aca="false">I14*Assumptions!$E$18</f>
         <v>0</v>
       </c>
-      <c r="J15" s="19" t="n">
+      <c r="J15" s="18" t="n">
         <f aca="false">J14*Assumptions!$E$18</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C16" s="19" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="C16" s="18" t="n">
         <f aca="false">C14</f>
         <v>0</v>
       </c>
-      <c r="D16" s="19" t="n">
+      <c r="D16" s="18" t="n">
         <f aca="false">MAX(0,D14+D10)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="19" t="n">
+      <c r="E16" s="18" t="n">
         <f aca="false">MAX(0,E14+E10)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="19" t="n">
+      <c r="F16" s="18" t="n">
         <f aca="false">MAX(0,F14+F10)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="19" t="n">
+      <c r="G16" s="18" t="n">
         <f aca="false">MAX(0,G14+G10)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="19" t="n">
+      <c r="H16" s="18" t="n">
         <f aca="false">MAX(0,H14+H10)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="19" t="n">
+      <c r="I16" s="18" t="n">
         <f aca="false">MAX(0,I14+I10)</f>
         <v>0</v>
       </c>
-      <c r="J16" s="19" t="n">
+      <c r="J16" s="18" t="n">
         <f aca="false">MAX(0,J14+J10)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C17" s="19" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="C17" s="18" t="n">
         <f aca="false">'Sources &amp; Uses'!F6</f>
         <v>93433.428</v>
       </c>
-      <c r="D17" s="19" t="n">
+      <c r="D17" s="18" t="n">
         <f aca="false">C21</f>
         <v>93433.428</v>
       </c>
-      <c r="E17" s="19" t="n">
+      <c r="E17" s="18" t="n">
         <f aca="false">D21</f>
-        <v>89592.0374146875</v>
-      </c>
-      <c r="F17" s="19" t="n">
+        <v>89592.1956178125</v>
+      </c>
+      <c r="F17" s="18" t="n">
         <f aca="false">E21</f>
-        <v>85308.6453178443</v>
-      </c>
-      <c r="G17" s="19" t="n">
+        <v>85308.9816230811</v>
+      </c>
+      <c r="G17" s="18" t="n">
         <f aca="false">F21</f>
-        <v>80724.9708933305</v>
-      </c>
-      <c r="H17" s="19" t="n">
+        <v>80725.4978883062</v>
+      </c>
+      <c r="H17" s="18" t="n">
         <f aca="false">G21</f>
-        <v>75845.4917113568</v>
-      </c>
-      <c r="I17" s="19" t="n">
+        <v>75846.2224081522</v>
+      </c>
+      <c r="I17" s="18" t="n">
         <f aca="false">H21</f>
-        <v>70665.4852730335</v>
-      </c>
-      <c r="J17" s="19" t="n">
+        <v>70666.4336269187</v>
+      </c>
+      <c r="J17" s="18" t="n">
         <f aca="false">I21</f>
-        <v>65178.4816343253</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="D18" s="19" t="n">
+        <v>65179.6626447022</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="0" t="s">
+        <v>219</v>
+      </c>
+      <c r="D18" s="18" t="n">
         <f aca="false">D17*Assumptions!$E$20</f>
         <v>7941.84138</v>
       </c>
-      <c r="E18" s="19" t="n">
+      <c r="E18" s="18" t="n">
         <f aca="false">E17*Assumptions!$E$20</f>
-        <v>7615.32318024844</v>
-      </c>
-      <c r="F18" s="19" t="n">
+        <v>7615.33662751406</v>
+      </c>
+      <c r="F18" s="18" t="n">
         <f aca="false">F17*Assumptions!$E$20</f>
-        <v>7251.23485201677</v>
-      </c>
-      <c r="G18" s="19" t="n">
+        <v>7251.2634379619</v>
+      </c>
+      <c r="G18" s="18" t="n">
         <f aca="false">G17*Assumptions!$E$20</f>
-        <v>6861.62252593309</v>
-      </c>
-      <c r="H18" s="19" t="n">
+        <v>6861.66732050603</v>
+      </c>
+      <c r="H18" s="18" t="n">
         <f aca="false">H17*Assumptions!$E$20</f>
-        <v>6446.86679546533</v>
-      </c>
-      <c r="I18" s="19" t="n">
+        <v>6446.92890469294</v>
+      </c>
+      <c r="I18" s="18" t="n">
         <f aca="false">I17*Assumptions!$E$20</f>
-        <v>6006.56624820785</v>
-      </c>
-      <c r="J18" s="19" t="n">
+        <v>6006.64685828809</v>
+      </c>
+      <c r="J18" s="18" t="n">
         <f aca="false">J17*Assumptions!$E$20</f>
-        <v>5540.17093891765</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="D19" s="19" t="n">
+        <v>5540.27132479968</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="0" t="s">
+        <v>220</v>
+      </c>
+      <c r="D19" s="18" t="n">
         <f aca="false">MIN(D17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
         <v>934.33428</v>
       </c>
-      <c r="E19" s="19" t="n">
+      <c r="E19" s="18" t="n">
         <f aca="false">MIN(E17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
         <v>934.33428</v>
       </c>
-      <c r="F19" s="19" t="n">
+      <c r="F19" s="18" t="n">
         <f aca="false">MIN(F17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
         <v>934.33428</v>
       </c>
-      <c r="G19" s="19" t="n">
+      <c r="G19" s="18" t="n">
         <f aca="false">MIN(G17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
         <v>934.33428</v>
       </c>
-      <c r="H19" s="19" t="n">
+      <c r="H19" s="18" t="n">
         <f aca="false">MIN(H17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
         <v>934.33428</v>
       </c>
-      <c r="I19" s="19" t="n">
+      <c r="I19" s="18" t="n">
         <f aca="false">MIN(I17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
         <v>934.33428</v>
       </c>
-      <c r="J19" s="19" t="n">
+      <c r="J19" s="18" t="n">
         <f aca="false">MIN(J17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
         <v>934.33428</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="29" t="s">
-        <v>219</v>
-      </c>
-      <c r="C20" s="30" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="C20" s="29" t="n">
         <f aca="false">'Sources &amp; Uses'!F7</f>
         <v>35037.5355</v>
       </c>
-      <c r="D20" s="30" t="n">
+      <c r="D20" s="29" t="n">
         <f aca="false">D11</f>
-        <v>2907.0563053125</v>
-      </c>
-      <c r="E20" s="30" t="n">
+        <v>2906.8981021875</v>
+      </c>
+      <c r="E20" s="29" t="n">
         <f aca="false">E11</f>
-        <v>3349.05781684321</v>
-      </c>
-      <c r="F20" s="30" t="n">
+        <v>3348.8797147314</v>
+      </c>
+      <c r="F20" s="29" t="n">
         <f aca="false">F11</f>
-        <v>3649.34014451383</v>
-      </c>
-      <c r="G20" s="30" t="n">
+        <v>3649.14945477494</v>
+      </c>
+      <c r="G20" s="29" t="n">
         <f aca="false">G11</f>
-        <v>3945.14490197372</v>
-      </c>
-      <c r="H20" s="30" t="n">
+        <v>3944.94120015396</v>
+      </c>
+      <c r="H20" s="29" t="n">
         <f aca="false">H11</f>
-        <v>4245.67215832329</v>
-      </c>
-      <c r="I20" s="30" t="n">
+        <v>4245.45450123354</v>
+      </c>
+      <c r="I20" s="29" t="n">
         <f aca="false">I11</f>
-        <v>4552.6693587082</v>
-      </c>
-      <c r="J20" s="30" t="n">
+        <v>4552.43670221653</v>
+      </c>
+      <c r="J20" s="29" t="n">
         <f aca="false">J11</f>
-        <v>4867.50217765439</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="C21" s="19" t="n">
+        <v>4867.25339570764</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="0" t="s">
+        <v>222</v>
+      </c>
+      <c r="C21" s="18" t="n">
         <f aca="false">C17</f>
         <v>93433.428</v>
       </c>
-      <c r="D21" s="19" t="n">
+      <c r="D21" s="18" t="n">
         <f aca="false">MAX(0,D17-D19-D20)</f>
-        <v>89592.0374146875</v>
-      </c>
-      <c r="E21" s="19" t="n">
+        <v>89592.1956178125</v>
+      </c>
+      <c r="E21" s="18" t="n">
         <f aca="false">MAX(0,E17-E19-E20)</f>
-        <v>85308.6453178443</v>
-      </c>
-      <c r="F21" s="19" t="n">
+        <v>85308.9816230811</v>
+      </c>
+      <c r="F21" s="18" t="n">
         <f aca="false">MAX(0,F17-F19-F20)</f>
-        <v>80724.9708933305</v>
-      </c>
-      <c r="G21" s="19" t="n">
+        <v>80725.4978883062</v>
+      </c>
+      <c r="G21" s="18" t="n">
         <f aca="false">MAX(0,G17-G19-G20)</f>
-        <v>75845.4917113568</v>
-      </c>
-      <c r="H21" s="19" t="n">
+        <v>75846.2224081522</v>
+      </c>
+      <c r="H21" s="18" t="n">
         <f aca="false">MAX(0,H17-H19-H20)</f>
-        <v>70665.4852730335</v>
-      </c>
-      <c r="I21" s="19" t="n">
+        <v>70666.4336269187</v>
+      </c>
+      <c r="I21" s="18" t="n">
         <f aca="false">MAX(0,I17-I19-I20)</f>
-        <v>65178.4816343253</v>
-      </c>
-      <c r="J21" s="19" t="n">
+        <v>65179.6626447022</v>
+      </c>
+      <c r="J21" s="18" t="n">
         <f aca="false">MAX(0,J17-J19-J20)</f>
-        <v>59376.6451766709</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="C22" s="19" t="n">
+        <v>59378.0749689945</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="0" t="s">
+        <v>223</v>
+      </c>
+      <c r="C22" s="18" t="n">
         <f aca="false">'Sources &amp; Uses'!F7</f>
         <v>35037.5355</v>
       </c>
-      <c r="D22" s="19" t="n">
+      <c r="D22" s="18" t="n">
         <f aca="false">C26</f>
         <v>35037.5355</v>
       </c>
-      <c r="E22" s="19" t="n">
+      <c r="E22" s="18" t="n">
         <f aca="false">D26</f>
-        <v>35361.8974886719</v>
-      </c>
-      <c r="F22" s="19" t="n">
+        <v>35361.9370394531</v>
+      </c>
+      <c r="F22" s="18" t="n">
         <f aca="false">E26</f>
-        <v>35585.4899591212</v>
-      </c>
-      <c r="G22" s="19" t="n">
+        <v>35585.5752219539</v>
+      </c>
+      <c r="G22" s="18" t="n">
         <f aca="false">F26</f>
-        <v>35740.7196217664</v>
-      </c>
-      <c r="H22" s="19" t="n">
+        <v>35740.8551149188</v>
+      </c>
+      <c r="H22" s="18" t="n">
         <f aca="false">G26</f>
-        <v>35826.654984926</v>
-      </c>
-      <c r="I22" s="19" t="n">
+        <v>35826.8454683278</v>
+      </c>
+      <c r="I22" s="18" t="n">
         <f aca="false">H26</f>
-        <v>35840.0365948929</v>
-      </c>
-      <c r="J22" s="19" t="n">
+        <v>35840.2872070693</v>
+      </c>
+      <c r="J22" s="18" t="n">
         <f aca="false">I26</f>
-        <v>35777.0703530627</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="D23" s="19" t="n">
+        <v>35777.3866477272</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="D23" s="18" t="n">
         <f aca="false">D22*Assumptions!$E$23</f>
         <v>3854.128905</v>
       </c>
-      <c r="E23" s="19" t="n">
+      <c r="E23" s="18" t="n">
         <f aca="false">E22*Assumptions!$E$23</f>
-        <v>3889.80872375391</v>
-      </c>
-      <c r="F23" s="19" t="n">
+        <v>3889.81307433984</v>
+      </c>
+      <c r="F23" s="18" t="n">
         <f aca="false">F22*Assumptions!$E$23</f>
-        <v>3914.40389550333</v>
-      </c>
-      <c r="G23" s="19" t="n">
+        <v>3914.41327441493</v>
+      </c>
+      <c r="G23" s="18" t="n">
         <f aca="false">G22*Assumptions!$E$23</f>
-        <v>3931.4791583943</v>
-      </c>
-      <c r="H23" s="19" t="n">
+        <v>3931.49406264106</v>
+      </c>
+      <c r="H23" s="18" t="n">
         <f aca="false">H22*Assumptions!$E$23</f>
-        <v>3940.93204834186</v>
-      </c>
-      <c r="I23" s="19" t="n">
+        <v>3940.95300151606</v>
+      </c>
+      <c r="I23" s="18" t="n">
         <f aca="false">I22*Assumptions!$E$23</f>
-        <v>3942.40402543822</v>
-      </c>
-      <c r="J23" s="19" t="n">
+        <v>3942.43159277762</v>
+      </c>
+      <c r="J23" s="18" t="n">
         <f aca="false">J22*Assumptions!$E$23</f>
-        <v>3935.47773883689</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30" t="n">
+        <v>3935.51253124999</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29" t="n">
         <f aca="false">D22*Assumptions!$E$24</f>
         <v>1051.126065</v>
       </c>
-      <c r="E24" s="30" t="n">
+      <c r="E24" s="29" t="n">
         <f aca="false">E22*Assumptions!$E$24</f>
-        <v>1060.85692466016</v>
-      </c>
-      <c r="F24" s="30" t="n">
+        <v>1060.85811118359</v>
+      </c>
+      <c r="F24" s="29" t="n">
         <f aca="false">F22*Assumptions!$E$24</f>
-        <v>1067.56469877364</v>
-      </c>
-      <c r="G24" s="30" t="n">
+        <v>1067.56725665862</v>
+      </c>
+      <c r="G24" s="29" t="n">
         <f aca="false">G22*Assumptions!$E$24</f>
-        <v>1072.22158865299</v>
-      </c>
-      <c r="H24" s="30" t="n">
+        <v>1072.22565344756</v>
+      </c>
+      <c r="H24" s="29" t="n">
         <f aca="false">H22*Assumptions!$E$24</f>
-        <v>1074.79964954778</v>
-      </c>
-      <c r="I24" s="30" t="n">
+        <v>1074.80536404983</v>
+      </c>
+      <c r="I24" s="29" t="n">
         <f aca="false">I22*Assumptions!$E$24</f>
-        <v>1075.20109784679</v>
-      </c>
-      <c r="J24" s="30" t="n">
+        <v>1075.20861621208</v>
+      </c>
+      <c r="J24" s="29" t="n">
         <f aca="false">J22*Assumptions!$E$24</f>
-        <v>1073.31211059188</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="29" t="s">
-        <v>224</v>
-      </c>
-      <c r="C25" s="30" t="n">
+        <v>1073.32159943182</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="C25" s="29" t="n">
         <f aca="false">SUM(C16,C20,C13)</f>
         <v>35057.5355</v>
       </c>
-      <c r="D25" s="30" t="n">
+      <c r="D25" s="29" t="n">
         <f aca="false">D12</f>
-        <v>726.764076328124</v>
-      </c>
-      <c r="E25" s="30" t="n">
+        <v>726.724525546874</v>
+      </c>
+      <c r="E25" s="29" t="n">
         <f aca="false">E12</f>
-        <v>837.264454210804</v>
-      </c>
-      <c r="F25" s="30" t="n">
+        <v>837.21992868285</v>
+      </c>
+      <c r="F25" s="29" t="n">
         <f aca="false">F12</f>
-        <v>912.335036128458</v>
-      </c>
-      <c r="G25" s="30" t="n">
+        <v>912.287363693735</v>
+      </c>
+      <c r="G25" s="29" t="n">
         <f aca="false">G12</f>
-        <v>986.28622549343</v>
-      </c>
-      <c r="H25" s="30" t="n">
+        <v>986.23530003849</v>
+      </c>
+      <c r="H25" s="29" t="n">
         <f aca="false">H12</f>
-        <v>1061.41803958082</v>
-      </c>
-      <c r="I25" s="30" t="n">
+        <v>1061.36362530838</v>
+      </c>
+      <c r="I25" s="29" t="n">
         <f aca="false">I12</f>
-        <v>1138.16733967705</v>
-      </c>
-      <c r="J25" s="30" t="n">
+        <v>1138.10917555413</v>
+      </c>
+      <c r="J25" s="29" t="n">
         <f aca="false">J12</f>
-        <v>1216.8755444136</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="29" t="s">
-        <v>225</v>
-      </c>
-      <c r="C26" s="30" t="n">
+        <v>1216.81334892691</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="C26" s="29" t="n">
         <f aca="false">C22</f>
         <v>35037.5355</v>
       </c>
-      <c r="D26" s="30" t="n">
+      <c r="D26" s="29" t="n">
         <f aca="false">MAX(0,D22+D24-D25)</f>
-        <v>35361.8974886719</v>
-      </c>
-      <c r="E26" s="30" t="n">
+        <v>35361.9370394531</v>
+      </c>
+      <c r="E26" s="29" t="n">
         <f aca="false">MAX(0,E22+E24-E25)</f>
-        <v>35585.4899591212</v>
-      </c>
-      <c r="F26" s="30" t="n">
+        <v>35585.5752219539</v>
+      </c>
+      <c r="F26" s="29" t="n">
         <f aca="false">MAX(0,F22+F24-F25)</f>
-        <v>35740.7196217664</v>
-      </c>
-      <c r="G26" s="30" t="n">
+        <v>35740.8551149188</v>
+      </c>
+      <c r="G26" s="29" t="n">
         <f aca="false">MAX(0,G22+G24-G25)</f>
-        <v>35826.654984926</v>
-      </c>
-      <c r="H26" s="30" t="n">
+        <v>35826.8454683278</v>
+      </c>
+      <c r="H26" s="29" t="n">
         <f aca="false">MAX(0,H22+H24-H25)</f>
-        <v>35840.0365948929</v>
-      </c>
-      <c r="I26" s="30" t="n">
+        <v>35840.2872070693</v>
+      </c>
+      <c r="I26" s="29" t="n">
         <f aca="false">MAX(0,I22+I24-I25)</f>
-        <v>35777.0703530627</v>
-      </c>
-      <c r="J26" s="30" t="n">
+        <v>35777.3866477272</v>
+      </c>
+      <c r="J26" s="29" t="n">
         <f aca="false">MAX(0,J22+J24-J25)</f>
-        <v>35633.5069192409</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="C27" s="19" t="n">
+        <v>35633.8948982321</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="0" t="s">
+        <v>228</v>
+      </c>
+      <c r="C27" s="18" t="n">
         <f aca="false">SUM(C16,C21,C26)</f>
         <v>128470.9635</v>
       </c>
-      <c r="D27" s="19" t="n">
+      <c r="D27" s="18" t="n">
         <f aca="false">SUM(D16,D21,D26)</f>
-        <v>124953.934903359</v>
-      </c>
-      <c r="E27" s="19" t="n">
+        <v>124954.132657266</v>
+      </c>
+      <c r="E27" s="18" t="n">
         <f aca="false">SUM(E16,E21,E26)</f>
-        <v>120894.135276966</v>
-      </c>
-      <c r="F27" s="19" t="n">
+        <v>120894.556845035</v>
+      </c>
+      <c r="F27" s="18" t="n">
         <f aca="false">SUM(F16,F21,F26)</f>
-        <v>116465.690515097</v>
-      </c>
-      <c r="G27" s="19" t="n">
+        <v>116466.353003225</v>
+      </c>
+      <c r="G27" s="18" t="n">
         <f aca="false">SUM(G16,G21,G26)</f>
-        <v>111672.146696283</v>
-      </c>
-      <c r="H27" s="19" t="n">
+        <v>111673.06787648</v>
+      </c>
+      <c r="H27" s="18" t="n">
         <f aca="false">SUM(H16,H21,H26)</f>
-        <v>106505.521867926</v>
-      </c>
-      <c r="I27" s="19" t="n">
+        <v>106506.720833988</v>
+      </c>
+      <c r="I27" s="18" t="n">
         <f aca="false">SUM(I16,I21,I26)</f>
-        <v>100955.551987388</v>
-      </c>
-      <c r="J27" s="19" t="n">
+        <v>100957.049292429</v>
+      </c>
+      <c r="J27" s="18" t="n">
         <f aca="false">SUM(J16,J21,J26)</f>
-        <v>95010.1520959118</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="C28" s="19" t="n">
+        <v>95011.9698672266</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="0" t="s">
+        <v>229</v>
+      </c>
+      <c r="C28" s="18" t="n">
         <f aca="false">C27-C13</f>
         <v>128450.9635</v>
       </c>
-      <c r="D28" s="19" t="n">
+      <c r="D28" s="18" t="n">
         <f aca="false">D27-D13</f>
-        <v>124691.68021125</v>
-      </c>
-      <c r="E28" s="19" t="n">
+        <v>124691.89114875</v>
+      </c>
+      <c r="E28" s="18" t="n">
         <f aca="false">E27-E13</f>
-        <v>120595.047125562</v>
-      </c>
-      <c r="F28" s="19" t="n">
+        <v>120595.483535474</v>
+      </c>
+      <c r="F28" s="18" t="n">
         <f aca="false">F27-F13</f>
-        <v>116141.578836387</v>
-      </c>
-      <c r="G28" s="19" t="n">
+        <v>116142.257215327</v>
+      </c>
+      <c r="G28" s="18" t="n">
         <f aca="false">G27-G13</f>
-        <v>111323.384621118</v>
-      </c>
-      <c r="H28" s="19" t="n">
+        <v>111324.322776467</v>
+      </c>
+      <c r="H28" s="18" t="n">
         <f aca="false">H27-H13</f>
-        <v>106131.715854733</v>
-      </c>
-      <c r="I28" s="19" t="n">
+        <v>106132.932958885</v>
+      </c>
+      <c r="I28" s="18" t="n">
         <f aca="false">I27-I13</f>
-        <v>100556.162874162</v>
-      </c>
-      <c r="J28" s="19" t="n">
+        <v>100557.679567245</v>
+      </c>
+      <c r="J28" s="18" t="n">
         <f aca="false">J27-J13</f>
-        <v>94584.5269144406</v>
+        <v>94586.3654175843</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="D29" s="18" t="n">
+        <f aca="false">MAX(0,Assumptions!$E$17-D14)*Assumptions!$E$33</f>
+        <v>0.28125</v>
+      </c>
+      <c r="E29" s="18" t="n">
+        <f aca="false">MAX(0,Assumptions!$E$17-E14)*Assumptions!$E$33</f>
+        <v>0.28125</v>
+      </c>
+      <c r="F29" s="18" t="n">
+        <f aca="false">MAX(0,Assumptions!$E$17-F14)*Assumptions!$E$33</f>
+        <v>0.28125</v>
+      </c>
+      <c r="G29" s="18" t="n">
+        <f aca="false">MAX(0,Assumptions!$E$17-G14)*Assumptions!$E$33</f>
+        <v>0.28125</v>
+      </c>
+      <c r="H29" s="18" t="n">
+        <f aca="false">MAX(0,Assumptions!$E$17-H14)*Assumptions!$E$33</f>
+        <v>0.28125</v>
+      </c>
+      <c r="I29" s="18" t="n">
+        <f aca="false">MAX(0,Assumptions!$E$17-I14)*Assumptions!$E$33</f>
+        <v>0.28125</v>
+      </c>
+      <c r="J29" s="18" t="n">
+        <f aca="false">MAX(0,Assumptions!$E$17-J14)*Assumptions!$E$33</f>
+        <v>0.28125</v>
       </c>
     </row>
   </sheetData>
@@ -6368,342 +6540,342 @@
   <dimension ref="B2:I13"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="E4" s="16" t="s">
+      <c r="B2" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="E4" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="F4" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="G4" s="15" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="C5" s="26" t="n">
+      <c r="H4" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
+        <v>232</v>
+      </c>
+      <c r="C5" s="25" t="n">
         <f aca="false">IFERROR('Debt Schedule'!D25/'Operating Model'!D8,0)</f>
-        <v>0.0310608810191831</v>
-      </c>
-      <c r="D5" s="26" t="n">
+        <v>0.0310591906740619</v>
+      </c>
+      <c r="D5" s="25" t="n">
         <f aca="false">IFERROR('Debt Schedule'!E25/'Operating Model'!E8,0)</f>
-        <v>0.0357586175131289</v>
-      </c>
-      <c r="E5" s="26" t="n">
+        <v>0.0357567158782086</v>
+      </c>
+      <c r="E5" s="25" t="n">
         <f aca="false">IFERROR('Debt Schedule'!F25/'Operating Model'!F8,0)</f>
-        <v>0.0389743613883853</v>
-      </c>
-      <c r="F5" s="26" t="n">
+        <v>0.0389723248528741</v>
+      </c>
+      <c r="F5" s="25" t="n">
         <f aca="false">IFERROR('Debt Schedule'!G25/'Operating Model'!G8,0)</f>
-        <v>0.0421812132080706</v>
-      </c>
-      <c r="G5" s="26" t="n">
+        <v>0.0421790352424689</v>
+      </c>
+      <c r="G5" s="25" t="n">
         <f aca="false">IFERROR('Debt Schedule'!H25/'Operating Model'!H8,0)</f>
-        <v>0.0454838197678832</v>
-      </c>
-      <c r="H5" s="26" t="n">
+        <v>0.0454814880108674</v>
+      </c>
+      <c r="H5" s="25" t="n">
         <f aca="false">IFERROR('Debt Schedule'!I25/'Operating Model'!I8,0)</f>
-        <v>0.048907308477008</v>
-      </c>
-      <c r="I5" s="26" t="n">
+        <v>0.0489048091514672</v>
+      </c>
+      <c r="I5" s="25" t="n">
         <f aca="false">IFERROR('Debt Schedule'!J25/'Operating Model'!J8,0)</f>
-        <v>0.052472929754076</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C6" s="26" t="n">
+        <v>0.0524702478204806</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
+        <v>233</v>
+      </c>
+      <c r="C6" s="25" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
-      <c r="D6" s="26" t="n">
+      <c r="D6" s="25" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
-      <c r="E6" s="26" t="n">
+      <c r="E6" s="25" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
-      <c r="F6" s="26" t="n">
+      <c r="F6" s="25" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
-      <c r="G6" s="26" t="n">
+      <c r="G6" s="25" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
-      <c r="H6" s="26" t="n">
+      <c r="H6" s="25" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
-      <c r="I6" s="26" t="n">
+      <c r="I6" s="25" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C7" s="26" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
+        <v>234</v>
+      </c>
+      <c r="C7" s="25" t="n">
         <f aca="false">C6-C5</f>
-        <v>6.96893911898082</v>
-      </c>
-      <c r="D7" s="26" t="n">
+        <v>6.96894080932594</v>
+      </c>
+      <c r="D7" s="25" t="n">
         <f aca="false">D6-D5</f>
-        <v>6.96424138248687</v>
-      </c>
-      <c r="E7" s="26" t="n">
+        <v>6.96424328412179</v>
+      </c>
+      <c r="E7" s="25" t="n">
         <f aca="false">E6-E5</f>
-        <v>6.96102563861161</v>
-      </c>
-      <c r="F7" s="26" t="n">
+        <v>6.96102767514713</v>
+      </c>
+      <c r="F7" s="25" t="n">
         <f aca="false">F6-F5</f>
-        <v>6.95781878679193</v>
-      </c>
-      <c r="G7" s="26" t="n">
+        <v>6.95782096475753</v>
+      </c>
+      <c r="G7" s="25" t="n">
         <f aca="false">G6-G5</f>
-        <v>6.95451618023212</v>
-      </c>
-      <c r="H7" s="26" t="n">
+        <v>6.95451851198913</v>
+      </c>
+      <c r="H7" s="25" t="n">
         <f aca="false">H6-H5</f>
-        <v>6.95109269152299</v>
-      </c>
-      <c r="I7" s="26" t="n">
+        <v>6.95109519084853</v>
+      </c>
+      <c r="I7" s="25" t="n">
         <f aca="false">I6-I5</f>
-        <v>6.94752707024592</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="C8" s="26" t="n">
+        <v>6.94752975217952</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
+        <v>235</v>
+      </c>
+      <c r="C8" s="25" t="n">
         <f aca="false">IFERROR('Operating Model'!D8/'Debt Schedule'!D7,0)</f>
-        <v>1.98356306218857</v>
-      </c>
-      <c r="D8" s="26" t="n">
+        <v>1.98351576944396</v>
+      </c>
+      <c r="D8" s="25" t="n">
         <f aca="false">IFERROR('Operating Model'!E8/'Debt Schedule'!E7,0)</f>
-        <v>2.03512144994659</v>
-      </c>
-      <c r="E8" s="26" t="n">
+        <v>2.03506855330153</v>
+      </c>
+      <c r="E8" s="25" t="n">
         <f aca="false">IFERROR('Operating Model'!F8/'Debt Schedule'!F7,0)</f>
-        <v>2.09648506468249</v>
-      </c>
-      <c r="F8" s="26" t="n">
+        <v>2.09642512990737</v>
+      </c>
+      <c r="F8" s="25" t="n">
         <f aca="false">IFERROR('Operating Model'!G8/'Debt Schedule'!G7,0)</f>
-        <v>2.16639493906224</v>
-      </c>
-      <c r="G8" s="26" t="n">
+        <v>2.16632650586418</v>
+      </c>
+      <c r="G8" s="25" t="n">
         <f aca="false">IFERROR('Operating Model'!H8/'Debt Schedule'!H7,0)</f>
-        <v>2.24649783033677</v>
-      </c>
-      <c r="H8" s="26" t="n">
+        <v>2.24641904576168</v>
+      </c>
+      <c r="H8" s="25" t="n">
         <f aca="false">IFERROR('Operating Model'!I8/'Debt Schedule'!I7,0)</f>
-        <v>2.3391292679201</v>
-      </c>
-      <c r="I8" s="26" t="n">
+        <v>2.33903771217155</v>
+      </c>
+      <c r="I8" s="25" t="n">
         <f aca="false">IFERROR('Operating Model'!J8/'Debt Schedule'!J7,0)</f>
-        <v>2.44738277868644</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="C9" s="26" t="n">
+        <v>2.4472752277751</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" s="25" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
-      <c r="D9" s="26" t="n">
+      <c r="D9" s="25" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
-      <c r="E9" s="26" t="n">
+      <c r="E9" s="25" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
-      <c r="F9" s="26" t="n">
+      <c r="F9" s="25" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
-      <c r="G9" s="26" t="n">
+      <c r="G9" s="25" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
-      <c r="H9" s="26" t="n">
+      <c r="H9" s="25" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
-      <c r="I9" s="26" t="n">
+      <c r="I9" s="25" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C10" s="26" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="C10" s="25" t="n">
         <f aca="false">C8-C9</f>
-        <v>0.233563062188571</v>
-      </c>
-      <c r="D10" s="26" t="n">
+        <v>0.233515769443958</v>
+      </c>
+      <c r="D10" s="25" t="n">
         <f aca="false">D8-D9</f>
-        <v>0.285121449946588</v>
-      </c>
-      <c r="E10" s="26" t="n">
+        <v>0.285068553301532</v>
+      </c>
+      <c r="E10" s="25" t="n">
         <f aca="false">E8-E9</f>
-        <v>0.34648506468249</v>
-      </c>
-      <c r="F10" s="26" t="n">
+        <v>0.346425129907365</v>
+      </c>
+      <c r="F10" s="25" t="n">
         <f aca="false">F8-F9</f>
-        <v>0.416394939062236</v>
-      </c>
-      <c r="G10" s="26" t="n">
+        <v>0.416326505864177</v>
+      </c>
+      <c r="G10" s="25" t="n">
         <f aca="false">G8-G9</f>
-        <v>0.496497830336767</v>
-      </c>
-      <c r="H10" s="26" t="n">
+        <v>0.496419045761675</v>
+      </c>
+      <c r="H10" s="25" t="n">
         <f aca="false">H8-H9</f>
-        <v>0.589129267920095</v>
-      </c>
-      <c r="I10" s="26" t="n">
+        <v>0.589037712171546</v>
+      </c>
+      <c r="I10" s="25" t="n">
         <f aca="false">I8-I9</f>
-        <v>0.697382778686439</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="s">
+        <v>0.697275227775098</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="0" t="s">
         <v>141</v>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="18" t="n">
         <f aca="false">Assumptions!$E$16</f>
         <v>20</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="18" t="n">
         <f aca="false">Assumptions!$E$16</f>
         <v>20</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="18" t="n">
         <f aca="false">Assumptions!$E$16</f>
         <v>20</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="18" t="n">
         <f aca="false">Assumptions!$E$16</f>
         <v>20</v>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="G11" s="18" t="n">
         <f aca="false">Assumptions!$E$16</f>
         <v>20</v>
       </c>
-      <c r="H11" s="19" t="n">
+      <c r="H11" s="18" t="n">
         <f aca="false">Assumptions!$E$16</f>
         <v>20</v>
       </c>
-      <c r="I11" s="19" t="n">
+      <c r="I11" s="18" t="n">
         <f aca="false">Assumptions!$E$16</f>
         <v>20</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="C12" s="19" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="0" t="s">
+        <v>238</v>
+      </c>
+      <c r="C12" s="18" t="n">
         <f aca="false">'Debt Schedule'!D13-C11</f>
-        <v>242.254692109375</v>
-      </c>
-      <c r="D12" s="19" t="n">
+        <v>242.241508515625</v>
+      </c>
+      <c r="D12" s="18" t="n">
         <f aca="false">'Debt Schedule'!E13-D11</f>
-        <v>279.088151403601</v>
-      </c>
-      <c r="E12" s="19" t="n">
+        <v>279.07330956095</v>
+      </c>
+      <c r="E12" s="18" t="n">
         <f aca="false">'Debt Schedule'!F13-E11</f>
-        <v>304.111678709486</v>
-      </c>
-      <c r="F12" s="19" t="n">
+        <v>304.095787897912</v>
+      </c>
+      <c r="F12" s="18" t="n">
         <f aca="false">'Debt Schedule'!G13-F11</f>
-        <v>328.762075164477</v>
-      </c>
-      <c r="G12" s="19" t="n">
+        <v>328.74510001283</v>
+      </c>
+      <c r="G12" s="18" t="n">
         <f aca="false">'Debt Schedule'!H13-G11</f>
-        <v>353.806013193608</v>
-      </c>
-      <c r="H12" s="19" t="n">
+        <v>353.787875102795</v>
+      </c>
+      <c r="H12" s="18" t="n">
         <f aca="false">'Debt Schedule'!I13-H11</f>
-        <v>379.389113225683</v>
-      </c>
-      <c r="I12" s="19" t="n">
+        <v>379.369725184711</v>
+      </c>
+      <c r="I12" s="18" t="n">
         <f aca="false">'Debt Schedule'!J13-I11</f>
-        <v>405.625181471199</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="1" t="s">
+        <v>405.604449642304</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="1" t="str">
+      <c r="C13" s="0" t="str">
         <f aca="false">IF(AND(C7&gt;=0,C10&gt;=0,C12&gt;=0),"PASS","BREACH")</f>
         <v>PASS</v>
       </c>
-      <c r="D13" s="1" t="str">
+      <c r="D13" s="0" t="str">
         <f aca="false">IF(AND(D7&gt;=0,D10&gt;=0,D12&gt;=0),"PASS","BREACH")</f>
         <v>PASS</v>
       </c>
-      <c r="E13" s="1" t="str">
+      <c r="E13" s="0" t="str">
         <f aca="false">IF(AND(E7&gt;=0,E10&gt;=0,E12&gt;=0),"PASS","BREACH")</f>
         <v>PASS</v>
       </c>
-      <c r="F13" s="1" t="str">
+      <c r="F13" s="0" t="str">
         <f aca="false">IF(AND(F7&gt;=0,F10&gt;=0,F12&gt;=0),"PASS","BREACH")</f>
         <v>PASS</v>
       </c>
-      <c r="G13" s="1" t="str">
+      <c r="G13" s="0" t="str">
         <f aca="false">IF(AND(G7&gt;=0,G10&gt;=0,G12&gt;=0),"PASS","BREACH")</f>
         <v>PASS</v>
       </c>
-      <c r="H13" s="1" t="str">
+      <c r="H13" s="0" t="str">
         <f aca="false">IF(AND(H7&gt;=0,H10&gt;=0,H12&gt;=0),"PASS","BREACH")</f>
         <v>PASS</v>
       </c>
-      <c r="I13" s="1" t="str">
+      <c r="I13" s="0" t="str">
         <f aca="false">IF(AND(I7&gt;=0,I10&gt;=0,I12&gt;=0),"PASS","BREACH")</f>
         <v>PASS</v>
       </c>

--- a/03_Private_Equity/instances/public_home_depot_2023.xlsx
+++ b/03_Private_Equity/instances/public_home_depot_2023.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="322">
   <si>
     <t xml:space="preserve">[TARGET] — LBO Underwriting Model</t>
   </si>
@@ -941,6 +941,30 @@
     <t xml:space="preserve">U.S. SEC; frozen curated observation as of case date</t>
   </si>
   <si>
+    <t xml:space="preserve">Home Depot Q4 &amp; FY2023 Earnings Call Transcript (2024-02-20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.alphavantage.co/documentation/#earnings-call-transcripts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Management-disclosed FY2023 operating margin (~14.2%), gross margin (~33.4%), opex/sales (~19.2%), and effective tax rate (24%), retrieved via Alpha Vantage EARNINGS_CALL_TRANSCRIPT (symbol=HD, quarter=2023Q4). Call predates the case as_of date of 2024-03-13.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home Depot FY2023 Cash Flow Statement (Alpha Vantage, SEC-derived)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.alphavantage.co/documentation/#cash-flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">depreciationDepletionAndAmortization=$3,247mm, capitalExpenditures=$3,226mm for fiscalDateEnding 2024-01-31 (Home Depot FY2023, ended 2024-01-28). Retrieved via Alpha Vantage CASH_FLOW (symbol=HD).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Frozen source snapshot</t>
   </si>
   <si>
@@ -968,13 +992,13 @@
     <t xml:space="preserve">Next check</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">External historical evidence materialization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generated public case pe-public-home-depot-2023 from canonical release template</t>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real judgment-density deepening from earnings call + cash-flow cross-check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added real, sourced overrides for EBITDA margin (corrected), D&amp;A/revenue, capex/revenue, and cash tax rate from Home Depot's FY2023 earnings call and SEC-derived cash-flow data; replaced the trailing revenue-growth actual with management's own FY2024 guidance for the model's forward growth mechanic.</t>
   </si>
   <si>
     <t xml:space="preserve">External historical case; human stakeholder approval remains pending</t>
@@ -1816,7 +1840,7 @@
       </c>
       <c r="C7" s="18" t="n">
         <f aca="false">'Sources &amp; Uses'!F8</f>
-        <v>109904.2779</v>
+        <v>117079.7209</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>127</v>
@@ -1831,7 +1855,7 @@
       </c>
       <c r="C8" s="18" t="n">
         <f aca="false">C7*(1+Assumptions!E31)^Assumptions!E29</f>
-        <v>161485.4412789</v>
+        <v>172028.521142278</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>127</v>
@@ -1930,35 +1954,35 @@
       </c>
       <c r="C5" s="18" t="n">
         <f aca="false">'Operating Model'!D8</f>
-        <v>23398.05094</v>
+        <v>25904.87592</v>
       </c>
       <c r="D5" s="18" t="n">
         <f aca="false">'Operating Model'!E8</f>
-        <v>23414.3407223</v>
+        <v>26942.6129137</v>
       </c>
       <c r="E5" s="18" t="n">
         <f aca="false">'Operating Model'!F8</f>
-        <v>23408.594871816</v>
+        <v>27998.514159682</v>
       </c>
       <c r="F5" s="18" t="n">
         <f aca="false">'Operating Model'!G8</f>
-        <v>23382.120865711</v>
+        <v>29072.8391692923</v>
       </c>
       <c r="G5" s="18" t="n">
         <f aca="false">'Operating Model'!H8</f>
-        <v>23336.1675645876</v>
+        <v>30165.8508276788</v>
       </c>
       <c r="H5" s="18" t="n">
         <f aca="false">'Operating Model'!I8</f>
-        <v>23271.9275527525</v>
+        <v>31277.8154353161</v>
       </c>
       <c r="I5" s="18" t="n">
         <f aca="false">'Operating Model'!J8</f>
-        <v>23190.5393908194</v>
+        <v>32409.0027500234</v>
       </c>
       <c r="J5" s="18" t="n">
         <f aca="false">INDEX(C5:I5,1,Assumptions!E29)</f>
-        <v>23336.1675645876</v>
+        <v>30165.8508276788</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2004,35 +2028,35 @@
       </c>
       <c r="C7" s="18" t="n">
         <f aca="false">C5*C6</f>
-        <v>233980.5094</v>
+        <v>259048.7592</v>
       </c>
       <c r="D7" s="18" t="n">
         <f aca="false">D5*D6</f>
-        <v>234143.407223</v>
+        <v>269426.129137</v>
       </c>
       <c r="E7" s="18" t="n">
         <f aca="false">E5*E6</f>
-        <v>234085.94871816</v>
+        <v>279985.14159682</v>
       </c>
       <c r="F7" s="18" t="n">
         <f aca="false">F5*F6</f>
-        <v>233821.20865711</v>
+        <v>290728.391692923</v>
       </c>
       <c r="G7" s="18" t="n">
         <f aca="false">G5*G6</f>
-        <v>233361.675645876</v>
+        <v>301658.508276788</v>
       </c>
       <c r="H7" s="18" t="n">
         <f aca="false">H5*H6</f>
-        <v>232719.275527525</v>
+        <v>312778.154353161</v>
       </c>
       <c r="I7" s="18" t="n">
         <f aca="false">I5*I6</f>
-        <v>231905.393908194</v>
+        <v>324090.027500234</v>
       </c>
       <c r="J7" s="18" t="n">
         <f aca="false">INDEX(C7:I7,1,Assumptions!E29)</f>
-        <v>233361.675645876</v>
+        <v>301658.508276788</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2041,35 +2065,35 @@
       </c>
       <c r="C8" s="18" t="n">
         <f aca="false">'Debt Schedule'!D28</f>
-        <v>124691.89114875</v>
+        <v>130418.39059612</v>
       </c>
       <c r="D8" s="18" t="n">
         <f aca="false">'Debt Schedule'!E28</f>
-        <v>120595.483535474</v>
+        <v>122831.999063324</v>
       </c>
       <c r="E8" s="18" t="n">
         <f aca="false">'Debt Schedule'!F28</f>
-        <v>116142.257215327</v>
+        <v>113965.621569917</v>
       </c>
       <c r="F8" s="18" t="n">
         <f aca="false">'Debt Schedule'!G28</f>
-        <v>111324.322776467</v>
+        <v>103708.889750267</v>
       </c>
       <c r="G8" s="18" t="n">
         <f aca="false">'Debt Schedule'!H28</f>
-        <v>106132.932958885</v>
+        <v>91944.0494702345</v>
       </c>
       <c r="H8" s="18" t="n">
         <f aca="false">'Debt Schedule'!I28</f>
-        <v>100557.679567245</v>
+        <v>78544.1557454496</v>
       </c>
       <c r="I8" s="18" t="n">
         <f aca="false">'Debt Schedule'!J28</f>
-        <v>94586.3654175843</v>
+        <v>63372.2818974546</v>
       </c>
       <c r="J8" s="18" t="n">
         <f aca="false">INDEX(C8:I8,1,Assumptions!E29)</f>
-        <v>106132.932958885</v>
+        <v>91944.0494702345</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2078,35 +2102,35 @@
       </c>
       <c r="C9" s="18" t="n">
         <f aca="false">MAX(0,C7-C8)</f>
-        <v>109288.61825125</v>
+        <v>128630.36860388</v>
       </c>
       <c r="D9" s="18" t="n">
         <f aca="false">MAX(0,D7-D8)</f>
-        <v>113547.923687526</v>
+        <v>146594.130073676</v>
       </c>
       <c r="E9" s="18" t="n">
         <f aca="false">MAX(0,E7-E8)</f>
-        <v>117943.691502833</v>
+        <v>166019.520026903</v>
       </c>
       <c r="F9" s="18" t="n">
         <f aca="false">MAX(0,F7-F8)</f>
-        <v>122496.885880643</v>
+        <v>187019.501942656</v>
       </c>
       <c r="G9" s="18" t="n">
         <f aca="false">MAX(0,G7-G8)</f>
-        <v>127228.742686991</v>
+        <v>209714.458806553</v>
       </c>
       <c r="H9" s="18" t="n">
         <f aca="false">MAX(0,H7-H8)</f>
-        <v>132161.59596028</v>
+        <v>234233.998607711</v>
       </c>
       <c r="I9" s="18" t="n">
         <f aca="false">MAX(0,I7-I8)</f>
-        <v>137319.02849061</v>
+        <v>260717.745602779</v>
       </c>
       <c r="J9" s="18" t="n">
         <f aca="false">INDEX(C9:I9,1,Assumptions!E29)</f>
-        <v>127228.742686991</v>
+        <v>209714.458806553</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2115,35 +2139,35 @@
       </c>
       <c r="C10" s="18" t="n">
         <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^1</f>
-        <v>118696.620132</v>
+        <v>126446.098572</v>
       </c>
       <c r="D10" s="18" t="n">
         <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^2</f>
-        <v>128192.34974256</v>
+        <v>136561.78645776</v>
       </c>
       <c r="E10" s="18" t="n">
         <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^3</f>
-        <v>138447.737721965</v>
+        <v>147486.729374381</v>
       </c>
       <c r="F10" s="18" t="n">
         <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^4</f>
-        <v>149523.556739722</v>
+        <v>159285.667724331</v>
       </c>
       <c r="G10" s="18" t="n">
         <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^5</f>
-        <v>161485.4412789</v>
+        <v>172028.521142278</v>
       </c>
       <c r="H10" s="18" t="n">
         <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^6</f>
-        <v>174404.276581212</v>
+        <v>185790.80283366</v>
       </c>
       <c r="I10" s="18" t="n">
         <f aca="false">'Management Equity'!$C$7*(1+Assumptions!$E$31)^7</f>
-        <v>188356.618707709</v>
+        <v>200654.067060353</v>
       </c>
       <c r="J10" s="18" t="n">
         <f aca="false">INDEX(C10:I10,1,Assumptions!E29)</f>
-        <v>161485.4412789</v>
+        <v>172028.521142278</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2152,35 +2176,35 @@
       </c>
       <c r="C11" s="18" t="n">
         <f aca="false">MAX(0,C9-C10)</f>
-        <v>0</v>
+        <v>2184.27003187996</v>
       </c>
       <c r="D11" s="18" t="n">
         <f aca="false">MAX(0,D9-D10)</f>
-        <v>0</v>
+        <v>10032.3436159156</v>
       </c>
       <c r="E11" s="18" t="n">
         <f aca="false">MAX(0,E9-E10)</f>
-        <v>0</v>
+        <v>18532.7906525221</v>
       </c>
       <c r="F11" s="18" t="n">
         <f aca="false">MAX(0,F9-F10)</f>
-        <v>0</v>
+        <v>27733.8342183242</v>
       </c>
       <c r="G11" s="18" t="n">
         <f aca="false">MAX(0,G9-G10)</f>
-        <v>0</v>
+        <v>37685.9376642754</v>
       </c>
       <c r="H11" s="18" t="n">
         <f aca="false">MAX(0,H9-H10)</f>
-        <v>0</v>
+        <v>48443.1957740512</v>
       </c>
       <c r="I11" s="18" t="n">
         <f aca="false">MAX(0,I9-I10)</f>
-        <v>0</v>
+        <v>60063.6785424262</v>
       </c>
       <c r="J11" s="18" t="n">
         <f aca="false">INDEX(C11:I11,1,Assumptions!E29)</f>
-        <v>0</v>
+        <v>37685.9376642754</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2189,35 +2213,35 @@
       </c>
       <c r="C12" s="18" t="n">
         <f aca="false">MIN(C9,C9*Assumptions!$E$30+C11*Assumptions!$E$32)</f>
-        <v>10928.861825125</v>
+        <v>13299.890866764</v>
       </c>
       <c r="D12" s="18" t="n">
         <f aca="false">MIN(D9,D9*Assumptions!$E$30+D11*Assumptions!$E$32)</f>
-        <v>11354.7923687526</v>
+        <v>16665.8817305507</v>
       </c>
       <c r="E12" s="18" t="n">
         <f aca="false">MIN(E9,E9*Assumptions!$E$30+E11*Assumptions!$E$32)</f>
-        <v>11794.3691502833</v>
+        <v>20308.5101331947</v>
       </c>
       <c r="F12" s="18" t="n">
         <f aca="false">MIN(F9,F9*Assumptions!$E$30+F11*Assumptions!$E$32)</f>
-        <v>12249.6885880643</v>
+        <v>24248.7170379304</v>
       </c>
       <c r="G12" s="18" t="n">
         <f aca="false">MIN(G9,G9*Assumptions!$E$30+G11*Assumptions!$E$32)</f>
-        <v>12722.8742686991</v>
+        <v>28508.6334135104</v>
       </c>
       <c r="H12" s="18" t="n">
         <f aca="false">MIN(H9,H9*Assumptions!$E$30+H11*Assumptions!$E$32)</f>
-        <v>13216.159596028</v>
+        <v>33112.0390155814</v>
       </c>
       <c r="I12" s="18" t="n">
         <f aca="false">MIN(I9,I9*Assumptions!$E$30+I11*Assumptions!$E$32)</f>
-        <v>13731.9028490609</v>
+        <v>38084.5102687632</v>
       </c>
       <c r="J12" s="18" t="n">
         <f aca="false">INDEX(C12:I12,1,Assumptions!E29)</f>
-        <v>12722.8742686991</v>
+        <v>28508.6334135104</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2226,35 +2250,35 @@
       </c>
       <c r="C13" s="18" t="n">
         <f aca="false">MAX(0,C9-C12)</f>
-        <v>98359.756426125</v>
+        <v>115330.477737116</v>
       </c>
       <c r="D13" s="18" t="n">
         <f aca="false">MAX(0,D9-D12)</f>
-        <v>102193.131318773</v>
+        <v>129928.248343125</v>
       </c>
       <c r="E13" s="18" t="n">
         <f aca="false">MAX(0,E9-E12)</f>
-        <v>106149.32235255</v>
+        <v>145711.009893708</v>
       </c>
       <c r="F13" s="18" t="n">
         <f aca="false">MAX(0,F9-F12)</f>
-        <v>110247.197292578</v>
+        <v>162770.784904725</v>
       </c>
       <c r="G13" s="18" t="n">
         <f aca="false">MAX(0,G9-G12)</f>
-        <v>114505.868418292</v>
+        <v>181205.825393043</v>
       </c>
       <c r="H13" s="18" t="n">
         <f aca="false">MAX(0,H9-H12)</f>
-        <v>118945.436364252</v>
+        <v>201121.95959213</v>
       </c>
       <c r="I13" s="18" t="n">
         <f aca="false">MAX(0,I9-I12)</f>
-        <v>123587.125641549</v>
+        <v>222633.235334016</v>
       </c>
       <c r="J13" s="18" t="n">
         <f aca="false">INDEX(C13:I13,1,Assumptions!E29)</f>
-        <v>114505.868418292</v>
+        <v>181205.825393043</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2263,35 +2287,35 @@
       </c>
       <c r="C14" s="25" t="n">
         <f aca="false">IFERROR(C13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>0.894958397484953</v>
+        <v>0.985059383901521</v>
       </c>
       <c r="D14" s="25" t="n">
         <f aca="false">IFERROR(D13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>0.929837612069633</v>
+        <v>1.10974169859953</v>
       </c>
       <c r="E14" s="25" t="n">
         <f aca="false">IFERROR(E13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>0.965834309462759</v>
+        <v>1.24454524467275</v>
       </c>
       <c r="F14" s="25" t="n">
         <f aca="false">IFERROR(F13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>1.00312016419316</v>
+        <v>1.39025600380232</v>
       </c>
       <c r="G14" s="25" t="n">
         <f aca="false">IFERROR(G13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>1.04186907558302</v>
+        <v>1.54771316501356</v>
       </c>
       <c r="H14" s="25" t="n">
         <f aca="false">IFERROR(H13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>1.08226393582676</v>
+        <v>1.71782062722811</v>
       </c>
       <c r="I14" s="25" t="n">
         <f aca="false">IFERROR(I13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>1.1244978630768</v>
+        <v>1.90155249451074</v>
       </c>
       <c r="J14" s="25" t="n">
         <f aca="false">INDEX(C14:I14,1,Assumptions!E29)</f>
-        <v>1.04186907558302</v>
+        <v>1.54771316501356</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2300,35 +2324,35 @@
       </c>
       <c r="C15" s="23" t="n">
         <f aca="false">IFERROR((C13/'Sources &amp; Uses'!$F$8)^(1/1)-1,0)</f>
-        <v>-0.105041602515047</v>
+        <v>-0.0149406160984794</v>
       </c>
       <c r="D15" s="23" t="n">
         <f aca="false">IFERROR((D13/'Sources &amp; Uses'!$F$8)^(1/2)-1,0)</f>
-        <v>-0.0357191217961267</v>
+        <v>0.053442783733189</v>
       </c>
       <c r="E15" s="23" t="n">
         <f aca="false">IFERROR((E13/'Sources &amp; Uses'!$F$8)^(1/3)-1,0)</f>
-        <v>-0.0115207822237074</v>
+        <v>0.0756481383470085</v>
       </c>
       <c r="F15" s="23" t="n">
         <f aca="false">IFERROR((F13/'Sources &amp; Uses'!$F$8)^(1/4)-1,0)</f>
-        <v>0.000779130009872731</v>
+        <v>0.0858596488737349</v>
       </c>
       <c r="G15" s="23" t="n">
         <f aca="false">IFERROR((G13/'Sources &amp; Uses'!$F$8)^(1/5)-1,0)</f>
-        <v>0.00823699655192778</v>
+        <v>0.0912847728470427</v>
       </c>
       <c r="H15" s="23" t="n">
         <f aca="false">IFERROR((H13/'Sources &amp; Uses'!$F$8)^(1/6)-1,0)</f>
-        <v>0.0132630312921269</v>
+        <v>0.0943669501469977</v>
       </c>
       <c r="I15" s="23" t="n">
         <f aca="false">IFERROR((I13/'Sources &amp; Uses'!$F$8)^(1/7)-1,0)</f>
-        <v>0.0169036471007922</v>
+        <v>0.0961566351060408</v>
       </c>
       <c r="J15" s="23" t="n">
         <f aca="false">INDEX(C15:I15,1,Assumptions!E29)</f>
-        <v>0.00823699655192778</v>
+        <v>0.0912847728470427</v>
       </c>
     </row>
   </sheetData>
@@ -2394,23 +2418,23 @@
       </c>
       <c r="C5" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.058173241584372</v>
+        <v>0.0751672306112294</v>
       </c>
       <c r="D5" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0142759798225731</v>
+        <v>0.129712830399603</v>
       </c>
       <c r="E5" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0704999543073663</v>
+        <v>0.175392874914771</v>
       </c>
       <c r="F5" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.116916573220379</v>
+        <v>0.214909698678224</v>
       </c>
       <c r="G5" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.156696019315141</v>
+        <v>0.24986760752772</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2419,23 +2443,23 @@
       </c>
       <c r="C6" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.115601439871313</v>
+        <v>0.0096022027661522</v>
       </c>
       <c r="D6" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0475698337163406</v>
+        <v>0.060821544399394</v>
       </c>
       <c r="E6" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.00522586531721747</v>
+        <v>0.103715963287841</v>
       </c>
       <c r="F6" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0488122155306767</v>
+        <v>0.140823002250723</v>
       </c>
       <c r="G6" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.086166096735014</v>
+        <v>0.173649134571073</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2444,23 +2468,23 @@
       </c>
       <c r="C7" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.156870222131174</v>
+        <v>-0.0375124505656633</v>
       </c>
       <c r="D7" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0920131819103536</v>
+        <v>0.0113166610162549</v>
       </c>
       <c r="E7" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0416810940877364</v>
+        <v>0.0522093452905523</v>
       </c>
       <c r="F7" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.000128618280630266</v>
+        <v>0.087584726703444</v>
       </c>
       <c r="G7" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0354822148688141</v>
+        <v>0.118878976624706</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2469,23 +2493,23 @@
       </c>
       <c r="C8" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.188748209504652</v>
+        <v>-0.0739054240051155</v>
       </c>
       <c r="D8" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.126343356317798</v>
+        <v>-0.0269226080577923</v>
       </c>
       <c r="E8" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0779142799914012</v>
+        <v>0.0124238677761599</v>
       </c>
       <c r="F8" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0379328663551319</v>
+        <v>0.0464616575319683</v>
       </c>
       <c r="G8" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.00366844714965531</v>
+        <v>0.076572628971487</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2494,23 +2518,23 @@
       </c>
       <c r="C9" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.214534067321629</v>
+        <v>-0.103343068452723</v>
       </c>
       <c r="D9" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.154112769290176</v>
+        <v>-0.0578536889932648</v>
       </c>
       <c r="E9" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.107223024267563</v>
+        <v>-0.0197579143251433</v>
       </c>
       <c r="F9" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.068512430689166</v>
+        <v>0.0131979207593107</v>
       </c>
       <c r="G9" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0353371153256351</v>
+        <v>0.042351758776191</v>
       </c>
     </row>
   </sheetData>
@@ -2680,7 +2704,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:E11"/>
+  <dimension ref="B2:E13"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -2804,10 +2828,38 @@
         <v>301</v>
       </c>
       <c r="D11" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="32" t="s">
+        <v>304</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>305</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="32" t="s">
+        <v>308</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>309</v>
+      </c>
+      <c r="D13" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="32" t="s">
-        <v>302</v>
+      <c r="E13" s="32" t="s">
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -2843,7 +2895,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -2856,39 +2908,39 @@
         <v>94</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="33" t="s">
+        <v>317</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>318</v>
+      </c>
+      <c r="D5" s="33" t="s">
         <v>309</v>
       </c>
-      <c r="C5" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>301</v>
-      </c>
       <c r="E5" s="33" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="G5" s="33" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4343,14 +4395,14 @@
         <v>128</v>
       </c>
       <c r="C6" s="19" t="n">
-        <v>0.153</v>
+        <v>0.163</v>
       </c>
       <c r="D6" s="20" t="n">
         <v>0.17</v>
       </c>
       <c r="E6" s="21" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D6,C6)</f>
-        <v>0.153</v>
+        <v>0.163</v>
       </c>
       <c r="F6" s="14" t="s">
         <v>129</v>
@@ -4361,14 +4413,14 @@
         <v>130</v>
       </c>
       <c r="C7" s="19" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="D7" s="20" t="n">
         <v>-0.02</v>
       </c>
       <c r="E7" s="21" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D7,C7)</f>
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="F7" s="14" t="s">
         <v>129</v>
@@ -4396,15 +4448,15 @@
       <c r="B9" s="0" t="s">
         <v>133</v>
       </c>
-      <c r="C9" s="20" t="n">
-        <v>0.025</v>
+      <c r="C9" s="19" t="n">
+        <v>0.0213</v>
       </c>
       <c r="D9" s="20" t="n">
         <v>0.025</v>
       </c>
       <c r="E9" s="21" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D9,C9)</f>
-        <v>0.025</v>
+        <v>0.0213</v>
       </c>
       <c r="F9" s="14" t="s">
         <v>129</v>
@@ -4414,15 +4466,15 @@
       <c r="B10" s="0" t="s">
         <v>134</v>
       </c>
-      <c r="C10" s="20" t="n">
-        <v>0.035</v>
+      <c r="C10" s="19" t="n">
+        <v>0.0211</v>
       </c>
       <c r="D10" s="20" t="n">
         <v>0.045</v>
       </c>
       <c r="E10" s="21" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D10,C10)</f>
-        <v>0.035</v>
+        <v>0.0211</v>
       </c>
       <c r="F10" s="14" t="s">
         <v>129</v>
@@ -4450,15 +4502,15 @@
       <c r="B12" s="0" t="s">
         <v>136</v>
       </c>
-      <c r="C12" s="20" t="n">
-        <v>0.25</v>
+      <c r="C12" s="19" t="n">
+        <v>0.24</v>
       </c>
       <c r="D12" s="20" t="n">
         <v>0.2</v>
       </c>
       <c r="E12" s="21" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D12,C12)</f>
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="F12" s="14" t="s">
         <v>129</v>
@@ -4905,7 +4957,7 @@
       </c>
       <c r="C5" s="18" t="n">
         <f aca="false">Assumptions!E5*Assumptions!E6*Assumptions!E13</f>
-        <v>233583.57</v>
+        <v>248850.47</v>
       </c>
       <c r="E5" s="14" t="s">
         <v>171</v>
@@ -4927,7 +4979,7 @@
       </c>
       <c r="F6" s="18" t="n">
         <f aca="false">Assumptions!E5*Assumptions!E6*Assumptions!E19</f>
-        <v>93433.428</v>
+        <v>99540.188</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4936,14 +4988,14 @@
       </c>
       <c r="C7" s="18" t="n">
         <f aca="false">C5*Assumptions!E14</f>
-        <v>4671.6714</v>
+        <v>4977.0094</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>175</v>
       </c>
       <c r="F7" s="18" t="n">
         <f aca="false">Assumptions!E5*Assumptions!E6*Assumptions!E22</f>
-        <v>35037.5355</v>
+        <v>37327.5705</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4959,7 +5011,7 @@
       </c>
       <c r="F8" s="18" t="n">
         <f aca="false">C9-SUM(F5:F7)</f>
-        <v>109904.2779</v>
+        <v>117079.7209</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4968,14 +5020,14 @@
       </c>
       <c r="C9" s="29" t="n">
         <f aca="false">SUM(C5:C8)</f>
-        <v>238375.2414</v>
+        <v>253947.4794</v>
       </c>
       <c r="E9" s="28" t="s">
         <v>179</v>
       </c>
       <c r="F9" s="29" t="n">
         <f aca="false">SUM(F5:F8)</f>
-        <v>238375.2414</v>
+        <v>253947.4794</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5065,31 +5117,31 @@
       </c>
       <c r="D5" s="18" t="n">
         <f aca="false">C5*(1+Assumptions!$E$7)</f>
-        <v>148088.93</v>
+        <v>154195.69</v>
       </c>
       <c r="E5" s="18" t="n">
         <f aca="false">D5*(1+Assumptions!$E$7)</f>
-        <v>143646.2621</v>
+        <v>155737.6469</v>
       </c>
       <c r="F5" s="18" t="n">
         <f aca="false">E5*(1+Assumptions!$E$7)</f>
-        <v>139336.874237</v>
+        <v>157295.023369</v>
       </c>
       <c r="G5" s="18" t="n">
         <f aca="false">F5*(1+Assumptions!$E$7)</f>
-        <v>135156.76800989</v>
+        <v>158867.97360269</v>
       </c>
       <c r="H5" s="18" t="n">
         <f aca="false">G5*(1+Assumptions!$E$7)</f>
-        <v>131102.064969593</v>
+        <v>160456.653338717</v>
       </c>
       <c r="I5" s="18" t="n">
         <f aca="false">H5*(1+Assumptions!$E$7)</f>
-        <v>127169.003020505</v>
+        <v>162061.219872104</v>
       </c>
       <c r="J5" s="18" t="n">
         <f aca="false">I5*(1+Assumptions!$E$7)</f>
-        <v>123353.93292989</v>
+        <v>163681.832070825</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5098,31 +5150,31 @@
       </c>
       <c r="D6" s="21" t="n">
         <f aca="false">IFERROR(D5/C5-1,0)</f>
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E6" s="21" t="n">
         <f aca="false">IFERROR(E5/D5-1,0)</f>
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="F6" s="21" t="n">
         <f aca="false">IFERROR(F5/E5-1,0)</f>
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="G6" s="21" t="n">
         <f aca="false">IFERROR(G5/F5-1,0)</f>
-        <v>-0.0299999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="H6" s="21" t="n">
         <f aca="false">IFERROR(H5/G5-1,0)</f>
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="I6" s="21" t="n">
         <f aca="false">IFERROR(I5/H5-1,0)</f>
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="J6" s="21" t="n">
         <f aca="false">IFERROR(J5/I5-1,0)</f>
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5131,35 +5183,35 @@
       </c>
       <c r="C7" s="21" t="n">
         <f aca="false">Assumptions!E6</f>
-        <v>0.153</v>
+        <v>0.163</v>
       </c>
       <c r="D7" s="21" t="n">
         <f aca="false">MAX(0,MIN(0.6,C7+Assumptions!$E$8))</f>
-        <v>0.158</v>
+        <v>0.168</v>
       </c>
       <c r="E7" s="21" t="n">
         <f aca="false">MAX(0,MIN(0.6,D7+Assumptions!$E$8))</f>
-        <v>0.163</v>
+        <v>0.173</v>
       </c>
       <c r="F7" s="21" t="n">
         <f aca="false">MAX(0,MIN(0.6,E7+Assumptions!$E$8))</f>
-        <v>0.168</v>
+        <v>0.178</v>
       </c>
       <c r="G7" s="21" t="n">
         <f aca="false">MAX(0,MIN(0.6,F7+Assumptions!$E$8))</f>
-        <v>0.173</v>
+        <v>0.183</v>
       </c>
       <c r="H7" s="21" t="n">
         <f aca="false">MAX(0,MIN(0.6,G7+Assumptions!$E$8))</f>
-        <v>0.178</v>
+        <v>0.188</v>
       </c>
       <c r="I7" s="21" t="n">
         <f aca="false">MAX(0,MIN(0.6,H7+Assumptions!$E$8))</f>
-        <v>0.183</v>
+        <v>0.193</v>
       </c>
       <c r="J7" s="21" t="n">
         <f aca="false">MAX(0,MIN(0.6,I7+Assumptions!$E$8))</f>
-        <v>0.188</v>
+        <v>0.198</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5168,35 +5220,35 @@
       </c>
       <c r="C8" s="29" t="n">
         <f aca="false">C5*C7</f>
-        <v>23358.357</v>
+        <v>24885.047</v>
       </c>
       <c r="D8" s="29" t="n">
         <f aca="false">D5*D7</f>
-        <v>23398.05094</v>
+        <v>25904.87592</v>
       </c>
       <c r="E8" s="29" t="n">
         <f aca="false">E5*E7</f>
-        <v>23414.3407223</v>
+        <v>26942.6129137</v>
       </c>
       <c r="F8" s="29" t="n">
         <f aca="false">F5*F7</f>
-        <v>23408.594871816</v>
+        <v>27998.514159682</v>
       </c>
       <c r="G8" s="29" t="n">
         <f aca="false">G5*G7</f>
-        <v>23382.120865711</v>
+        <v>29072.8391692923</v>
       </c>
       <c r="H8" s="29" t="n">
         <f aca="false">H5*H7</f>
-        <v>23336.1675645876</v>
+        <v>30165.8508276788</v>
       </c>
       <c r="I8" s="29" t="n">
         <f aca="false">I5*I7</f>
-        <v>23271.9275527525</v>
+        <v>31277.8154353161</v>
       </c>
       <c r="J8" s="29" t="n">
         <f aca="false">J5*J7</f>
-        <v>23190.5393908194</v>
+        <v>32409.0027500234</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5205,35 +5257,35 @@
       </c>
       <c r="C9" s="18" t="n">
         <f aca="false">C5*Assumptions!E9</f>
-        <v>3816.725</v>
+        <v>3251.8497</v>
       </c>
       <c r="D9" s="18" t="n">
         <f aca="false">D5*Assumptions!$E$9</f>
-        <v>3702.22325</v>
+        <v>3284.368197</v>
       </c>
       <c r="E9" s="18" t="n">
         <f aca="false">E5*Assumptions!$E$9</f>
-        <v>3591.1565525</v>
+        <v>3317.21187897</v>
       </c>
       <c r="F9" s="18" t="n">
         <f aca="false">F5*Assumptions!$E$9</f>
-        <v>3483.421855925</v>
+        <v>3350.3839977597</v>
       </c>
       <c r="G9" s="18" t="n">
         <f aca="false">G5*Assumptions!$E$9</f>
-        <v>3378.91920024725</v>
+        <v>3383.8878377373</v>
       </c>
       <c r="H9" s="18" t="n">
         <f aca="false">H5*Assumptions!$E$9</f>
-        <v>3277.55162423983</v>
+        <v>3417.72671611467</v>
       </c>
       <c r="I9" s="18" t="n">
         <f aca="false">I5*Assumptions!$E$9</f>
-        <v>3179.22507551264</v>
+        <v>3451.90398327582</v>
       </c>
       <c r="J9" s="18" t="n">
         <f aca="false">J5*Assumptions!$E$9</f>
-        <v>3083.84832324726</v>
+        <v>3486.42302310858</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5242,35 +5294,35 @@
       </c>
       <c r="C10" s="18" t="n">
         <f aca="false">C8-C9</f>
-        <v>19541.632</v>
+        <v>21633.1973</v>
       </c>
       <c r="D10" s="18" t="n">
         <f aca="false">D8-D9</f>
-        <v>19695.82769</v>
+        <v>22620.507723</v>
       </c>
       <c r="E10" s="18" t="n">
         <f aca="false">E8-E9</f>
-        <v>19823.1841698</v>
+        <v>23625.40103473</v>
       </c>
       <c r="F10" s="18" t="n">
         <f aca="false">F8-F9</f>
-        <v>19925.173015891</v>
+        <v>24648.1301619223</v>
       </c>
       <c r="G10" s="18" t="n">
         <f aca="false">G8-G9</f>
-        <v>20003.2016654637</v>
+        <v>25688.951331555</v>
       </c>
       <c r="H10" s="18" t="n">
         <f aca="false">H8-H9</f>
-        <v>20058.6159403478</v>
+        <v>26748.1241115641</v>
       </c>
       <c r="I10" s="18" t="n">
         <f aca="false">I8-I9</f>
-        <v>20092.7024772399</v>
+        <v>27825.9114520403</v>
       </c>
       <c r="J10" s="18" t="n">
         <f aca="false">J8-J9</f>
-        <v>20106.6910675721</v>
+        <v>28922.5797269148</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5279,31 +5331,31 @@
       </c>
       <c r="D11" s="18" t="n">
         <f aca="false">'Debt Schedule'!D7</f>
-        <v>11796.251535</v>
+        <v>12567.229985</v>
       </c>
       <c r="E11" s="18" t="n">
         <f aca="false">'Debt Schedule'!E7</f>
-        <v>11505.4309518539</v>
+        <v>12052.825511757</v>
       </c>
       <c r="F11" s="18" t="n">
         <f aca="false">'Debt Schedule'!F7</f>
-        <v>11165.9579623768</v>
+        <v>11406.1523505739</v>
       </c>
       <c r="G11" s="18" t="n">
         <f aca="false">'Debt Schedule'!G7</f>
-        <v>10793.4426331471</v>
+        <v>10642.924404858</v>
       </c>
       <c r="H11" s="18" t="n">
         <f aca="false">'Debt Schedule'!H7</f>
-        <v>10388.163156209</v>
+        <v>9754.6664167885</v>
       </c>
       <c r="I11" s="18" t="n">
         <f aca="false">'Debt Schedule'!I7</f>
-        <v>9949.35970106571</v>
+        <v>8730.74316327125</v>
       </c>
       <c r="J11" s="18" t="n">
         <f aca="false">'Debt Schedule'!J7</f>
-        <v>9476.06510604968</v>
+        <v>7559.59080772125</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5312,31 +5364,31 @@
       </c>
       <c r="D12" s="18" t="n">
         <f aca="false">D10-D11</f>
-        <v>7899.576155</v>
+        <v>10053.277738</v>
       </c>
       <c r="E12" s="18" t="n">
         <f aca="false">E10-E11</f>
-        <v>8317.75321794609</v>
+        <v>11572.575522973</v>
       </c>
       <c r="F12" s="18" t="n">
         <f aca="false">F10-F11</f>
-        <v>8759.21505351418</v>
+        <v>13241.9778113484</v>
       </c>
       <c r="G12" s="18" t="n">
         <f aca="false">G10-G11</f>
-        <v>9209.75903231663</v>
+        <v>15046.026926697</v>
       </c>
       <c r="H12" s="18" t="n">
         <f aca="false">H10-H11</f>
-        <v>9670.45278413877</v>
+        <v>16993.4576947756</v>
       </c>
       <c r="I12" s="18" t="n">
         <f aca="false">I10-I11</f>
-        <v>10143.3427761742</v>
+        <v>19095.168288769</v>
       </c>
       <c r="J12" s="18" t="n">
         <f aca="false">J10-J11</f>
-        <v>10630.6259615224</v>
+        <v>21362.9889191936</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5345,31 +5397,31 @@
       </c>
       <c r="D13" s="18" t="n">
         <f aca="false">MAX(0,D12*Assumptions!$E$12)</f>
-        <v>1974.89403875</v>
+        <v>2412.78665712</v>
       </c>
       <c r="E13" s="18" t="n">
         <f aca="false">MAX(0,E12*Assumptions!$E$12)</f>
-        <v>2079.43830448652</v>
+        <v>2777.41812551352</v>
       </c>
       <c r="F13" s="18" t="n">
         <f aca="false">MAX(0,F12*Assumptions!$E$12)</f>
-        <v>2189.80376337854</v>
+        <v>3178.07467472361</v>
       </c>
       <c r="G13" s="18" t="n">
         <f aca="false">MAX(0,G12*Assumptions!$E$12)</f>
-        <v>2302.43975807916</v>
+        <v>3611.04646240729</v>
       </c>
       <c r="H13" s="18" t="n">
         <f aca="false">MAX(0,H12*Assumptions!$E$12)</f>
-        <v>2417.61319603469</v>
+        <v>4078.42984674615</v>
       </c>
       <c r="I13" s="18" t="n">
         <f aca="false">MAX(0,I12*Assumptions!$E$12)</f>
-        <v>2535.83569404354</v>
+        <v>4582.84038930457</v>
       </c>
       <c r="J13" s="18" t="n">
         <f aca="false">MAX(0,J12*Assumptions!$E$12)</f>
-        <v>2657.65649038061</v>
+        <v>5127.11734060645</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5378,31 +5430,31 @@
       </c>
       <c r="D14" s="18" t="n">
         <f aca="false">D12-D13</f>
-        <v>5924.68211625</v>
+        <v>7640.49108088</v>
       </c>
       <c r="E14" s="18" t="n">
         <f aca="false">E12-E13</f>
-        <v>6238.31491345957</v>
+        <v>8795.15739745948</v>
       </c>
       <c r="F14" s="18" t="n">
         <f aca="false">F12-F13</f>
-        <v>6569.41129013564</v>
+        <v>10063.9031366248</v>
       </c>
       <c r="G14" s="18" t="n">
         <f aca="false">G12-G13</f>
-        <v>6907.31927423747</v>
+        <v>11434.9804642897</v>
       </c>
       <c r="H14" s="18" t="n">
         <f aca="false">H12-H13</f>
-        <v>7252.83958810408</v>
+        <v>12915.0278480295</v>
       </c>
       <c r="I14" s="18" t="n">
         <f aca="false">I12-I13</f>
-        <v>7607.50708213062</v>
+        <v>14512.3278994645</v>
       </c>
       <c r="J14" s="18" t="n">
         <f aca="false">J12-J13</f>
-        <v>7972.96947114184</v>
+        <v>16235.8715785871</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5411,31 +5463,31 @@
       </c>
       <c r="D15" s="18" t="n">
         <f aca="false">D5*Assumptions!$E$10</f>
-        <v>5183.11255</v>
+        <v>3253.529059</v>
       </c>
       <c r="E15" s="18" t="n">
         <f aca="false">E5*Assumptions!$E$10</f>
-        <v>5027.6191735</v>
+        <v>3286.06434959</v>
       </c>
       <c r="F15" s="18" t="n">
         <f aca="false">F5*Assumptions!$E$10</f>
-        <v>4876.790598295</v>
+        <v>3318.9249930859</v>
       </c>
       <c r="G15" s="18" t="n">
         <f aca="false">G5*Assumptions!$E$10</f>
-        <v>4730.48688034615</v>
+        <v>3352.11424301676</v>
       </c>
       <c r="H15" s="18" t="n">
         <f aca="false">H5*Assumptions!$E$10</f>
-        <v>4588.57227393577</v>
+        <v>3385.63538544693</v>
       </c>
       <c r="I15" s="18" t="n">
         <f aca="false">I5*Assumptions!$E$10</f>
-        <v>4450.91510571769</v>
+        <v>3419.4917393014</v>
       </c>
       <c r="J15" s="18" t="n">
         <f aca="false">J5*Assumptions!$E$10</f>
-        <v>4317.38765254616</v>
+        <v>3453.68665669441</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5448,31 +5500,31 @@
       </c>
       <c r="D16" s="18" t="n">
         <f aca="false">D5*Assumptions!$E$11</f>
-        <v>11847.1144</v>
+        <v>12335.6552</v>
       </c>
       <c r="E16" s="18" t="n">
         <f aca="false">E5*Assumptions!$E$11</f>
-        <v>11491.700968</v>
+        <v>12459.011752</v>
       </c>
       <c r="F16" s="18" t="n">
         <f aca="false">F5*Assumptions!$E$11</f>
-        <v>11146.94993896</v>
+        <v>12583.60186952</v>
       </c>
       <c r="G16" s="18" t="n">
         <f aca="false">G5*Assumptions!$E$11</f>
-        <v>10812.5414407912</v>
+        <v>12709.4378882152</v>
       </c>
       <c r="H16" s="18" t="n">
         <f aca="false">H5*Assumptions!$E$11</f>
-        <v>10488.1651975675</v>
+        <v>12836.5322670974</v>
       </c>
       <c r="I16" s="18" t="n">
         <f aca="false">I5*Assumptions!$E$11</f>
-        <v>10173.5202416404</v>
+        <v>12964.8975897683</v>
       </c>
       <c r="J16" s="18" t="n">
         <f aca="false">J5*Assumptions!$E$11</f>
-        <v>9868.31463439123</v>
+        <v>13094.546565666</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5481,31 +5533,31 @@
       </c>
       <c r="D17" s="18" t="n">
         <f aca="false">D16-C16</f>
-        <v>-366.4056</v>
+        <v>122.135200000001</v>
       </c>
       <c r="E17" s="18" t="n">
         <f aca="false">E16-D16</f>
-        <v>-355.413432000001</v>
+        <v>123.356551999999</v>
       </c>
       <c r="F17" s="18" t="n">
         <f aca="false">F16-E16</f>
-        <v>-344.751029040001</v>
+        <v>124.59011752</v>
       </c>
       <c r="G17" s="18" t="n">
         <f aca="false">G16-F16</f>
-        <v>-334.408498168799</v>
+        <v>125.836018695201</v>
       </c>
       <c r="H17" s="18" t="n">
         <f aca="false">H16-G16</f>
-        <v>-324.376243223736</v>
+        <v>127.094378882153</v>
       </c>
       <c r="I17" s="18" t="n">
         <f aca="false">I16-H16</f>
-        <v>-314.644955927024</v>
+        <v>128.365322670972</v>
       </c>
       <c r="J17" s="18" t="n">
         <f aca="false">J16-I16</f>
-        <v>-305.205607249214</v>
+        <v>129.648975897684</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5515,31 +5567,31 @@
       <c r="C18" s="29"/>
       <c r="D18" s="29" t="n">
         <f aca="false">D14+D9-D15-D17</f>
-        <v>4810.19841625</v>
+        <v>7549.19501888</v>
       </c>
       <c r="E18" s="29" t="n">
         <f aca="false">E14+E9-E15-E17</f>
-        <v>5157.26572445957</v>
+        <v>8702.94837483948</v>
       </c>
       <c r="F18" s="29" t="n">
         <f aca="false">F14+F9-F15-F17</f>
-        <v>5520.79357680564</v>
+        <v>9970.77202377857</v>
       </c>
       <c r="G18" s="29" t="n">
         <f aca="false">G14+G9-G15-G17</f>
-        <v>5890.16009230737</v>
+        <v>11340.9180403151</v>
       </c>
       <c r="H18" s="29" t="n">
         <f aca="false">H14+H9-H15-H17</f>
-        <v>6266.19518163188</v>
+        <v>12820.0247998151</v>
       </c>
       <c r="I18" s="29" t="n">
         <f aca="false">I14+I9-I15-I17</f>
-        <v>6650.46200785259</v>
+        <v>14416.3748207679</v>
       </c>
       <c r="J18" s="29" t="n">
         <f aca="false">J14+J9-J15-J17</f>
-        <v>7044.63574909215</v>
+        <v>16138.9589691036</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5549,31 +5601,31 @@
       <c r="C19" s="29"/>
       <c r="D19" s="29" t="n">
         <f aca="false">D8-D13-D15-D17</f>
-        <v>16606.44995125</v>
+        <v>20116.42500388</v>
       </c>
       <c r="E19" s="29" t="n">
         <f aca="false">E8-E13-E15-E17</f>
-        <v>16662.6966763135</v>
+        <v>20755.7738865965</v>
       </c>
       <c r="F19" s="29" t="n">
         <f aca="false">F8-F13-F15-F17</f>
-        <v>16686.7515391825</v>
+        <v>21376.9243743525</v>
       </c>
       <c r="G19" s="29" t="n">
         <f aca="false">G8-G13-G15-G17</f>
-        <v>16683.6027254545</v>
+        <v>21983.842445173</v>
       </c>
       <c r="H19" s="29" t="n">
         <f aca="false">H8-H13-H15-H17</f>
-        <v>16654.3583378409</v>
+        <v>22574.6912166036</v>
       </c>
       <c r="I19" s="29" t="n">
         <f aca="false">I8-I13-I15-I17</f>
-        <v>16599.8217089183</v>
+        <v>23147.1179840392</v>
       </c>
       <c r="J19" s="29" t="n">
         <f aca="false">J8-J13-J15-J17</f>
-        <v>16520.7008551418</v>
+        <v>23698.5497768248</v>
       </c>
     </row>
   </sheetData>
@@ -5658,27 +5710,27 @@
       </c>
       <c r="E5" s="18" t="n">
         <f aca="false">D13</f>
-        <v>262.241508515625</v>
+        <v>429.61207118</v>
       </c>
       <c r="F5" s="18" t="n">
         <f aca="false">E13</f>
-        <v>299.07330956095</v>
+        <v>527.322410376218</v>
       </c>
       <c r="G5" s="18" t="n">
         <f aca="false">F13</f>
-        <v>324.095787897912</v>
+        <v>612.668284634674</v>
       </c>
       <c r="H5" s="18" t="n">
         <f aca="false">G13</f>
-        <v>348.74510001283</v>
+        <v>703.636527809359</v>
       </c>
       <c r="I5" s="18" t="n">
         <f aca="false">H13</f>
-        <v>373.787875102795</v>
+        <v>801.766215476526</v>
       </c>
       <c r="J5" s="18" t="n">
         <f aca="false">I13</f>
-        <v>399.369725184711</v>
+        <v>907.671197265277</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5687,31 +5739,31 @@
       </c>
       <c r="D6" s="18" t="n">
         <f aca="false">'Operating Model'!D19</f>
-        <v>16606.44995125</v>
+        <v>20116.42500388</v>
       </c>
       <c r="E6" s="18" t="n">
         <f aca="false">'Operating Model'!E19</f>
-        <v>16662.6966763135</v>
+        <v>20755.7738865965</v>
       </c>
       <c r="F6" s="18" t="n">
         <f aca="false">'Operating Model'!F19</f>
-        <v>16686.7515391825</v>
+        <v>21376.9243743525</v>
       </c>
       <c r="G6" s="18" t="n">
         <f aca="false">'Operating Model'!G19</f>
-        <v>16683.6027254545</v>
+        <v>21983.842445173</v>
       </c>
       <c r="H6" s="18" t="n">
         <f aca="false">'Operating Model'!H19</f>
-        <v>16654.3583378409</v>
+        <v>22574.6912166036</v>
       </c>
       <c r="I6" s="18" t="n">
         <f aca="false">'Operating Model'!I19</f>
-        <v>16599.8217089183</v>
+        <v>23147.1179840392</v>
       </c>
       <c r="J6" s="18" t="n">
         <f aca="false">'Operating Model'!J19</f>
-        <v>16520.7008551418</v>
+        <v>23698.5497768248</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5720,31 +5772,31 @@
       </c>
       <c r="D7" s="18" t="n">
         <f aca="false">SUM(D15,D18,D23,D29)</f>
-        <v>11796.251535</v>
+        <v>12567.229985</v>
       </c>
       <c r="E7" s="18" t="n">
         <f aca="false">SUM(E15,E18,E23,E29)</f>
-        <v>11505.4309518539</v>
+        <v>12052.825511757</v>
       </c>
       <c r="F7" s="18" t="n">
         <f aca="false">SUM(F15,F18,F23,F29)</f>
-        <v>11165.9579623768</v>
+        <v>11406.1523505739</v>
       </c>
       <c r="G7" s="18" t="n">
         <f aca="false">SUM(G15,G18,G23,G29)</f>
-        <v>10793.4426331471</v>
+        <v>10642.924404858</v>
       </c>
       <c r="H7" s="18" t="n">
         <f aca="false">SUM(H15,H18,H23,H29)</f>
-        <v>10388.163156209</v>
+        <v>9754.6664167885</v>
       </c>
       <c r="I7" s="18" t="n">
         <f aca="false">SUM(I15,I18,I23,I29)</f>
-        <v>9949.35970106571</v>
+        <v>8730.74316327125</v>
       </c>
       <c r="J7" s="18" t="n">
         <f aca="false">SUM(J15,J18,J23,J29)</f>
-        <v>9476.06510604968</v>
+        <v>7559.59080772125</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5753,31 +5805,31 @@
       </c>
       <c r="D8" s="18" t="n">
         <f aca="false">D19</f>
-        <v>934.33428</v>
+        <v>995.40188</v>
       </c>
       <c r="E8" s="18" t="n">
         <f aca="false">E19</f>
-        <v>934.33428</v>
+        <v>995.40188</v>
       </c>
       <c r="F8" s="18" t="n">
         <f aca="false">F19</f>
-        <v>934.33428</v>
+        <v>995.40188</v>
       </c>
       <c r="G8" s="18" t="n">
         <f aca="false">G19</f>
-        <v>934.33428</v>
+        <v>995.40188</v>
       </c>
       <c r="H8" s="18" t="n">
         <f aca="false">H19</f>
-        <v>934.33428</v>
+        <v>995.40188</v>
       </c>
       <c r="I8" s="18" t="n">
         <f aca="false">I19</f>
-        <v>934.33428</v>
+        <v>995.40188</v>
       </c>
       <c r="J8" s="18" t="n">
         <f aca="false">J19</f>
-        <v>934.33428</v>
+        <v>995.40188</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5786,31 +5838,31 @@
       </c>
       <c r="D9" s="18" t="n">
         <f aca="false">D5+D6-D7-D8</f>
-        <v>3895.86413625</v>
+        <v>6573.79313888</v>
       </c>
       <c r="E9" s="18" t="n">
         <f aca="false">E5+E6-E7-E8</f>
-        <v>4485.1729529752</v>
+        <v>8137.15856601948</v>
       </c>
       <c r="F9" s="18" t="n">
         <f aca="false">F5+F6-F7-F8</f>
-        <v>4885.53260636659</v>
+        <v>9502.69255415479</v>
       </c>
       <c r="G9" s="18" t="n">
         <f aca="false">G5+G6-G7-G8</f>
-        <v>5279.92160020528</v>
+        <v>10958.1844449498</v>
       </c>
       <c r="H9" s="18" t="n">
         <f aca="false">H5+H6-H7-H8</f>
-        <v>5680.60600164471</v>
+        <v>12528.2594476244</v>
       </c>
       <c r="I9" s="18" t="n">
         <f aca="false">I5+I6-I7-I8</f>
-        <v>6089.91560295538</v>
+        <v>14222.7391562444</v>
       </c>
       <c r="J9" s="18" t="n">
         <f aca="false">J5+J6-J7-J8</f>
-        <v>6509.67119427686</v>
+        <v>16051.2282863689</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5852,31 +5904,31 @@
       </c>
       <c r="D11" s="18" t="n">
         <f aca="false">MIN(MAX(0,D17-D19),MAX(0,D9+D10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>2906.8981021875</v>
+        <v>4915.34485416</v>
       </c>
       <c r="E11" s="18" t="n">
         <f aca="false">MIN(MAX(0,E17-E19),MAX(0,E9+E10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>3348.8797147314</v>
+        <v>6087.86892451461</v>
       </c>
       <c r="F11" s="18" t="n">
         <f aca="false">MIN(MAX(0,F17-F19),MAX(0,F9+F10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>3649.14945477494</v>
+        <v>7112.01941561609</v>
       </c>
       <c r="G11" s="18" t="n">
         <f aca="false">MIN(MAX(0,G17-G19),MAX(0,G9+G10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>3944.94120015396</v>
+        <v>8203.63833371231</v>
       </c>
       <c r="H11" s="18" t="n">
         <f aca="false">MIN(MAX(0,H17-H19),MAX(0,H9+H10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>4245.45450123354</v>
+        <v>9381.19458571831</v>
       </c>
       <c r="I11" s="18" t="n">
         <f aca="false">MIN(MAX(0,I17-I19),MAX(0,I9+I10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>4552.43670221653</v>
+        <v>10652.0543671833</v>
       </c>
       <c r="J11" s="18" t="n">
         <f aca="false">MIN(MAX(0,J17-J19),MAX(0,J9+J10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>4867.25339570764</v>
+        <v>12023.4212147766</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5885,31 +5937,31 @@
       </c>
       <c r="D12" s="18" t="n">
         <f aca="false">MIN(MAX(0,D22+D24),MAX(0,D9+D10-D11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>726.724525546874</v>
+        <v>1228.83621354</v>
       </c>
       <c r="E12" s="18" t="n">
         <f aca="false">MIN(MAX(0,E22+E24),MAX(0,E9+E10-E11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>837.21992868285</v>
+        <v>1521.96723112865</v>
       </c>
       <c r="F12" s="18" t="n">
         <f aca="false">MIN(MAX(0,F22+F24),MAX(0,F9+F10-F11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>912.287363693735</v>
+        <v>1778.00485390402</v>
       </c>
       <c r="G12" s="18" t="n">
         <f aca="false">MIN(MAX(0,G22+G24),MAX(0,G9+G10-G11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>986.23530003849</v>
+        <v>2050.90958342808</v>
       </c>
       <c r="H12" s="18" t="n">
         <f aca="false">MIN(MAX(0,H22+H24),MAX(0,H9+H10-H11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>1061.36362530838</v>
+        <v>2345.29864642958</v>
       </c>
       <c r="I12" s="18" t="n">
         <f aca="false">MIN(MAX(0,I22+I24),MAX(0,I9+I10-I11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>1138.10917555413</v>
+        <v>2663.01359179583</v>
       </c>
       <c r="J12" s="18" t="n">
         <f aca="false">MIN(MAX(0,J22+J24),MAX(0,J9+J10-J11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>1216.81334892691</v>
+        <v>3005.85530369416</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5922,31 +5974,31 @@
       </c>
       <c r="D13" s="29" t="n">
         <f aca="false">D9+D10-D11-D12</f>
-        <v>262.241508515625</v>
+        <v>429.61207118</v>
       </c>
       <c r="E13" s="29" t="n">
         <f aca="false">E9+E10-E11-E12</f>
-        <v>299.07330956095</v>
+        <v>527.322410376218</v>
       </c>
       <c r="F13" s="29" t="n">
         <f aca="false">F9+F10-F11-F12</f>
-        <v>324.095787897912</v>
+        <v>612.668284634674</v>
       </c>
       <c r="G13" s="29" t="n">
         <f aca="false">G9+G10-G11-G12</f>
-        <v>348.74510001283</v>
+        <v>703.636527809359</v>
       </c>
       <c r="H13" s="29" t="n">
         <f aca="false">H9+H10-H11-H12</f>
-        <v>373.787875102795</v>
+        <v>801.766215476526</v>
       </c>
       <c r="I13" s="29" t="n">
         <f aca="false">I9+I10-I11-I12</f>
-        <v>399.369725184711</v>
+        <v>907.671197265277</v>
       </c>
       <c r="J13" s="29" t="n">
         <f aca="false">J9+J10-J11-J12</f>
-        <v>425.604449642304</v>
+        <v>1021.95176789805</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6062,35 +6114,35 @@
       </c>
       <c r="C17" s="18" t="n">
         <f aca="false">'Sources &amp; Uses'!F6</f>
-        <v>93433.428</v>
+        <v>99540.188</v>
       </c>
       <c r="D17" s="18" t="n">
         <f aca="false">C21</f>
-        <v>93433.428</v>
+        <v>99540.188</v>
       </c>
       <c r="E17" s="18" t="n">
         <f aca="false">D21</f>
-        <v>89592.1956178125</v>
+        <v>93629.44126584</v>
       </c>
       <c r="F17" s="18" t="n">
         <f aca="false">E21</f>
-        <v>85308.9816230811</v>
+        <v>86546.1704613254</v>
       </c>
       <c r="G17" s="18" t="n">
         <f aca="false">F21</f>
-        <v>80725.4978883062</v>
+        <v>78438.7491657093</v>
       </c>
       <c r="H17" s="18" t="n">
         <f aca="false">G21</f>
-        <v>75846.2224081522</v>
+        <v>69239.708951997</v>
       </c>
       <c r="I17" s="18" t="n">
         <f aca="false">H21</f>
-        <v>70666.4336269187</v>
+        <v>58863.1124862787</v>
       </c>
       <c r="J17" s="18" t="n">
         <f aca="false">I21</f>
-        <v>65179.6626447022</v>
+        <v>47215.6562390954</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6099,31 +6151,31 @@
       </c>
       <c r="D18" s="18" t="n">
         <f aca="false">D17*Assumptions!$E$20</f>
-        <v>7941.84138</v>
+        <v>8460.91598</v>
       </c>
       <c r="E18" s="18" t="n">
         <f aca="false">E17*Assumptions!$E$20</f>
-        <v>7615.33662751406</v>
+        <v>7958.5025075964</v>
       </c>
       <c r="F18" s="18" t="n">
         <f aca="false">F17*Assumptions!$E$20</f>
-        <v>7251.2634379619</v>
+        <v>7356.42448921266</v>
       </c>
       <c r="G18" s="18" t="n">
         <f aca="false">G17*Assumptions!$E$20</f>
-        <v>6861.66732050603</v>
+        <v>6667.29367908529</v>
       </c>
       <c r="H18" s="18" t="n">
         <f aca="false">H17*Assumptions!$E$20</f>
-        <v>6446.92890469294</v>
+        <v>5885.37526091974</v>
       </c>
       <c r="I18" s="18" t="n">
         <f aca="false">I17*Assumptions!$E$20</f>
-        <v>6006.64685828809</v>
+        <v>5003.36456133369</v>
       </c>
       <c r="J18" s="18" t="n">
         <f aca="false">J17*Assumptions!$E$20</f>
-        <v>5540.27132479968</v>
+        <v>4013.33078032311</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6132,31 +6184,31 @@
       </c>
       <c r="D19" s="18" t="n">
         <f aca="false">MIN(D17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
-        <v>934.33428</v>
+        <v>995.40188</v>
       </c>
       <c r="E19" s="18" t="n">
         <f aca="false">MIN(E17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
-        <v>934.33428</v>
+        <v>995.40188</v>
       </c>
       <c r="F19" s="18" t="n">
         <f aca="false">MIN(F17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
-        <v>934.33428</v>
+        <v>995.40188</v>
       </c>
       <c r="G19" s="18" t="n">
         <f aca="false">MIN(G17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
-        <v>934.33428</v>
+        <v>995.40188</v>
       </c>
       <c r="H19" s="18" t="n">
         <f aca="false">MIN(H17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
-        <v>934.33428</v>
+        <v>995.40188</v>
       </c>
       <c r="I19" s="18" t="n">
         <f aca="false">MIN(I17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
-        <v>934.33428</v>
+        <v>995.40188</v>
       </c>
       <c r="J19" s="18" t="n">
         <f aca="false">MIN(J17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
-        <v>934.33428</v>
+        <v>995.40188</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6165,35 +6217,35 @@
       </c>
       <c r="C20" s="29" t="n">
         <f aca="false">'Sources &amp; Uses'!F7</f>
-        <v>35037.5355</v>
+        <v>37327.5705</v>
       </c>
       <c r="D20" s="29" t="n">
         <f aca="false">D11</f>
-        <v>2906.8981021875</v>
+        <v>4915.34485416</v>
       </c>
       <c r="E20" s="29" t="n">
         <f aca="false">E11</f>
-        <v>3348.8797147314</v>
+        <v>6087.86892451461</v>
       </c>
       <c r="F20" s="29" t="n">
         <f aca="false">F11</f>
-        <v>3649.14945477494</v>
+        <v>7112.01941561609</v>
       </c>
       <c r="G20" s="29" t="n">
         <f aca="false">G11</f>
-        <v>3944.94120015396</v>
+        <v>8203.63833371231</v>
       </c>
       <c r="H20" s="29" t="n">
         <f aca="false">H11</f>
-        <v>4245.45450123354</v>
+        <v>9381.19458571831</v>
       </c>
       <c r="I20" s="29" t="n">
         <f aca="false">I11</f>
-        <v>4552.43670221653</v>
+        <v>10652.0543671833</v>
       </c>
       <c r="J20" s="29" t="n">
         <f aca="false">J11</f>
-        <v>4867.25339570764</v>
+        <v>12023.4212147766</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6202,35 +6254,35 @@
       </c>
       <c r="C21" s="18" t="n">
         <f aca="false">C17</f>
-        <v>93433.428</v>
+        <v>99540.188</v>
       </c>
       <c r="D21" s="18" t="n">
         <f aca="false">MAX(0,D17-D19-D20)</f>
-        <v>89592.1956178125</v>
+        <v>93629.44126584</v>
       </c>
       <c r="E21" s="18" t="n">
         <f aca="false">MAX(0,E17-E19-E20)</f>
-        <v>85308.9816230811</v>
+        <v>86546.1704613254</v>
       </c>
       <c r="F21" s="18" t="n">
         <f aca="false">MAX(0,F17-F19-F20)</f>
-        <v>80725.4978883062</v>
+        <v>78438.7491657093</v>
       </c>
       <c r="G21" s="18" t="n">
         <f aca="false">MAX(0,G17-G19-G20)</f>
-        <v>75846.2224081522</v>
+        <v>69239.708951997</v>
       </c>
       <c r="H21" s="18" t="n">
         <f aca="false">MAX(0,H17-H19-H20)</f>
-        <v>70666.4336269187</v>
+        <v>58863.1124862787</v>
       </c>
       <c r="I21" s="18" t="n">
         <f aca="false">MAX(0,I17-I19-I20)</f>
-        <v>65179.6626447022</v>
+        <v>47215.6562390954</v>
       </c>
       <c r="J21" s="18" t="n">
         <f aca="false">MAX(0,J17-J19-J20)</f>
-        <v>59378.0749689945</v>
+        <v>34196.8331443187</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6239,35 +6291,35 @@
       </c>
       <c r="C22" s="18" t="n">
         <f aca="false">'Sources &amp; Uses'!F7</f>
-        <v>35037.5355</v>
+        <v>37327.5705</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">C26</f>
-        <v>35037.5355</v>
+        <v>37327.5705</v>
       </c>
       <c r="E22" s="18" t="n">
         <f aca="false">D26</f>
-        <v>35361.9370394531</v>
+        <v>37218.56140146</v>
       </c>
       <c r="F22" s="18" t="n">
         <f aca="false">E26</f>
-        <v>35585.5752219539</v>
+        <v>36813.1510123751</v>
       </c>
       <c r="G22" s="18" t="n">
         <f aca="false">F26</f>
-        <v>35740.8551149188</v>
+        <v>36139.5406888424</v>
       </c>
       <c r="H22" s="18" t="n">
         <f aca="false">G26</f>
-        <v>35826.8454683278</v>
+        <v>35172.8173260796</v>
       </c>
       <c r="I22" s="18" t="n">
         <f aca="false">H26</f>
-        <v>35840.2872070693</v>
+        <v>33882.7031994324</v>
       </c>
       <c r="J22" s="18" t="n">
         <f aca="false">I26</f>
-        <v>35777.3866477272</v>
+        <v>32236.1707036195</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6276,31 +6328,31 @@
       </c>
       <c r="D23" s="18" t="n">
         <f aca="false">D22*Assumptions!$E$23</f>
-        <v>3854.128905</v>
+        <v>4106.032755</v>
       </c>
       <c r="E23" s="18" t="n">
         <f aca="false">E22*Assumptions!$E$23</f>
-        <v>3889.81307433984</v>
+        <v>4094.0417541606</v>
       </c>
       <c r="F23" s="18" t="n">
         <f aca="false">F22*Assumptions!$E$23</f>
-        <v>3914.41327441493</v>
+        <v>4049.44661136127</v>
       </c>
       <c r="G23" s="18" t="n">
         <f aca="false">G22*Assumptions!$E$23</f>
-        <v>3931.49406264106</v>
+        <v>3975.34947577266</v>
       </c>
       <c r="H23" s="18" t="n">
         <f aca="false">H22*Assumptions!$E$23</f>
-        <v>3940.95300151606</v>
+        <v>3869.00990586875</v>
       </c>
       <c r="I23" s="18" t="n">
         <f aca="false">I22*Assumptions!$E$23</f>
-        <v>3942.43159277762</v>
+        <v>3727.09735193756</v>
       </c>
       <c r="J23" s="18" t="n">
         <f aca="false">J22*Assumptions!$E$23</f>
-        <v>3935.51253124999</v>
+        <v>3545.97877739815</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6310,31 +6362,31 @@
       <c r="C24" s="29"/>
       <c r="D24" s="29" t="n">
         <f aca="false">D22*Assumptions!$E$24</f>
-        <v>1051.126065</v>
+        <v>1119.827115</v>
       </c>
       <c r="E24" s="29" t="n">
         <f aca="false">E22*Assumptions!$E$24</f>
-        <v>1060.85811118359</v>
+        <v>1116.5568420438</v>
       </c>
       <c r="F24" s="29" t="n">
         <f aca="false">F22*Assumptions!$E$24</f>
-        <v>1067.56725665862</v>
+        <v>1104.39453037125</v>
       </c>
       <c r="G24" s="29" t="n">
         <f aca="false">G22*Assumptions!$E$24</f>
-        <v>1072.22565344756</v>
+        <v>1084.18622066527</v>
       </c>
       <c r="H24" s="29" t="n">
         <f aca="false">H22*Assumptions!$E$24</f>
-        <v>1074.80536404983</v>
+        <v>1055.18451978239</v>
       </c>
       <c r="I24" s="29" t="n">
         <f aca="false">I22*Assumptions!$E$24</f>
-        <v>1075.20861621208</v>
+        <v>1016.48109598297</v>
       </c>
       <c r="J24" s="29" t="n">
         <f aca="false">J22*Assumptions!$E$24</f>
-        <v>1073.32159943182</v>
+        <v>967.085121108585</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6343,35 +6395,35 @@
       </c>
       <c r="C25" s="29" t="n">
         <f aca="false">SUM(C16,C20,C13)</f>
-        <v>35057.5355</v>
+        <v>37347.5705</v>
       </c>
       <c r="D25" s="29" t="n">
         <f aca="false">D12</f>
-        <v>726.724525546874</v>
+        <v>1228.83621354</v>
       </c>
       <c r="E25" s="29" t="n">
         <f aca="false">E12</f>
-        <v>837.21992868285</v>
+        <v>1521.96723112865</v>
       </c>
       <c r="F25" s="29" t="n">
         <f aca="false">F12</f>
-        <v>912.287363693735</v>
+        <v>1778.00485390402</v>
       </c>
       <c r="G25" s="29" t="n">
         <f aca="false">G12</f>
-        <v>986.23530003849</v>
+        <v>2050.90958342808</v>
       </c>
       <c r="H25" s="29" t="n">
         <f aca="false">H12</f>
-        <v>1061.36362530838</v>
+        <v>2345.29864642958</v>
       </c>
       <c r="I25" s="29" t="n">
         <f aca="false">I12</f>
-        <v>1138.10917555413</v>
+        <v>2663.01359179583</v>
       </c>
       <c r="J25" s="29" t="n">
         <f aca="false">J12</f>
-        <v>1216.81334892691</v>
+        <v>3005.85530369416</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6380,35 +6432,35 @@
       </c>
       <c r="C26" s="29" t="n">
         <f aca="false">C22</f>
-        <v>35037.5355</v>
+        <v>37327.5705</v>
       </c>
       <c r="D26" s="29" t="n">
         <f aca="false">MAX(0,D22+D24-D25)</f>
-        <v>35361.9370394531</v>
+        <v>37218.56140146</v>
       </c>
       <c r="E26" s="29" t="n">
         <f aca="false">MAX(0,E22+E24-E25)</f>
-        <v>35585.5752219539</v>
+        <v>36813.1510123751</v>
       </c>
       <c r="F26" s="29" t="n">
         <f aca="false">MAX(0,F22+F24-F25)</f>
-        <v>35740.8551149188</v>
+        <v>36139.5406888424</v>
       </c>
       <c r="G26" s="29" t="n">
         <f aca="false">MAX(0,G22+G24-G25)</f>
-        <v>35826.8454683278</v>
+        <v>35172.8173260796</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">MAX(0,H22+H24-H25)</f>
-        <v>35840.2872070693</v>
+        <v>33882.7031994324</v>
       </c>
       <c r="I26" s="29" t="n">
         <f aca="false">MAX(0,I22+I24-I25)</f>
-        <v>35777.3866477272</v>
+        <v>32236.1707036195</v>
       </c>
       <c r="J26" s="29" t="n">
         <f aca="false">MAX(0,J22+J24-J25)</f>
-        <v>35633.8948982321</v>
+        <v>30197.4005210339</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6417,35 +6469,35 @@
       </c>
       <c r="C27" s="18" t="n">
         <f aca="false">SUM(C16,C21,C26)</f>
-        <v>128470.9635</v>
+        <v>136867.7585</v>
       </c>
       <c r="D27" s="18" t="n">
         <f aca="false">SUM(D16,D21,D26)</f>
-        <v>124954.132657266</v>
+        <v>130848.0026673</v>
       </c>
       <c r="E27" s="18" t="n">
         <f aca="false">SUM(E16,E21,E26)</f>
-        <v>120894.556845035</v>
+        <v>123359.321473701</v>
       </c>
       <c r="F27" s="18" t="n">
         <f aca="false">SUM(F16,F21,F26)</f>
-        <v>116466.353003225</v>
+        <v>114578.289854552</v>
       </c>
       <c r="G27" s="18" t="n">
         <f aca="false">SUM(G16,G21,G26)</f>
-        <v>111673.06787648</v>
+        <v>104412.526278077</v>
       </c>
       <c r="H27" s="18" t="n">
         <f aca="false">SUM(H16,H21,H26)</f>
-        <v>106506.720833988</v>
+        <v>92745.815685711</v>
       </c>
       <c r="I27" s="18" t="n">
         <f aca="false">SUM(I16,I21,I26)</f>
-        <v>100957.049292429</v>
+        <v>79451.8269427149</v>
       </c>
       <c r="J27" s="18" t="n">
         <f aca="false">SUM(J16,J21,J26)</f>
-        <v>95011.9698672266</v>
+        <v>64394.2336653526</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6454,35 +6506,35 @@
       </c>
       <c r="C28" s="18" t="n">
         <f aca="false">C27-C13</f>
-        <v>128450.9635</v>
+        <v>136847.7585</v>
       </c>
       <c r="D28" s="18" t="n">
         <f aca="false">D27-D13</f>
-        <v>124691.89114875</v>
+        <v>130418.39059612</v>
       </c>
       <c r="E28" s="18" t="n">
         <f aca="false">E27-E13</f>
-        <v>120595.483535474</v>
+        <v>122831.999063324</v>
       </c>
       <c r="F28" s="18" t="n">
         <f aca="false">F27-F13</f>
-        <v>116142.257215327</v>
+        <v>113965.621569917</v>
       </c>
       <c r="G28" s="18" t="n">
         <f aca="false">G27-G13</f>
-        <v>111324.322776467</v>
+        <v>103708.889750267</v>
       </c>
       <c r="H28" s="18" t="n">
         <f aca="false">H27-H13</f>
-        <v>106132.932958885</v>
+        <v>91944.0494702345</v>
       </c>
       <c r="I28" s="18" t="n">
         <f aca="false">I27-I13</f>
-        <v>100557.679567245</v>
+        <v>78544.1557454496</v>
       </c>
       <c r="J28" s="18" t="n">
         <f aca="false">J27-J13</f>
-        <v>94586.3654175843</v>
+        <v>63372.2818974546</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6589,31 +6641,31 @@
       </c>
       <c r="C5" s="25" t="n">
         <f aca="false">IFERROR('Debt Schedule'!D25/'Operating Model'!D8,0)</f>
-        <v>0.0310591906740619</v>
+        <v>0.0474364832834914</v>
       </c>
       <c r="D5" s="25" t="n">
         <f aca="false">IFERROR('Debt Schedule'!E25/'Operating Model'!E8,0)</f>
-        <v>0.0357567158782086</v>
+        <v>0.056489221591227</v>
       </c>
       <c r="E5" s="25" t="n">
         <f aca="false">IFERROR('Debt Schedule'!F25/'Operating Model'!F8,0)</f>
-        <v>0.0389723248528741</v>
+        <v>0.0635035432153167</v>
       </c>
       <c r="F5" s="25" t="n">
         <f aca="false">IFERROR('Debt Schedule'!G25/'Operating Model'!G8,0)</f>
-        <v>0.0421790352424689</v>
+        <v>0.0705438354845756</v>
       </c>
       <c r="G5" s="25" t="n">
         <f aca="false">IFERROR('Debt Schedule'!H25/'Operating Model'!H8,0)</f>
-        <v>0.0454814880108674</v>
+        <v>0.0777468091262203</v>
       </c>
       <c r="H5" s="25" t="n">
         <f aca="false">IFERROR('Debt Schedule'!I25/'Operating Model'!I8,0)</f>
-        <v>0.0489048091514672</v>
+        <v>0.0851406517601289</v>
       </c>
       <c r="I5" s="25" t="n">
         <f aca="false">IFERROR('Debt Schedule'!J25/'Operating Model'!J8,0)</f>
-        <v>0.0524702478204806</v>
+        <v>0.0927475407644869</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6655,31 +6707,31 @@
       </c>
       <c r="C7" s="25" t="n">
         <f aca="false">C6-C5</f>
-        <v>6.96894080932594</v>
+        <v>6.95256351671651</v>
       </c>
       <c r="D7" s="25" t="n">
         <f aca="false">D6-D5</f>
-        <v>6.96424328412179</v>
+        <v>6.94351077840877</v>
       </c>
       <c r="E7" s="25" t="n">
         <f aca="false">E6-E5</f>
-        <v>6.96102767514713</v>
+        <v>6.93649645678468</v>
       </c>
       <c r="F7" s="25" t="n">
         <f aca="false">F6-F5</f>
-        <v>6.95782096475753</v>
+        <v>6.92945616451542</v>
       </c>
       <c r="G7" s="25" t="n">
         <f aca="false">G6-G5</f>
-        <v>6.95451851198913</v>
+        <v>6.92225319087378</v>
       </c>
       <c r="H7" s="25" t="n">
         <f aca="false">H6-H5</f>
-        <v>6.95109519084853</v>
+        <v>6.91485934823987</v>
       </c>
       <c r="I7" s="25" t="n">
         <f aca="false">I6-I5</f>
-        <v>6.94752975217952</v>
+        <v>6.90725245923551</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6688,31 +6740,31 @@
       </c>
       <c r="C8" s="25" t="n">
         <f aca="false">IFERROR('Operating Model'!D8/'Debt Schedule'!D7,0)</f>
-        <v>1.98351576944396</v>
+        <v>2.06130356100108</v>
       </c>
       <c r="D8" s="25" t="n">
         <f aca="false">IFERROR('Operating Model'!E8/'Debt Schedule'!E7,0)</f>
-        <v>2.03506855330153</v>
+        <v>2.23537733018857</v>
       </c>
       <c r="E8" s="25" t="n">
         <f aca="false">IFERROR('Operating Model'!F8/'Debt Schedule'!F7,0)</f>
-        <v>2.09642512990737</v>
+        <v>2.45468526976787</v>
       </c>
       <c r="F8" s="25" t="n">
         <f aca="false">IFERROR('Operating Model'!G8/'Debt Schedule'!G7,0)</f>
-        <v>2.16632650586418</v>
+        <v>2.73165889969321</v>
       </c>
       <c r="G8" s="25" t="n">
         <f aca="false">IFERROR('Operating Model'!H8/'Debt Schedule'!H7,0)</f>
-        <v>2.24641904576168</v>
+        <v>3.09245334886708</v>
       </c>
       <c r="H8" s="25" t="n">
         <f aca="false">IFERROR('Operating Model'!I8/'Debt Schedule'!I7,0)</f>
-        <v>2.33903771217155</v>
+        <v>3.58249175933803</v>
       </c>
       <c r="I8" s="25" t="n">
         <f aca="false">IFERROR('Operating Model'!J8/'Debt Schedule'!J7,0)</f>
-        <v>2.4472752277751</v>
+        <v>4.2871371710915</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6754,31 +6806,31 @@
       </c>
       <c r="C10" s="25" t="n">
         <f aca="false">C8-C9</f>
-        <v>0.233515769443958</v>
+        <v>0.311303561001076</v>
       </c>
       <c r="D10" s="25" t="n">
         <f aca="false">D8-D9</f>
-        <v>0.285068553301532</v>
+        <v>0.485377330188566</v>
       </c>
       <c r="E10" s="25" t="n">
         <f aca="false">E8-E9</f>
-        <v>0.346425129907365</v>
+        <v>0.704685269767872</v>
       </c>
       <c r="F10" s="25" t="n">
         <f aca="false">F8-F9</f>
-        <v>0.416326505864177</v>
+        <v>0.981658899693209</v>
       </c>
       <c r="G10" s="25" t="n">
         <f aca="false">G8-G9</f>
-        <v>0.496419045761675</v>
+        <v>1.34245334886708</v>
       </c>
       <c r="H10" s="25" t="n">
         <f aca="false">H8-H9</f>
-        <v>0.589037712171546</v>
+        <v>1.83249175933803</v>
       </c>
       <c r="I10" s="25" t="n">
         <f aca="false">I8-I9</f>
-        <v>0.697275227775098</v>
+        <v>2.5371371710915</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6820,31 +6872,31 @@
       </c>
       <c r="C12" s="18" t="n">
         <f aca="false">'Debt Schedule'!D13-C11</f>
-        <v>242.241508515625</v>
+        <v>409.61207118</v>
       </c>
       <c r="D12" s="18" t="n">
         <f aca="false">'Debt Schedule'!E13-D11</f>
-        <v>279.07330956095</v>
+        <v>507.322410376218</v>
       </c>
       <c r="E12" s="18" t="n">
         <f aca="false">'Debt Schedule'!F13-E11</f>
-        <v>304.095787897912</v>
+        <v>592.668284634674</v>
       </c>
       <c r="F12" s="18" t="n">
         <f aca="false">'Debt Schedule'!G13-F11</f>
-        <v>328.74510001283</v>
+        <v>683.636527809359</v>
       </c>
       <c r="G12" s="18" t="n">
         <f aca="false">'Debt Schedule'!H13-G11</f>
-        <v>353.787875102795</v>
+        <v>781.766215476526</v>
       </c>
       <c r="H12" s="18" t="n">
         <f aca="false">'Debt Schedule'!I13-H11</f>
-        <v>379.369725184711</v>
+        <v>887.671197265277</v>
       </c>
       <c r="I12" s="18" t="n">
         <f aca="false">'Debt Schedule'!J13-I11</f>
-        <v>405.604449642304</v>
+        <v>1001.95176789805</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/03_Private_Equity/instances/public_home_depot_2023.xlsx
+++ b/03_Private_Equity/instances/public_home_depot_2023.xlsx
@@ -992,13 +992,13 @@
     <t xml:space="preserve">Next check</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real judgment-density deepening from earnings call + cash-flow cross-check</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Added real, sourced overrides for EBITDA margin (corrected), D&amp;A/revenue, capex/revenue, and cash tax rate from Home Depot's FY2023 earnings call and SEC-derived cash-flow data; replaced the trailing revenue-growth actual with management's own FY2024 guidance for the model's forward growth mechanic.</t>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full input accounting: every candidate cell sourced or declared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sourced annual EBITDA-margin change (C8) from management's own FY2024 operating-margin guidance vs FY2023 actual. Explicitly declared every remaining candidate input cell that has no disclosed value to source, each with a stated reason. NWC/revenue (C11) and existing net debt refinanced (C15) remain deliberately undeclared: both are real Home Depot balance-sheet facts that should be sourced, not declared away.</t>
   </si>
   <si>
     <t xml:space="preserve">External historical case; human stakeholder approval remains pending</t>
@@ -1219,7 +1219,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1305,6 +1305,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1954,70 +1958,70 @@
       </c>
       <c r="C5" s="18" t="n">
         <f aca="false">'Operating Model'!D8</f>
-        <v>25904.87592</v>
+        <v>24979.70178</v>
       </c>
       <c r="D5" s="18" t="n">
         <f aca="false">'Operating Model'!E8</f>
-        <v>26942.6129137</v>
+        <v>25073.7611509</v>
       </c>
       <c r="E5" s="18" t="n">
         <f aca="false">'Operating Model'!F8</f>
-        <v>27998.514159682</v>
+        <v>25167.20373904</v>
       </c>
       <c r="F5" s="18" t="n">
         <f aca="false">'Operating Model'!G8</f>
-        <v>29072.8391692923</v>
+        <v>25260.0078028277</v>
       </c>
       <c r="G5" s="18" t="n">
         <f aca="false">'Operating Model'!H8</f>
-        <v>30165.8508276788</v>
+        <v>25352.1512275173</v>
       </c>
       <c r="H5" s="18" t="n">
         <f aca="false">'Operating Model'!I8</f>
-        <v>31277.8154353161</v>
+        <v>25443.6115199203</v>
       </c>
       <c r="I5" s="18" t="n">
         <f aca="false">'Operating Model'!J8</f>
-        <v>32409.0027500234</v>
+        <v>25534.3658030487</v>
       </c>
       <c r="J5" s="18" t="n">
         <f aca="false">INDEX(C5:I5,1,Assumptions!E29)</f>
-        <v>30165.8508276788</v>
+        <v>25352.1512275173</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
         <v>256</v>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="26" t="n">
         <f aca="false">Assumptions!$E$28</f>
         <v>10</v>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="26" t="n">
         <f aca="false">Assumptions!$E$28</f>
         <v>10</v>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="26" t="n">
         <f aca="false">Assumptions!$E$28</f>
         <v>10</v>
       </c>
-      <c r="F6" s="25" t="n">
+      <c r="F6" s="26" t="n">
         <f aca="false">Assumptions!$E$28</f>
         <v>10</v>
       </c>
-      <c r="G6" s="25" t="n">
+      <c r="G6" s="26" t="n">
         <f aca="false">Assumptions!$E$28</f>
         <v>10</v>
       </c>
-      <c r="H6" s="25" t="n">
+      <c r="H6" s="26" t="n">
         <f aca="false">Assumptions!$E$28</f>
         <v>10</v>
       </c>
-      <c r="I6" s="25" t="n">
+      <c r="I6" s="26" t="n">
         <f aca="false">Assumptions!$E$28</f>
         <v>10</v>
       </c>
-      <c r="J6" s="25" t="n">
+      <c r="J6" s="26" t="n">
         <f aca="false">INDEX(C6:I6,1,Assumptions!E29)</f>
         <v>10</v>
       </c>
@@ -2028,35 +2032,35 @@
       </c>
       <c r="C7" s="18" t="n">
         <f aca="false">C5*C6</f>
-        <v>259048.7592</v>
+        <v>249797.0178</v>
       </c>
       <c r="D7" s="18" t="n">
         <f aca="false">D5*D6</f>
-        <v>269426.129137</v>
+        <v>250737.611509</v>
       </c>
       <c r="E7" s="18" t="n">
         <f aca="false">E5*E6</f>
-        <v>279985.14159682</v>
+        <v>251672.0373904</v>
       </c>
       <c r="F7" s="18" t="n">
         <f aca="false">F5*F6</f>
-        <v>290728.391692923</v>
+        <v>252600.078028277</v>
       </c>
       <c r="G7" s="18" t="n">
         <f aca="false">G5*G6</f>
-        <v>301658.508276788</v>
+        <v>253521.512275173</v>
       </c>
       <c r="H7" s="18" t="n">
         <f aca="false">H5*H6</f>
-        <v>312778.154353161</v>
+        <v>254436.115199203</v>
       </c>
       <c r="I7" s="18" t="n">
         <f aca="false">I5*I6</f>
-        <v>324090.027500234</v>
+        <v>255343.658030487</v>
       </c>
       <c r="J7" s="18" t="n">
         <f aca="false">INDEX(C7:I7,1,Assumptions!E29)</f>
-        <v>301658.508276788</v>
+        <v>253521.512275173</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2065,35 +2069,35 @@
       </c>
       <c r="C8" s="18" t="n">
         <f aca="false">'Debt Schedule'!D28</f>
-        <v>130418.39059612</v>
+        <v>131121.52294252</v>
       </c>
       <c r="D8" s="18" t="n">
         <f aca="false">'Debt Schedule'!E28</f>
-        <v>122831.999063324</v>
+        <v>125004.502230614</v>
       </c>
       <c r="E8" s="18" t="n">
         <f aca="false">'Debt Schedule'!F28</f>
-        <v>113965.621569917</v>
+        <v>118444.691402373</v>
       </c>
       <c r="F8" s="18" t="n">
         <f aca="false">'Debt Schedule'!G28</f>
-        <v>103708.889750267</v>
+        <v>111408.495992671</v>
       </c>
       <c r="G8" s="18" t="n">
         <f aca="false">'Debt Schedule'!H28</f>
-        <v>91944.0494702345</v>
+        <v>103861.052609691</v>
       </c>
       <c r="H8" s="18" t="n">
         <f aca="false">'Debt Schedule'!I28</f>
-        <v>78544.1557454496</v>
+        <v>95764.893699977</v>
       </c>
       <c r="I8" s="18" t="n">
         <f aca="false">'Debt Schedule'!J28</f>
-        <v>63372.2818974546</v>
+        <v>87079.6718865768</v>
       </c>
       <c r="J8" s="18" t="n">
         <f aca="false">INDEX(C8:I8,1,Assumptions!E29)</f>
-        <v>91944.0494702345</v>
+        <v>103861.052609691</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2102,35 +2106,35 @@
       </c>
       <c r="C9" s="18" t="n">
         <f aca="false">MAX(0,C7-C8)</f>
-        <v>128630.36860388</v>
+        <v>118675.49485748</v>
       </c>
       <c r="D9" s="18" t="n">
         <f aca="false">MAX(0,D7-D8)</f>
-        <v>146594.130073676</v>
+        <v>125733.109278386</v>
       </c>
       <c r="E9" s="18" t="n">
         <f aca="false">MAX(0,E7-E8)</f>
-        <v>166019.520026903</v>
+        <v>133227.345988027</v>
       </c>
       <c r="F9" s="18" t="n">
         <f aca="false">MAX(0,F7-F8)</f>
-        <v>187019.501942656</v>
+        <v>141191.582035606</v>
       </c>
       <c r="G9" s="18" t="n">
         <f aca="false">MAX(0,G7-G8)</f>
-        <v>209714.458806553</v>
+        <v>149660.459665482</v>
       </c>
       <c r="H9" s="18" t="n">
         <f aca="false">MAX(0,H7-H8)</f>
-        <v>234233.998607711</v>
+        <v>158671.221499226</v>
       </c>
       <c r="I9" s="18" t="n">
         <f aca="false">MAX(0,I7-I8)</f>
-        <v>260717.745602779</v>
+        <v>168263.98614391</v>
       </c>
       <c r="J9" s="18" t="n">
         <f aca="false">INDEX(C9:I9,1,Assumptions!E29)</f>
-        <v>209714.458806553</v>
+        <v>149660.459665482</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2176,35 +2180,35 @@
       </c>
       <c r="C11" s="18" t="n">
         <f aca="false">MAX(0,C9-C10)</f>
-        <v>2184.27003187996</v>
+        <v>0</v>
       </c>
       <c r="D11" s="18" t="n">
         <f aca="false">MAX(0,D9-D10)</f>
-        <v>10032.3436159156</v>
+        <v>0</v>
       </c>
       <c r="E11" s="18" t="n">
         <f aca="false">MAX(0,E9-E10)</f>
-        <v>18532.7906525221</v>
+        <v>0</v>
       </c>
       <c r="F11" s="18" t="n">
         <f aca="false">MAX(0,F9-F10)</f>
-        <v>27733.8342183242</v>
+        <v>0</v>
       </c>
       <c r="G11" s="18" t="n">
         <f aca="false">MAX(0,G9-G10)</f>
-        <v>37685.9376642754</v>
+        <v>0</v>
       </c>
       <c r="H11" s="18" t="n">
         <f aca="false">MAX(0,H9-H10)</f>
-        <v>48443.1957740512</v>
+        <v>0</v>
       </c>
       <c r="I11" s="18" t="n">
         <f aca="false">MAX(0,I9-I10)</f>
-        <v>60063.6785424262</v>
+        <v>0</v>
       </c>
       <c r="J11" s="18" t="n">
         <f aca="false">INDEX(C11:I11,1,Assumptions!E29)</f>
-        <v>37685.9376642754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2213,35 +2217,35 @@
       </c>
       <c r="C12" s="18" t="n">
         <f aca="false">MIN(C9,C9*Assumptions!$E$30+C11*Assumptions!$E$32)</f>
-        <v>13299.890866764</v>
+        <v>11867.549485748</v>
       </c>
       <c r="D12" s="18" t="n">
         <f aca="false">MIN(D9,D9*Assumptions!$E$30+D11*Assumptions!$E$32)</f>
-        <v>16665.8817305507</v>
+        <v>12573.3109278386</v>
       </c>
       <c r="E12" s="18" t="n">
         <f aca="false">MIN(E9,E9*Assumptions!$E$30+E11*Assumptions!$E$32)</f>
-        <v>20308.5101331947</v>
+        <v>13322.7345988027</v>
       </c>
       <c r="F12" s="18" t="n">
         <f aca="false">MIN(F9,F9*Assumptions!$E$30+F11*Assumptions!$E$32)</f>
-        <v>24248.7170379304</v>
+        <v>14119.1582035606</v>
       </c>
       <c r="G12" s="18" t="n">
         <f aca="false">MIN(G9,G9*Assumptions!$E$30+G11*Assumptions!$E$32)</f>
-        <v>28508.6334135104</v>
+        <v>14966.0459665482</v>
       </c>
       <c r="H12" s="18" t="n">
         <f aca="false">MIN(H9,H9*Assumptions!$E$30+H11*Assumptions!$E$32)</f>
-        <v>33112.0390155814</v>
+        <v>15867.1221499226</v>
       </c>
       <c r="I12" s="18" t="n">
         <f aca="false">MIN(I9,I9*Assumptions!$E$30+I11*Assumptions!$E$32)</f>
-        <v>38084.5102687632</v>
+        <v>16826.398614391</v>
       </c>
       <c r="J12" s="18" t="n">
         <f aca="false">INDEX(C12:I12,1,Assumptions!E29)</f>
-        <v>28508.6334135104</v>
+        <v>14966.0459665482</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2250,109 +2254,109 @@
       </c>
       <c r="C13" s="18" t="n">
         <f aca="false">MAX(0,C9-C12)</f>
-        <v>115330.477737116</v>
+        <v>106807.945371732</v>
       </c>
       <c r="D13" s="18" t="n">
         <f aca="false">MAX(0,D9-D12)</f>
-        <v>129928.248343125</v>
+        <v>113159.798350548</v>
       </c>
       <c r="E13" s="18" t="n">
         <f aca="false">MAX(0,E9-E12)</f>
-        <v>145711.009893708</v>
+        <v>119904.611389224</v>
       </c>
       <c r="F13" s="18" t="n">
         <f aca="false">MAX(0,F9-F12)</f>
-        <v>162770.784904725</v>
+        <v>127072.423832046</v>
       </c>
       <c r="G13" s="18" t="n">
         <f aca="false">MAX(0,G9-G12)</f>
-        <v>181205.825393043</v>
+        <v>134694.413698934</v>
       </c>
       <c r="H13" s="18" t="n">
         <f aca="false">MAX(0,H9-H12)</f>
-        <v>201121.95959213</v>
+        <v>142804.099349304</v>
       </c>
       <c r="I13" s="18" t="n">
         <f aca="false">MAX(0,I9-I12)</f>
-        <v>222633.235334016</v>
+        <v>151437.587529519</v>
       </c>
       <c r="J13" s="18" t="n">
         <f aca="false">INDEX(C13:I13,1,Assumptions!E29)</f>
-        <v>181205.825393043</v>
+        <v>134694.413698934</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
         <v>262</v>
       </c>
-      <c r="C14" s="25" t="n">
+      <c r="C14" s="26" t="n">
         <f aca="false">IFERROR(C13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>0.985059383901521</v>
-      </c>
-      <c r="D14" s="25" t="n">
+        <v>0.912266825977136</v>
+      </c>
+      <c r="D14" s="26" t="n">
         <f aca="false">IFERROR(D13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>1.10974169859953</v>
-      </c>
-      <c r="E14" s="25" t="n">
+        <v>0.966519201452483</v>
+      </c>
+      <c r="E14" s="26" t="n">
         <f aca="false">IFERROR(E13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>1.24454524467275</v>
-      </c>
-      <c r="F14" s="25" t="n">
+        <v>1.02412792298708</v>
+      </c>
+      <c r="F14" s="26" t="n">
         <f aca="false">IFERROR(F13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>1.39025600380232</v>
-      </c>
-      <c r="G14" s="25" t="n">
+        <v>1.08534956229167</v>
+      </c>
+      <c r="G14" s="26" t="n">
         <f aca="false">IFERROR(G13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>1.54771316501356</v>
-      </c>
-      <c r="H14" s="25" t="n">
+        <v>1.15045041672058</v>
+      </c>
+      <c r="H14" s="26" t="n">
         <f aca="false">IFERROR(H13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>1.71782062722811</v>
-      </c>
-      <c r="I14" s="25" t="n">
+        <v>1.21971677290959</v>
+      </c>
+      <c r="I14" s="26" t="n">
         <f aca="false">IFERROR(I13/'Sources &amp; Uses'!$F$8,0)</f>
-        <v>1.90155249451074</v>
-      </c>
-      <c r="J14" s="25" t="n">
+        <v>1.2934570253961</v>
+      </c>
+      <c r="J14" s="26" t="n">
         <f aca="false">INDEX(C14:I14,1,Assumptions!E29)</f>
-        <v>1.54771316501356</v>
+        <v>1.15045041672058</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="0" t="s">
         <v>263</v>
       </c>
-      <c r="C15" s="23" t="n">
+      <c r="C15" s="24" t="n">
         <f aca="false">IFERROR((C13/'Sources &amp; Uses'!$F$8)^(1/1)-1,0)</f>
-        <v>-0.0149406160984794</v>
-      </c>
-      <c r="D15" s="23" t="n">
+        <v>-0.087733174022864</v>
+      </c>
+      <c r="D15" s="24" t="n">
         <f aca="false">IFERROR((D13/'Sources &amp; Uses'!$F$8)^(1/2)-1,0)</f>
-        <v>0.053442783733189</v>
-      </c>
-      <c r="E15" s="23" t="n">
+        <v>-0.0168829156949397</v>
+      </c>
+      <c r="E15" s="24" t="n">
         <f aca="false">IFERROR((E13/'Sources &amp; Uses'!$F$8)^(1/3)-1,0)</f>
-        <v>0.0756481383470085</v>
-      </c>
-      <c r="F15" s="23" t="n">
+        <v>0.00797881026828362</v>
+      </c>
+      <c r="F15" s="24" t="n">
         <f aca="false">IFERROR((F13/'Sources &amp; Uses'!$F$8)^(1/4)-1,0)</f>
-        <v>0.0858596488737349</v>
-      </c>
-      <c r="G15" s="23" t="n">
+        <v>0.0206865897800075</v>
+      </c>
+      <c r="G15" s="24" t="n">
         <f aca="false">IFERROR((G13/'Sources &amp; Uses'!$F$8)^(1/5)-1,0)</f>
-        <v>0.0912847728470427</v>
-      </c>
-      <c r="H15" s="23" t="n">
+        <v>0.0284272633192819</v>
+      </c>
+      <c r="H15" s="24" t="n">
         <f aca="false">IFERROR((H13/'Sources &amp; Uses'!$F$8)^(1/6)-1,0)</f>
-        <v>0.0943669501469977</v>
-      </c>
-      <c r="I15" s="23" t="n">
+        <v>0.0336571173086588</v>
+      </c>
+      <c r="I15" s="24" t="n">
         <f aca="false">IFERROR((I13/'Sources &amp; Uses'!$F$8)^(1/7)-1,0)</f>
-        <v>0.0961566351060408</v>
-      </c>
-      <c r="J15" s="23" t="n">
+        <v>0.0374437818774869</v>
+      </c>
+      <c r="J15" s="24" t="n">
         <f aca="false">INDEX(C15:I15,1,Assumptions!E29)</f>
-        <v>0.0912847728470427</v>
+        <v>0.0284272633192819</v>
       </c>
     </row>
   </sheetData>
@@ -2396,145 +2400,145 @@
       <c r="B4" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="C4" s="30" t="n">
+      <c r="C4" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="D4" s="30" t="n">
+      <c r="D4" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="30" t="n">
+      <c r="E4" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="F4" s="30" t="n">
+      <c r="F4" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="G4" s="30" t="n">
+      <c r="G4" s="31" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="25" t="n">
+      <c r="B5" s="26" t="n">
         <v>8</v>
       </c>
       <c r="C5" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0751672306112294</v>
+        <v>-0.0245247399205034</v>
       </c>
       <c r="D5" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.129712830399603</v>
+        <v>0.0409517146216205</v>
       </c>
       <c r="E5" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.175392874914771</v>
+        <v>0.0931821356781608</v>
       </c>
       <c r="F5" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.214909698678224</v>
+        <v>0.136998355868621</v>
       </c>
       <c r="G5" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.24986760752772</v>
+        <v>0.174946150946277</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="25" t="n">
+      <c r="B6" s="26" t="n">
         <v>9</v>
       </c>
       <c r="C6" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0096022027661522</v>
+        <v>-0.0840104280705566</v>
       </c>
       <c r="D6" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.060821544399394</v>
+        <v>-0.0225268087293444</v>
       </c>
       <c r="E6" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.103715963287841</v>
+        <v>0.0265185366353098</v>
       </c>
       <c r="F6" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.140823002250723</v>
+        <v>0.0676627895121642</v>
       </c>
       <c r="G6" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.173649134571073</v>
+        <v>0.103296481099602</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="25" t="n">
+      <c r="B7" s="26" t="n">
         <v>10</v>
       </c>
       <c r="C7" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0375124505656633</v>
+        <v>-0.126756502731222</v>
       </c>
       <c r="D7" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0113166610162549</v>
+        <v>-0.0681421118870451</v>
       </c>
       <c r="E7" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0522093452905523</v>
+        <v>-0.0213855436645798</v>
       </c>
       <c r="F7" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.087584726703444</v>
+        <v>0.0178386488106841</v>
       </c>
       <c r="G7" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.118878976624706</v>
+        <v>0.0518094388895125</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="25" t="n">
+      <c r="B8" s="26" t="n">
         <v>11</v>
       </c>
       <c r="C8" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0739054240051155</v>
+        <v>-0.159775036239478</v>
       </c>
       <c r="D8" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0269226080577923</v>
+        <v>-0.103376935850607</v>
       </c>
       <c r="E8" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0124238677761599</v>
+        <v>-0.0583882975576665</v>
       </c>
       <c r="F8" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0464616575319683</v>
+        <v>-0.0206472255609741</v>
       </c>
       <c r="G8" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.076572628971487</v>
+        <v>0.0120390823842593</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="25" t="n">
+      <c r="B9" s="26" t="n">
         <v>12</v>
       </c>
       <c r="C9" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.103343068452723</v>
+        <v>-0.186483154805678</v>
       </c>
       <c r="D9" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0578536889932648</v>
+        <v>-0.131877773292181</v>
       </c>
       <c r="E9" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>-0.0197579143251433</v>
+        <v>-0.0883191828286724</v>
       </c>
       <c r="F9" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.0131979207593107</v>
+        <v>-0.051777781240714</v>
       </c>
       <c r="G9" s="21" t="n">
         <f aca="false">IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
-        <v>0.042351758776191</v>
+        <v>-0.0201304685952459</v>
       </c>
     </row>
   </sheetData>
@@ -2737,128 +2741,128 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="32" t="s">
         <v>282</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="32" t="s">
         <v>283</v>
       </c>
-      <c r="E5" s="31" t="s">
+      <c r="E5" s="32" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="32" t="s">
         <v>285</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="32" t="s">
         <v>286</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="E6" s="32" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="32" t="s">
         <v>288</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="32" t="s">
         <v>289</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="31" t="s">
+      <c r="E7" s="32" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="32" t="s">
         <v>291</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="32" t="s">
         <v>292</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="31" t="s">
+      <c r="E8" s="32" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="32" t="s">
         <v>294</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="32" t="s">
         <v>295</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D9" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="31" t="s">
+      <c r="E9" s="32" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="33" t="s">
         <v>297</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="33" t="s">
         <v>298</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="33" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="33" t="s">
         <v>300</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="E11" s="32" t="s">
+      <c r="E11" s="33" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="33" t="s">
         <v>304</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="33" t="s">
         <v>305</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="33" t="s">
         <v>306</v>
       </c>
-      <c r="E12" s="32" t="s">
+      <c r="E12" s="33" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="33" t="s">
         <v>308</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="33" t="s">
         <v>309</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="32" t="s">
+      <c r="E13" s="33" t="s">
         <v>310</v>
       </c>
     </row>
@@ -2924,216 +2928,216 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="34" t="s">
         <v>317</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C5" s="34" t="s">
         <v>318</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="34" t="s">
         <v>309</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="34" t="s">
         <v>319</v>
       </c>
-      <c r="F5" s="33" t="s">
+      <c r="F5" s="34" t="s">
         <v>320</v>
       </c>
-      <c r="G5" s="33" t="s">
+      <c r="G5" s="34" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="33"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="33"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="33"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="33"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="33"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="33"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="33"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="33"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="33"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="33"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="34"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="33"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="33"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
+      <c r="B26" s="34"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="33"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="33"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="33"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="33"/>
+      <c r="B29" s="34"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4431,14 +4435,14 @@
         <v>131</v>
       </c>
       <c r="C8" s="22" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="D8" s="22" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="D8" s="23" t="n">
         <v>-0.003</v>
       </c>
-      <c r="E8" s="23" t="n">
+      <c r="E8" s="24" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D8,C8)</f>
-        <v>0.005</v>
+        <v>-0.001</v>
       </c>
       <c r="F8" s="14" t="s">
         <v>132</v>
@@ -4520,13 +4524,13 @@
       <c r="B13" s="0" t="s">
         <v>137</v>
       </c>
-      <c r="C13" s="24" t="n">
+      <c r="C13" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="E13" s="25" t="n">
+      <c r="E13" s="26" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D13,C13)</f>
         <v>10</v>
       </c>
@@ -4610,13 +4614,13 @@
       <c r="B18" s="0" t="s">
         <v>143</v>
       </c>
-      <c r="C18" s="22" t="n">
+      <c r="C18" s="23" t="n">
         <v>0.09</v>
       </c>
-      <c r="D18" s="22" t="n">
+      <c r="D18" s="23" t="n">
         <v>0.115</v>
       </c>
-      <c r="E18" s="23" t="n">
+      <c r="E18" s="24" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D18,C18)</f>
         <v>0.09</v>
       </c>
@@ -4628,13 +4632,13 @@
       <c r="B19" s="0" t="s">
         <v>144</v>
       </c>
-      <c r="C19" s="24" t="n">
+      <c r="C19" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="D19" s="24" t="n">
+      <c r="D19" s="25" t="n">
         <v>3.5</v>
       </c>
-      <c r="E19" s="25" t="n">
+      <c r="E19" s="26" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D19,C19)</f>
         <v>4</v>
       </c>
@@ -4646,13 +4650,13 @@
       <c r="B20" s="0" t="s">
         <v>146</v>
       </c>
-      <c r="C20" s="22" t="n">
+      <c r="C20" s="23" t="n">
         <v>0.085</v>
       </c>
-      <c r="D20" s="22" t="n">
+      <c r="D20" s="23" t="n">
         <v>0.105</v>
       </c>
-      <c r="E20" s="23" t="n">
+      <c r="E20" s="24" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D20,C20)</f>
         <v>0.085</v>
       </c>
@@ -4682,13 +4686,13 @@
       <c r="B22" s="0" t="s">
         <v>149</v>
       </c>
-      <c r="C22" s="24" t="n">
+      <c r="C22" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="D22" s="24" t="n">
+      <c r="D22" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="25" t="n">
+      <c r="E22" s="26" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D22,C22)</f>
         <v>1.5</v>
       </c>
@@ -4700,13 +4704,13 @@
       <c r="B23" s="0" t="s">
         <v>150</v>
       </c>
-      <c r="C23" s="22" t="n">
+      <c r="C23" s="23" t="n">
         <v>0.11</v>
       </c>
-      <c r="D23" s="22" t="n">
+      <c r="D23" s="23" t="n">
         <v>0.13</v>
       </c>
-      <c r="E23" s="23" t="n">
+      <c r="E23" s="24" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D23,C23)</f>
         <v>0.11</v>
       </c>
@@ -4718,13 +4722,13 @@
       <c r="B24" s="0" t="s">
         <v>151</v>
       </c>
-      <c r="C24" s="22" t="n">
+      <c r="C24" s="23" t="n">
         <v>0.03</v>
       </c>
-      <c r="D24" s="22" t="n">
+      <c r="D24" s="23" t="n">
         <v>0.05</v>
       </c>
-      <c r="E24" s="23" t="n">
+      <c r="E24" s="24" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D24,C24)</f>
         <v>0.03</v>
       </c>
@@ -4754,13 +4758,13 @@
       <c r="B26" s="0" t="s">
         <v>154</v>
       </c>
-      <c r="C26" s="24" t="n">
+      <c r="C26" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="D26" s="24" t="n">
+      <c r="D26" s="25" t="n">
         <v>6.5</v>
       </c>
-      <c r="E26" s="25" t="n">
+      <c r="E26" s="26" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D26,C26)</f>
         <v>7</v>
       </c>
@@ -4772,13 +4776,13 @@
       <c r="B27" s="0" t="s">
         <v>155</v>
       </c>
-      <c r="C27" s="24" t="n">
+      <c r="C27" s="25" t="n">
         <v>1.75</v>
       </c>
-      <c r="D27" s="24" t="n">
+      <c r="D27" s="25" t="n">
         <v>1.5</v>
       </c>
-      <c r="E27" s="25" t="n">
+      <c r="E27" s="26" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D27,C27)</f>
         <v>1.75</v>
       </c>
@@ -4790,13 +4794,13 @@
       <c r="B28" s="0" t="s">
         <v>156</v>
       </c>
-      <c r="C28" s="24" t="n">
+      <c r="C28" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="D28" s="24" t="n">
+      <c r="D28" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="E28" s="25" t="n">
+      <c r="E28" s="26" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D28,C28)</f>
         <v>10</v>
       </c>
@@ -4808,13 +4812,13 @@
       <c r="B29" s="0" t="s">
         <v>157</v>
       </c>
-      <c r="C29" s="26" t="n">
+      <c r="C29" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="D29" s="26" t="n">
+      <c r="D29" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="E29" s="27" t="n">
+      <c r="E29" s="28" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D29,C29)</f>
         <v>5</v>
       </c>
@@ -4880,13 +4884,13 @@
       <c r="B33" s="0" t="s">
         <v>164</v>
       </c>
-      <c r="C33" s="22" t="n">
+      <c r="C33" s="23" t="n">
         <v>0.00375</v>
       </c>
-      <c r="D33" s="22" t="n">
+      <c r="D33" s="23" t="n">
         <v>0.005</v>
       </c>
-      <c r="E33" s="23" t="n">
+      <c r="E33" s="24" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D33,C33)</f>
         <v>0.00375</v>
       </c>
@@ -5015,17 +5019,17 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="29" t="s">
         <v>178</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="30" t="n">
         <f aca="false">SUM(C5:C8)</f>
         <v>253947.4794</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="E9" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="30" t="n">
         <f aca="false">SUM(F5:F8)</f>
         <v>253947.4794</v>
       </c>
@@ -5187,68 +5191,68 @@
       </c>
       <c r="D7" s="21" t="n">
         <f aca="false">MAX(0,MIN(0.6,C7+Assumptions!$E$8))</f>
-        <v>0.168</v>
+        <v>0.162</v>
       </c>
       <c r="E7" s="21" t="n">
         <f aca="false">MAX(0,MIN(0.6,D7+Assumptions!$E$8))</f>
-        <v>0.173</v>
+        <v>0.161</v>
       </c>
       <c r="F7" s="21" t="n">
         <f aca="false">MAX(0,MIN(0.6,E7+Assumptions!$E$8))</f>
-        <v>0.178</v>
+        <v>0.16</v>
       </c>
       <c r="G7" s="21" t="n">
         <f aca="false">MAX(0,MIN(0.6,F7+Assumptions!$E$8))</f>
-        <v>0.183</v>
+        <v>0.159</v>
       </c>
       <c r="H7" s="21" t="n">
         <f aca="false">MAX(0,MIN(0.6,G7+Assumptions!$E$8))</f>
-        <v>0.188</v>
+        <v>0.158</v>
       </c>
       <c r="I7" s="21" t="n">
         <f aca="false">MAX(0,MIN(0.6,H7+Assumptions!$E$8))</f>
-        <v>0.193</v>
+        <v>0.157</v>
       </c>
       <c r="J7" s="21" t="n">
         <f aca="false">MAX(0,MIN(0.6,I7+Assumptions!$E$8))</f>
-        <v>0.198</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="29" t="s">
         <v>194</v>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="30" t="n">
         <f aca="false">C5*C7</f>
         <v>24885.047</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="30" t="n">
         <f aca="false">D5*D7</f>
-        <v>25904.87592</v>
-      </c>
-      <c r="E8" s="29" t="n">
+        <v>24979.70178</v>
+      </c>
+      <c r="E8" s="30" t="n">
         <f aca="false">E5*E7</f>
-        <v>26942.6129137</v>
-      </c>
-      <c r="F8" s="29" t="n">
+        <v>25073.7611509</v>
+      </c>
+      <c r="F8" s="30" t="n">
         <f aca="false">F5*F7</f>
-        <v>27998.514159682</v>
-      </c>
-      <c r="G8" s="29" t="n">
+        <v>25167.20373904</v>
+      </c>
+      <c r="G8" s="30" t="n">
         <f aca="false">G5*G7</f>
-        <v>29072.8391692923</v>
-      </c>
-      <c r="H8" s="29" t="n">
+        <v>25260.0078028277</v>
+      </c>
+      <c r="H8" s="30" t="n">
         <f aca="false">H5*H7</f>
-        <v>30165.8508276788</v>
-      </c>
-      <c r="I8" s="29" t="n">
+        <v>25352.1512275173</v>
+      </c>
+      <c r="I8" s="30" t="n">
         <f aca="false">I5*I7</f>
-        <v>31277.8154353161</v>
-      </c>
-      <c r="J8" s="29" t="n">
+        <v>25443.6115199203</v>
+      </c>
+      <c r="J8" s="30" t="n">
         <f aca="false">J5*J7</f>
-        <v>32409.0027500234</v>
+        <v>25534.3658030487</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5298,31 +5302,31 @@
       </c>
       <c r="D10" s="18" t="n">
         <f aca="false">D8-D9</f>
-        <v>22620.507723</v>
+        <v>21695.333583</v>
       </c>
       <c r="E10" s="18" t="n">
         <f aca="false">E8-E9</f>
-        <v>23625.40103473</v>
+        <v>21756.54927193</v>
       </c>
       <c r="F10" s="18" t="n">
         <f aca="false">F8-F9</f>
-        <v>24648.1301619223</v>
+        <v>21816.8197412803</v>
       </c>
       <c r="G10" s="18" t="n">
         <f aca="false">G8-G9</f>
-        <v>25688.951331555</v>
+        <v>21876.1199650904</v>
       </c>
       <c r="H10" s="18" t="n">
         <f aca="false">H8-H9</f>
-        <v>26748.1241115641</v>
+        <v>21934.4245114026</v>
       </c>
       <c r="I10" s="18" t="n">
         <f aca="false">I8-I9</f>
-        <v>27825.9114520403</v>
+        <v>21991.7075366445</v>
       </c>
       <c r="J10" s="18" t="n">
         <f aca="false">J8-J9</f>
-        <v>28922.5797269148</v>
+        <v>22047.9427799401</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5335,27 +5339,27 @@
       </c>
       <c r="E11" s="18" t="n">
         <f aca="false">'Debt Schedule'!E7</f>
-        <v>12052.825511757</v>
+        <v>12112.1523034845</v>
       </c>
       <c r="F11" s="18" t="n">
         <f aca="false">'Debt Schedule'!F7</f>
-        <v>11406.1523505739</v>
+        <v>11593.2665797328</v>
       </c>
       <c r="G11" s="18" t="n">
         <f aca="false">'Debt Schedule'!G7</f>
-        <v>10642.924404858</v>
+        <v>11032.9366705236</v>
       </c>
       <c r="H11" s="18" t="n">
         <f aca="false">'Debt Schedule'!H7</f>
-        <v>9754.6664167885</v>
+        <v>10429.6820580664</v>
       </c>
       <c r="I11" s="18" t="n">
         <f aca="false">'Debt Schedule'!I7</f>
-        <v>8730.74316327125</v>
+        <v>9780.4111150332</v>
       </c>
       <c r="J11" s="18" t="n">
         <f aca="false">'Debt Schedule'!J7</f>
-        <v>7559.59080772125</v>
+        <v>9081.70588740268</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5364,31 +5368,31 @@
       </c>
       <c r="D12" s="18" t="n">
         <f aca="false">D10-D11</f>
-        <v>10053.277738</v>
+        <v>9128.103598</v>
       </c>
       <c r="E12" s="18" t="n">
         <f aca="false">E10-E11</f>
-        <v>11572.575522973</v>
+        <v>9644.3969684455</v>
       </c>
       <c r="F12" s="18" t="n">
         <f aca="false">F10-F11</f>
-        <v>13241.9778113484</v>
+        <v>10223.5531615475</v>
       </c>
       <c r="G12" s="18" t="n">
         <f aca="false">G10-G11</f>
-        <v>15046.026926697</v>
+        <v>10843.1832945669</v>
       </c>
       <c r="H12" s="18" t="n">
         <f aca="false">H10-H11</f>
-        <v>16993.4576947756</v>
+        <v>11504.7424533362</v>
       </c>
       <c r="I12" s="18" t="n">
         <f aca="false">I10-I11</f>
-        <v>19095.168288769</v>
+        <v>12211.2964216113</v>
       </c>
       <c r="J12" s="18" t="n">
         <f aca="false">J10-J11</f>
-        <v>21362.9889191936</v>
+        <v>12966.2368925375</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5397,31 +5401,31 @@
       </c>
       <c r="D13" s="18" t="n">
         <f aca="false">MAX(0,D12*Assumptions!$E$12)</f>
-        <v>2412.78665712</v>
+        <v>2190.74486352</v>
       </c>
       <c r="E13" s="18" t="n">
         <f aca="false">MAX(0,E12*Assumptions!$E$12)</f>
-        <v>2777.41812551352</v>
+        <v>2314.65527242692</v>
       </c>
       <c r="F13" s="18" t="n">
         <f aca="false">MAX(0,F12*Assumptions!$E$12)</f>
-        <v>3178.07467472361</v>
+        <v>2453.6527587714</v>
       </c>
       <c r="G13" s="18" t="n">
         <f aca="false">MAX(0,G12*Assumptions!$E$12)</f>
-        <v>3611.04646240729</v>
+        <v>2602.36399069605</v>
       </c>
       <c r="H13" s="18" t="n">
         <f aca="false">MAX(0,H12*Assumptions!$E$12)</f>
-        <v>4078.42984674615</v>
+        <v>2761.13818880068</v>
       </c>
       <c r="I13" s="18" t="n">
         <f aca="false">MAX(0,I12*Assumptions!$E$12)</f>
-        <v>4582.84038930457</v>
+        <v>2930.71114118672</v>
       </c>
       <c r="J13" s="18" t="n">
         <f aca="false">MAX(0,J12*Assumptions!$E$12)</f>
-        <v>5127.11734060645</v>
+        <v>3111.89685420899</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5430,31 +5434,31 @@
       </c>
       <c r="D14" s="18" t="n">
         <f aca="false">D12-D13</f>
-        <v>7640.49108088</v>
+        <v>6937.35873448</v>
       </c>
       <c r="E14" s="18" t="n">
         <f aca="false">E12-E13</f>
-        <v>8795.15739745948</v>
+        <v>7329.74169601858</v>
       </c>
       <c r="F14" s="18" t="n">
         <f aca="false">F12-F13</f>
-        <v>10063.9031366248</v>
+        <v>7769.90040277609</v>
       </c>
       <c r="G14" s="18" t="n">
         <f aca="false">G12-G13</f>
-        <v>11434.9804642897</v>
+        <v>8240.81930387081</v>
       </c>
       <c r="H14" s="18" t="n">
         <f aca="false">H12-H13</f>
-        <v>12915.0278480295</v>
+        <v>8743.60426453549</v>
       </c>
       <c r="I14" s="18" t="n">
         <f aca="false">I12-I13</f>
-        <v>14512.3278994645</v>
+        <v>9280.58528042461</v>
       </c>
       <c r="J14" s="18" t="n">
         <f aca="false">J12-J13</f>
-        <v>16235.8715785871</v>
+        <v>9854.34003832847</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5561,71 +5565,71 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="29" t="s">
         <v>204</v>
       </c>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29" t="n">
+      <c r="C18" s="30"/>
+      <c r="D18" s="30" t="n">
         <f aca="false">D14+D9-D15-D17</f>
-        <v>7549.19501888</v>
-      </c>
-      <c r="E18" s="29" t="n">
+        <v>6846.06267248</v>
+      </c>
+      <c r="E18" s="30" t="n">
         <f aca="false">E14+E9-E15-E17</f>
-        <v>8702.94837483948</v>
-      </c>
-      <c r="F18" s="29" t="n">
+        <v>7237.53267339858</v>
+      </c>
+      <c r="F18" s="30" t="n">
         <f aca="false">F14+F9-F15-F17</f>
-        <v>9970.77202377857</v>
-      </c>
-      <c r="G18" s="29" t="n">
+        <v>7676.76928992989</v>
+      </c>
+      <c r="G18" s="30" t="n">
         <f aca="false">G14+G9-G15-G17</f>
-        <v>11340.9180403151</v>
-      </c>
-      <c r="H18" s="29" t="n">
+        <v>8146.75687989615</v>
+      </c>
+      <c r="H18" s="30" t="n">
         <f aca="false">H14+H9-H15-H17</f>
-        <v>12820.0247998151</v>
-      </c>
-      <c r="I18" s="29" t="n">
+        <v>8648.60121632108</v>
+      </c>
+      <c r="I18" s="30" t="n">
         <f aca="false">I14+I9-I15-I17</f>
-        <v>14416.3748207679</v>
-      </c>
-      <c r="J18" s="29" t="n">
+        <v>9184.63220172806</v>
+      </c>
+      <c r="J18" s="30" t="n">
         <f aca="false">J14+J9-J15-J17</f>
-        <v>16138.9589691036</v>
+        <v>9757.42742884495</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29" t="n">
+      <c r="C19" s="30"/>
+      <c r="D19" s="30" t="n">
         <f aca="false">D8-D13-D15-D17</f>
-        <v>20116.42500388</v>
-      </c>
-      <c r="E19" s="29" t="n">
+        <v>19413.29265748</v>
+      </c>
+      <c r="E19" s="30" t="n">
         <f aca="false">E8-E13-E15-E17</f>
-        <v>20755.7738865965</v>
-      </c>
-      <c r="F19" s="29" t="n">
+        <v>19349.6849768831</v>
+      </c>
+      <c r="F19" s="30" t="n">
         <f aca="false">F8-F13-F15-F17</f>
-        <v>21376.9243743525</v>
-      </c>
-      <c r="G19" s="29" t="n">
+        <v>19270.0358696627</v>
+      </c>
+      <c r="G19" s="30" t="n">
         <f aca="false">G8-G13-G15-G17</f>
-        <v>21983.842445173</v>
-      </c>
-      <c r="H19" s="29" t="n">
+        <v>19179.6935504197</v>
+      </c>
+      <c r="H19" s="30" t="n">
         <f aca="false">H8-H13-H15-H17</f>
-        <v>22574.6912166036</v>
-      </c>
-      <c r="I19" s="29" t="n">
+        <v>19078.2832743875</v>
+      </c>
+      <c r="I19" s="30" t="n">
         <f aca="false">I8-I13-I15-I17</f>
-        <v>23147.1179840392</v>
-      </c>
-      <c r="J19" s="29" t="n">
+        <v>18965.0433167613</v>
+      </c>
+      <c r="J19" s="30" t="n">
         <f aca="false">J8-J13-J15-J17</f>
-        <v>23698.5497768248</v>
+        <v>18839.1333162476</v>
       </c>
     </row>
   </sheetData>
@@ -5710,27 +5714,27 @@
       </c>
       <c r="E5" s="18" t="n">
         <f aca="false">D13</f>
-        <v>429.61207118</v>
+        <v>385.66629953</v>
       </c>
       <c r="F5" s="18" t="n">
         <f aca="false">E13</f>
-        <v>527.322410376218</v>
+        <v>432.987318308036</v>
       </c>
       <c r="G5" s="18" t="n">
         <f aca="false">F13</f>
-        <v>612.668284634674</v>
+        <v>463.397170514871</v>
       </c>
       <c r="H5" s="18" t="n">
         <f aca="false">G13</f>
-        <v>703.636527809359</v>
+        <v>494.672010650688</v>
       </c>
       <c r="I5" s="18" t="n">
         <f aca="false">H13</f>
-        <v>801.766215476526</v>
+        <v>527.991959185735</v>
       </c>
       <c r="J5" s="18" t="n">
         <f aca="false">I13</f>
-        <v>907.671197265277</v>
+        <v>563.576392557112</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5739,31 +5743,31 @@
       </c>
       <c r="D6" s="18" t="n">
         <f aca="false">'Operating Model'!D19</f>
-        <v>20116.42500388</v>
+        <v>19413.29265748</v>
       </c>
       <c r="E6" s="18" t="n">
         <f aca="false">'Operating Model'!E19</f>
-        <v>20755.7738865965</v>
+        <v>19349.6849768831</v>
       </c>
       <c r="F6" s="18" t="n">
         <f aca="false">'Operating Model'!F19</f>
-        <v>21376.9243743525</v>
+        <v>19270.0358696627</v>
       </c>
       <c r="G6" s="18" t="n">
         <f aca="false">'Operating Model'!G19</f>
-        <v>21983.842445173</v>
+        <v>19179.6935504197</v>
       </c>
       <c r="H6" s="18" t="n">
         <f aca="false">'Operating Model'!H19</f>
-        <v>22574.6912166036</v>
+        <v>19078.2832743875</v>
       </c>
       <c r="I6" s="18" t="n">
         <f aca="false">'Operating Model'!I19</f>
-        <v>23147.1179840392</v>
+        <v>18965.0433167613</v>
       </c>
       <c r="J6" s="18" t="n">
         <f aca="false">'Operating Model'!J19</f>
-        <v>23698.5497768248</v>
+        <v>18839.1333162476</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5776,27 +5780,27 @@
       </c>
       <c r="E7" s="18" t="n">
         <f aca="false">SUM(E15,E18,E23,E29)</f>
-        <v>12052.825511757</v>
+        <v>12112.1523034845</v>
       </c>
       <c r="F7" s="18" t="n">
         <f aca="false">SUM(F15,F18,F23,F29)</f>
-        <v>11406.1523505739</v>
+        <v>11593.2665797328</v>
       </c>
       <c r="G7" s="18" t="n">
         <f aca="false">SUM(G15,G18,G23,G29)</f>
-        <v>10642.924404858</v>
+        <v>11032.9366705236</v>
       </c>
       <c r="H7" s="18" t="n">
         <f aca="false">SUM(H15,H18,H23,H29)</f>
-        <v>9754.6664167885</v>
+        <v>10429.6820580664</v>
       </c>
       <c r="I7" s="18" t="n">
         <f aca="false">SUM(I15,I18,I23,I29)</f>
-        <v>8730.74316327125</v>
+        <v>9780.4111150332</v>
       </c>
       <c r="J7" s="18" t="n">
         <f aca="false">SUM(J15,J18,J23,J29)</f>
-        <v>7559.59080772125</v>
+        <v>9081.70588740268</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5838,31 +5842,31 @@
       </c>
       <c r="D9" s="18" t="n">
         <f aca="false">D5+D6-D7-D8</f>
-        <v>6573.79313888</v>
+        <v>5870.66079248</v>
       </c>
       <c r="E9" s="18" t="n">
         <f aca="false">E5+E6-E7-E8</f>
-        <v>8137.15856601948</v>
+        <v>6627.79709292858</v>
       </c>
       <c r="F9" s="18" t="n">
         <f aca="false">F5+F6-F7-F8</f>
-        <v>9502.69255415479</v>
+        <v>7114.35472823793</v>
       </c>
       <c r="G9" s="18" t="n">
         <f aca="false">G5+G6-G7-G8</f>
-        <v>10958.1844449498</v>
+        <v>7614.75217041102</v>
       </c>
       <c r="H9" s="18" t="n">
         <f aca="false">H5+H6-H7-H8</f>
-        <v>12528.2594476244</v>
+        <v>8147.87134697176</v>
       </c>
       <c r="I9" s="18" t="n">
         <f aca="false">I5+I6-I7-I8</f>
-        <v>14222.7391562444</v>
+        <v>8717.2222809138</v>
       </c>
       <c r="J9" s="18" t="n">
         <f aca="false">J5+J6-J7-J8</f>
-        <v>16051.2282863689</v>
+        <v>9325.60194140207</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5904,31 +5908,31 @@
       </c>
       <c r="D11" s="18" t="n">
         <f aca="false">MIN(MAX(0,D17-D19),MAX(0,D9+D10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>4915.34485416</v>
+        <v>4387.99559436</v>
       </c>
       <c r="E11" s="18" t="n">
         <f aca="false">MIN(MAX(0,E17-E19),MAX(0,E9+E10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>6087.86892451461</v>
+        <v>4955.84781969643</v>
       </c>
       <c r="F11" s="18" t="n">
         <f aca="false">MIN(MAX(0,F17-F19),MAX(0,F9+F10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>7112.01941561609</v>
+        <v>5320.76604617845</v>
       </c>
       <c r="G11" s="18" t="n">
         <f aca="false">MIN(MAX(0,G17-G19),MAX(0,G9+G10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>8203.63833371231</v>
+        <v>5696.06412780826</v>
       </c>
       <c r="H11" s="18" t="n">
         <f aca="false">MIN(MAX(0,H17-H19),MAX(0,H9+H10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>9381.19458571831</v>
+        <v>6095.90351022882</v>
       </c>
       <c r="I11" s="18" t="n">
         <f aca="false">MIN(MAX(0,I17-I19),MAX(0,I9+I10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>10652.0543671833</v>
+        <v>6522.91671068535</v>
       </c>
       <c r="J11" s="18" t="n">
         <f aca="false">MIN(MAX(0,J17-J19),MAX(0,J9+J10-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>12023.4212147766</v>
+        <v>6979.20145605155</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5937,68 +5941,68 @@
       </c>
       <c r="D12" s="18" t="n">
         <f aca="false">MIN(MAX(0,D22+D24),MAX(0,D9+D10-D11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>1228.83621354</v>
+        <v>1096.99889859</v>
       </c>
       <c r="E12" s="18" t="n">
         <f aca="false">MIN(MAX(0,E22+E24),MAX(0,E9+E10-E11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>1521.96723112865</v>
+        <v>1238.96195492411</v>
       </c>
       <c r="F12" s="18" t="n">
         <f aca="false">MIN(MAX(0,F22+F24),MAX(0,F9+F10-F11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>1778.00485390402</v>
+        <v>1330.19151154461</v>
       </c>
       <c r="G12" s="18" t="n">
         <f aca="false">MIN(MAX(0,G22+G24),MAX(0,G9+G10-G11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>2050.90958342808</v>
+        <v>1424.01603195207</v>
       </c>
       <c r="H12" s="18" t="n">
         <f aca="false">MIN(MAX(0,H22+H24),MAX(0,H9+H10-H11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>2345.29864642958</v>
+        <v>1523.97587755721</v>
       </c>
       <c r="I12" s="18" t="n">
         <f aca="false">MIN(MAX(0,I22+I24),MAX(0,I9+I10-I11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>2663.01359179583</v>
+        <v>1630.72917767134</v>
       </c>
       <c r="J12" s="18" t="n">
         <f aca="false">MIN(MAX(0,J22+J24),MAX(0,J9+J10-J11-Assumptions!$E$16)*Assumptions!$E$25)</f>
-        <v>3005.85530369416</v>
+        <v>1744.80036401289</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="30" t="n">
         <f aca="false">C5</f>
         <v>20</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="30" t="n">
         <f aca="false">D9+D10-D11-D12</f>
-        <v>429.61207118</v>
-      </c>
-      <c r="E13" s="29" t="n">
+        <v>385.66629953</v>
+      </c>
+      <c r="E13" s="30" t="n">
         <f aca="false">E9+E10-E11-E12</f>
-        <v>527.322410376218</v>
-      </c>
-      <c r="F13" s="29" t="n">
+        <v>432.987318308036</v>
+      </c>
+      <c r="F13" s="30" t="n">
         <f aca="false">F9+F10-F11-F12</f>
-        <v>612.668284634674</v>
-      </c>
-      <c r="G13" s="29" t="n">
+        <v>463.397170514871</v>
+      </c>
+      <c r="G13" s="30" t="n">
         <f aca="false">G9+G10-G11-G12</f>
-        <v>703.636527809359</v>
-      </c>
-      <c r="H13" s="29" t="n">
+        <v>494.672010650688</v>
+      </c>
+      <c r="H13" s="30" t="n">
         <f aca="false">H9+H10-H11-H12</f>
-        <v>801.766215476526</v>
-      </c>
-      <c r="I13" s="29" t="n">
+        <v>527.991959185735</v>
+      </c>
+      <c r="I13" s="30" t="n">
         <f aca="false">I9+I10-I11-I12</f>
-        <v>907.671197265277</v>
-      </c>
-      <c r="J13" s="29" t="n">
+        <v>563.576392557112</v>
+      </c>
+      <c r="J13" s="30" t="n">
         <f aca="false">J9+J10-J11-J12</f>
-        <v>1021.95176789805</v>
+        <v>601.600121337629</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6122,27 +6126,27 @@
       </c>
       <c r="E17" s="18" t="n">
         <f aca="false">D21</f>
-        <v>93629.44126584</v>
+        <v>94156.79052564</v>
       </c>
       <c r="F17" s="18" t="n">
         <f aca="false">E21</f>
-        <v>86546.1704613254</v>
+        <v>88205.5408259436</v>
       </c>
       <c r="G17" s="18" t="n">
         <f aca="false">F21</f>
-        <v>78438.7491657093</v>
+        <v>81889.3728997651</v>
       </c>
       <c r="H17" s="18" t="n">
         <f aca="false">G21</f>
-        <v>69239.708951997</v>
+        <v>75197.9068919569</v>
       </c>
       <c r="I17" s="18" t="n">
         <f aca="false">H21</f>
-        <v>58863.1124862787</v>
+        <v>68106.601501728</v>
       </c>
       <c r="J17" s="18" t="n">
         <f aca="false">I21</f>
-        <v>47215.6562390954</v>
+        <v>60588.2829110427</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6155,27 +6159,27 @@
       </c>
       <c r="E18" s="18" t="n">
         <f aca="false">E17*Assumptions!$E$20</f>
-        <v>7958.5025075964</v>
+        <v>8003.3271946794</v>
       </c>
       <c r="F18" s="18" t="n">
         <f aca="false">F17*Assumptions!$E$20</f>
-        <v>7356.42448921266</v>
+        <v>7497.47097020521</v>
       </c>
       <c r="G18" s="18" t="n">
         <f aca="false">G17*Assumptions!$E$20</f>
-        <v>6667.29367908529</v>
+        <v>6960.59669648004</v>
       </c>
       <c r="H18" s="18" t="n">
         <f aca="false">H17*Assumptions!$E$20</f>
-        <v>5885.37526091974</v>
+        <v>6391.82208581633</v>
       </c>
       <c r="I18" s="18" t="n">
         <f aca="false">I17*Assumptions!$E$20</f>
-        <v>5003.36456133369</v>
+        <v>5789.06112764688</v>
       </c>
       <c r="J18" s="18" t="n">
         <f aca="false">J17*Assumptions!$E$20</f>
-        <v>4013.33078032311</v>
+        <v>5150.00404743863</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6212,40 +6216,40 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="30" t="n">
         <f aca="false">'Sources &amp; Uses'!F7</f>
         <v>37327.5705</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="30" t="n">
         <f aca="false">D11</f>
-        <v>4915.34485416</v>
-      </c>
-      <c r="E20" s="29" t="n">
+        <v>4387.99559436</v>
+      </c>
+      <c r="E20" s="30" t="n">
         <f aca="false">E11</f>
-        <v>6087.86892451461</v>
-      </c>
-      <c r="F20" s="29" t="n">
+        <v>4955.84781969643</v>
+      </c>
+      <c r="F20" s="30" t="n">
         <f aca="false">F11</f>
-        <v>7112.01941561609</v>
-      </c>
-      <c r="G20" s="29" t="n">
+        <v>5320.76604617845</v>
+      </c>
+      <c r="G20" s="30" t="n">
         <f aca="false">G11</f>
-        <v>8203.63833371231</v>
-      </c>
-      <c r="H20" s="29" t="n">
+        <v>5696.06412780826</v>
+      </c>
+      <c r="H20" s="30" t="n">
         <f aca="false">H11</f>
-        <v>9381.19458571831</v>
-      </c>
-      <c r="I20" s="29" t="n">
+        <v>6095.90351022882</v>
+      </c>
+      <c r="I20" s="30" t="n">
         <f aca="false">I11</f>
-        <v>10652.0543671833</v>
-      </c>
-      <c r="J20" s="29" t="n">
+        <v>6522.91671068535</v>
+      </c>
+      <c r="J20" s="30" t="n">
         <f aca="false">J11</f>
-        <v>12023.4212147766</v>
+        <v>6979.20145605155</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6258,31 +6262,31 @@
       </c>
       <c r="D21" s="18" t="n">
         <f aca="false">MAX(0,D17-D19-D20)</f>
-        <v>93629.44126584</v>
+        <v>94156.79052564</v>
       </c>
       <c r="E21" s="18" t="n">
         <f aca="false">MAX(0,E17-E19-E20)</f>
-        <v>86546.1704613254</v>
+        <v>88205.5408259436</v>
       </c>
       <c r="F21" s="18" t="n">
         <f aca="false">MAX(0,F17-F19-F20)</f>
-        <v>78438.7491657093</v>
+        <v>81889.3728997651</v>
       </c>
       <c r="G21" s="18" t="n">
         <f aca="false">MAX(0,G17-G19-G20)</f>
-        <v>69239.708951997</v>
+        <v>75197.9068919569</v>
       </c>
       <c r="H21" s="18" t="n">
         <f aca="false">MAX(0,H17-H19-H20)</f>
-        <v>58863.1124862787</v>
+        <v>68106.601501728</v>
       </c>
       <c r="I21" s="18" t="n">
         <f aca="false">MAX(0,I17-I19-I20)</f>
-        <v>47215.6562390954</v>
+        <v>60588.2829110427</v>
       </c>
       <c r="J21" s="18" t="n">
         <f aca="false">MAX(0,J17-J19-J20)</f>
-        <v>34196.8331443187</v>
+        <v>52613.6795749912</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6299,27 +6303,27 @@
       </c>
       <c r="E22" s="18" t="n">
         <f aca="false">D26</f>
-        <v>37218.56140146</v>
+        <v>37350.39871641</v>
       </c>
       <c r="F22" s="18" t="n">
         <f aca="false">E26</f>
-        <v>36813.1510123751</v>
+        <v>37231.9487229782</v>
       </c>
       <c r="G22" s="18" t="n">
         <f aca="false">F26</f>
-        <v>36139.5406888424</v>
+        <v>37018.7156731229</v>
       </c>
       <c r="H22" s="18" t="n">
         <f aca="false">G26</f>
-        <v>35172.8173260796</v>
+        <v>36705.2611113646</v>
       </c>
       <c r="I22" s="18" t="n">
         <f aca="false">H26</f>
-        <v>33882.7031994324</v>
+        <v>36282.4430671483</v>
       </c>
       <c r="J22" s="18" t="n">
         <f aca="false">I26</f>
-        <v>32236.1707036195</v>
+        <v>35740.1871814914</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6332,135 +6336,135 @@
       </c>
       <c r="E23" s="18" t="n">
         <f aca="false">E22*Assumptions!$E$23</f>
-        <v>4094.0417541606</v>
+        <v>4108.5438588051</v>
       </c>
       <c r="F23" s="18" t="n">
         <f aca="false">F22*Assumptions!$E$23</f>
-        <v>4049.44661136127</v>
+        <v>4095.5143595276</v>
       </c>
       <c r="G23" s="18" t="n">
         <f aca="false">G22*Assumptions!$E$23</f>
-        <v>3975.34947577266</v>
+        <v>4072.05872404352</v>
       </c>
       <c r="H23" s="18" t="n">
         <f aca="false">H22*Assumptions!$E$23</f>
-        <v>3869.00990586875</v>
+        <v>4037.5787222501</v>
       </c>
       <c r="I23" s="18" t="n">
         <f aca="false">I22*Assumptions!$E$23</f>
-        <v>3727.09735193756</v>
+        <v>3991.06873738631</v>
       </c>
       <c r="J23" s="18" t="n">
         <f aca="false">J22*Assumptions!$E$23</f>
-        <v>3545.97877739815</v>
+        <v>3931.42058996405</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="29" t="s">
         <v>225</v>
       </c>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29" t="n">
+      <c r="C24" s="30"/>
+      <c r="D24" s="30" t="n">
         <f aca="false">D22*Assumptions!$E$24</f>
         <v>1119.827115</v>
       </c>
-      <c r="E24" s="29" t="n">
+      <c r="E24" s="30" t="n">
         <f aca="false">E22*Assumptions!$E$24</f>
-        <v>1116.5568420438</v>
-      </c>
-      <c r="F24" s="29" t="n">
+        <v>1120.5119614923</v>
+      </c>
+      <c r="F24" s="30" t="n">
         <f aca="false">F22*Assumptions!$E$24</f>
-        <v>1104.39453037125</v>
-      </c>
-      <c r="G24" s="29" t="n">
+        <v>1116.95846168935</v>
+      </c>
+      <c r="G24" s="30" t="n">
         <f aca="false">G22*Assumptions!$E$24</f>
-        <v>1084.18622066527</v>
-      </c>
-      <c r="H24" s="29" t="n">
+        <v>1110.56147019369</v>
+      </c>
+      <c r="H24" s="30" t="n">
         <f aca="false">H22*Assumptions!$E$24</f>
-        <v>1055.18451978239</v>
-      </c>
-      <c r="I24" s="29" t="n">
+        <v>1101.15783334094</v>
+      </c>
+      <c r="I24" s="30" t="n">
         <f aca="false">I22*Assumptions!$E$24</f>
-        <v>1016.48109598297</v>
-      </c>
-      <c r="J24" s="29" t="n">
+        <v>1088.47329201445</v>
+      </c>
+      <c r="J24" s="30" t="n">
         <f aca="false">J22*Assumptions!$E$24</f>
-        <v>967.085121108585</v>
+        <v>1072.20561544474</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="29" t="s">
         <v>226</v>
       </c>
-      <c r="C25" s="29" t="n">
+      <c r="C25" s="30" t="n">
         <f aca="false">SUM(C16,C20,C13)</f>
         <v>37347.5705</v>
       </c>
-      <c r="D25" s="29" t="n">
+      <c r="D25" s="30" t="n">
         <f aca="false">D12</f>
-        <v>1228.83621354</v>
-      </c>
-      <c r="E25" s="29" t="n">
+        <v>1096.99889859</v>
+      </c>
+      <c r="E25" s="30" t="n">
         <f aca="false">E12</f>
-        <v>1521.96723112865</v>
-      </c>
-      <c r="F25" s="29" t="n">
+        <v>1238.96195492411</v>
+      </c>
+      <c r="F25" s="30" t="n">
         <f aca="false">F12</f>
-        <v>1778.00485390402</v>
-      </c>
-      <c r="G25" s="29" t="n">
+        <v>1330.19151154461</v>
+      </c>
+      <c r="G25" s="30" t="n">
         <f aca="false">G12</f>
-        <v>2050.90958342808</v>
-      </c>
-      <c r="H25" s="29" t="n">
+        <v>1424.01603195207</v>
+      </c>
+      <c r="H25" s="30" t="n">
         <f aca="false">H12</f>
-        <v>2345.29864642958</v>
-      </c>
-      <c r="I25" s="29" t="n">
+        <v>1523.97587755721</v>
+      </c>
+      <c r="I25" s="30" t="n">
         <f aca="false">I12</f>
-        <v>2663.01359179583</v>
-      </c>
-      <c r="J25" s="29" t="n">
+        <v>1630.72917767134</v>
+      </c>
+      <c r="J25" s="30" t="n">
         <f aca="false">J12</f>
-        <v>3005.85530369416</v>
+        <v>1744.80036401289</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="29" t="s">
         <v>227</v>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="30" t="n">
         <f aca="false">C22</f>
         <v>37327.5705</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="30" t="n">
         <f aca="false">MAX(0,D22+D24-D25)</f>
-        <v>37218.56140146</v>
-      </c>
-      <c r="E26" s="29" t="n">
+        <v>37350.39871641</v>
+      </c>
+      <c r="E26" s="30" t="n">
         <f aca="false">MAX(0,E22+E24-E25)</f>
-        <v>36813.1510123751</v>
-      </c>
-      <c r="F26" s="29" t="n">
+        <v>37231.9487229782</v>
+      </c>
+      <c r="F26" s="30" t="n">
         <f aca="false">MAX(0,F22+F24-F25)</f>
-        <v>36139.5406888424</v>
-      </c>
-      <c r="G26" s="29" t="n">
+        <v>37018.7156731229</v>
+      </c>
+      <c r="G26" s="30" t="n">
         <f aca="false">MAX(0,G22+G24-G25)</f>
-        <v>35172.8173260796</v>
-      </c>
-      <c r="H26" s="29" t="n">
+        <v>36705.2611113646</v>
+      </c>
+      <c r="H26" s="30" t="n">
         <f aca="false">MAX(0,H22+H24-H25)</f>
-        <v>33882.7031994324</v>
-      </c>
-      <c r="I26" s="29" t="n">
+        <v>36282.4430671483</v>
+      </c>
+      <c r="I26" s="30" t="n">
         <f aca="false">MAX(0,I22+I24-I25)</f>
-        <v>32236.1707036195</v>
-      </c>
-      <c r="J26" s="29" t="n">
+        <v>35740.1871814914</v>
+      </c>
+      <c r="J26" s="30" t="n">
         <f aca="false">MAX(0,J22+J24-J25)</f>
-        <v>30197.4005210339</v>
+        <v>35067.5924329232</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6473,31 +6477,31 @@
       </c>
       <c r="D27" s="18" t="n">
         <f aca="false">SUM(D16,D21,D26)</f>
-        <v>130848.0026673</v>
+        <v>131507.18924205</v>
       </c>
       <c r="E27" s="18" t="n">
         <f aca="false">SUM(E16,E21,E26)</f>
-        <v>123359.321473701</v>
+        <v>125437.489548922</v>
       </c>
       <c r="F27" s="18" t="n">
         <f aca="false">SUM(F16,F21,F26)</f>
-        <v>114578.289854552</v>
+        <v>118908.088572888</v>
       </c>
       <c r="G27" s="18" t="n">
         <f aca="false">SUM(G16,G21,G26)</f>
-        <v>104412.526278077</v>
+        <v>111903.168003321</v>
       </c>
       <c r="H27" s="18" t="n">
         <f aca="false">SUM(H16,H21,H26)</f>
-        <v>92745.815685711</v>
+        <v>104389.044568876</v>
       </c>
       <c r="I27" s="18" t="n">
         <f aca="false">SUM(I16,I21,I26)</f>
-        <v>79451.8269427149</v>
+        <v>96328.4700925341</v>
       </c>
       <c r="J27" s="18" t="n">
         <f aca="false">SUM(J16,J21,J26)</f>
-        <v>64394.2336653526</v>
+        <v>87681.2720079144</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6510,31 +6514,31 @@
       </c>
       <c r="D28" s="18" t="n">
         <f aca="false">D27-D13</f>
-        <v>130418.39059612</v>
+        <v>131121.52294252</v>
       </c>
       <c r="E28" s="18" t="n">
         <f aca="false">E27-E13</f>
-        <v>122831.999063324</v>
+        <v>125004.502230614</v>
       </c>
       <c r="F28" s="18" t="n">
         <f aca="false">F27-F13</f>
-        <v>113965.621569917</v>
+        <v>118444.691402373</v>
       </c>
       <c r="G28" s="18" t="n">
         <f aca="false">G27-G13</f>
-        <v>103708.889750267</v>
+        <v>111408.495992671</v>
       </c>
       <c r="H28" s="18" t="n">
         <f aca="false">H27-H13</f>
-        <v>91944.0494702345</v>
+        <v>103861.052609691</v>
       </c>
       <c r="I28" s="18" t="n">
         <f aca="false">I27-I13</f>
-        <v>78544.1557454496</v>
+        <v>95764.893699977</v>
       </c>
       <c r="J28" s="18" t="n">
         <f aca="false">J27-J13</f>
-        <v>63372.2818974546</v>
+        <v>87079.6718865768</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6639,64 +6643,64 @@
       <c r="B5" s="0" t="s">
         <v>232</v>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="26" t="n">
         <f aca="false">IFERROR('Debt Schedule'!D25/'Operating Model'!D8,0)</f>
-        <v>0.0474364832834914</v>
-      </c>
-      <c r="D5" s="25" t="n">
+        <v>0.0439156122939911</v>
+      </c>
+      <c r="D5" s="26" t="n">
         <f aca="false">IFERROR('Debt Schedule'!E25/'Operating Model'!E8,0)</f>
-        <v>0.056489221591227</v>
-      </c>
-      <c r="E5" s="25" t="n">
+        <v>0.0494126887253864</v>
+      </c>
+      <c r="E5" s="26" t="n">
         <f aca="false">IFERROR('Debt Schedule'!F25/'Operating Model'!F8,0)</f>
-        <v>0.0635035432153167</v>
-      </c>
-      <c r="F5" s="25" t="n">
+        <v>0.0528541639086104</v>
+      </c>
+      <c r="F5" s="26" t="n">
         <f aca="false">IFERROR('Debt Schedule'!G25/'Operating Model'!G8,0)</f>
-        <v>0.0705438354845756</v>
-      </c>
-      <c r="G5" s="25" t="n">
+        <v>0.0563743306442152</v>
+      </c>
+      <c r="G5" s="26" t="n">
         <f aca="false">IFERROR('Debt Schedule'!H25/'Operating Model'!H8,0)</f>
-        <v>0.0777468091262203</v>
-      </c>
-      <c r="H5" s="25" t="n">
+        <v>0.0601122904277677</v>
+      </c>
+      <c r="H5" s="26" t="n">
         <f aca="false">IFERROR('Debt Schedule'!I25/'Operating Model'!I8,0)</f>
-        <v>0.0851406517601289</v>
-      </c>
-      <c r="I5" s="25" t="n">
+        <v>0.064091891058571</v>
+      </c>
+      <c r="I5" s="26" t="n">
         <f aca="false">IFERROR('Debt Schedule'!J25/'Operating Model'!J8,0)</f>
-        <v>0.0927475407644869</v>
+        <v>0.0683314548507237</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
         <v>233</v>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="26" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="26" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="26" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
-      <c r="F6" s="25" t="n">
+      <c r="F6" s="26" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
-      <c r="G6" s="25" t="n">
+      <c r="G6" s="26" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
-      <c r="H6" s="25" t="n">
+      <c r="H6" s="26" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
-      <c r="I6" s="25" t="n">
+      <c r="I6" s="26" t="n">
         <f aca="false">Assumptions!$E$26</f>
         <v>7</v>
       </c>
@@ -6705,97 +6709,97 @@
       <c r="B7" s="0" t="s">
         <v>234</v>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="26" t="n">
         <f aca="false">C6-C5</f>
-        <v>6.95256351671651</v>
-      </c>
-      <c r="D7" s="25" t="n">
+        <v>6.95608438770601</v>
+      </c>
+      <c r="D7" s="26" t="n">
         <f aca="false">D6-D5</f>
-        <v>6.94351077840877</v>
-      </c>
-      <c r="E7" s="25" t="n">
+        <v>6.95058731127461</v>
+      </c>
+      <c r="E7" s="26" t="n">
         <f aca="false">E6-E5</f>
-        <v>6.93649645678468</v>
-      </c>
-      <c r="F7" s="25" t="n">
+        <v>6.94714583609139</v>
+      </c>
+      <c r="F7" s="26" t="n">
         <f aca="false">F6-F5</f>
-        <v>6.92945616451542</v>
-      </c>
-      <c r="G7" s="25" t="n">
+        <v>6.94362566935579</v>
+      </c>
+      <c r="G7" s="26" t="n">
         <f aca="false">G6-G5</f>
-        <v>6.92225319087378</v>
-      </c>
-      <c r="H7" s="25" t="n">
+        <v>6.93988770957223</v>
+      </c>
+      <c r="H7" s="26" t="n">
         <f aca="false">H6-H5</f>
-        <v>6.91485934823987</v>
-      </c>
-      <c r="I7" s="25" t="n">
+        <v>6.93590810894143</v>
+      </c>
+      <c r="I7" s="26" t="n">
         <f aca="false">I6-I5</f>
-        <v>6.90725245923551</v>
+        <v>6.93166854514928</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="C8" s="25" t="n">
+      <c r="C8" s="26" t="n">
         <f aca="false">IFERROR('Operating Model'!D8/'Debt Schedule'!D7,0)</f>
-        <v>2.06130356100108</v>
-      </c>
-      <c r="D8" s="25" t="n">
+        <v>1.98768557667961</v>
+      </c>
+      <c r="D8" s="26" t="n">
         <f aca="false">IFERROR('Operating Model'!E8/'Debt Schedule'!E7,0)</f>
-        <v>2.23537733018857</v>
-      </c>
-      <c r="E8" s="25" t="n">
+        <v>2.07013258441992</v>
+      </c>
+      <c r="E8" s="26" t="n">
         <f aca="false">IFERROR('Operating Model'!F8/'Debt Schedule'!F7,0)</f>
-        <v>2.45468526976787</v>
-      </c>
-      <c r="F8" s="25" t="n">
+        <v>2.17084663463505</v>
+      </c>
+      <c r="F8" s="26" t="n">
         <f aca="false">IFERROR('Operating Model'!G8/'Debt Schedule'!G7,0)</f>
-        <v>2.73165889969321</v>
-      </c>
-      <c r="G8" s="25" t="n">
+        <v>2.28950899993057</v>
+      </c>
+      <c r="G8" s="26" t="n">
         <f aca="false">IFERROR('Operating Model'!H8/'Debt Schedule'!H7,0)</f>
-        <v>3.09245334886708</v>
-      </c>
-      <c r="H8" s="25" t="n">
+        <v>2.43076932608024</v>
+      </c>
+      <c r="H8" s="26" t="n">
         <f aca="false">IFERROR('Operating Model'!I8/'Debt Schedule'!I7,0)</f>
-        <v>3.58249175933803</v>
-      </c>
-      <c r="I8" s="25" t="n">
+        <v>2.60148691304108</v>
+      </c>
+      <c r="I8" s="26" t="n">
         <f aca="false">IFERROR('Operating Model'!J8/'Debt Schedule'!J7,0)</f>
-        <v>4.2871371710915</v>
+        <v>2.81162659522675</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
         <v>236</v>
       </c>
-      <c r="C9" s="25" t="n">
+      <c r="C9" s="26" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="26" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
-      <c r="E9" s="25" t="n">
+      <c r="E9" s="26" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
-      <c r="F9" s="25" t="n">
+      <c r="F9" s="26" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
-      <c r="G9" s="25" t="n">
+      <c r="G9" s="26" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
-      <c r="H9" s="25" t="n">
+      <c r="H9" s="26" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
-      <c r="I9" s="25" t="n">
+      <c r="I9" s="26" t="n">
         <f aca="false">Assumptions!$E$27</f>
         <v>1.75</v>
       </c>
@@ -6804,33 +6808,33 @@
       <c r="B10" s="0" t="s">
         <v>237</v>
       </c>
-      <c r="C10" s="25" t="n">
+      <c r="C10" s="26" t="n">
         <f aca="false">C8-C9</f>
-        <v>0.311303561001076</v>
-      </c>
-      <c r="D10" s="25" t="n">
+        <v>0.237685576679609</v>
+      </c>
+      <c r="D10" s="26" t="n">
         <f aca="false">D8-D9</f>
-        <v>0.485377330188566</v>
-      </c>
-      <c r="E10" s="25" t="n">
+        <v>0.320132584419915</v>
+      </c>
+      <c r="E10" s="26" t="n">
         <f aca="false">E8-E9</f>
-        <v>0.704685269767872</v>
-      </c>
-      <c r="F10" s="25" t="n">
+        <v>0.420846634635053</v>
+      </c>
+      <c r="F10" s="26" t="n">
         <f aca="false">F8-F9</f>
-        <v>0.981658899693209</v>
-      </c>
-      <c r="G10" s="25" t="n">
+        <v>0.53950899993057</v>
+      </c>
+      <c r="G10" s="26" t="n">
         <f aca="false">G8-G9</f>
-        <v>1.34245334886708</v>
-      </c>
-      <c r="H10" s="25" t="n">
+        <v>0.680769326080235</v>
+      </c>
+      <c r="H10" s="26" t="n">
         <f aca="false">H8-H9</f>
-        <v>1.83249175933803</v>
-      </c>
-      <c r="I10" s="25" t="n">
+        <v>0.851486913041077</v>
+      </c>
+      <c r="I10" s="26" t="n">
         <f aca="false">I8-I9</f>
-        <v>2.5371371710915</v>
+        <v>1.06162659522675</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6872,31 +6876,31 @@
       </c>
       <c r="C12" s="18" t="n">
         <f aca="false">'Debt Schedule'!D13-C11</f>
-        <v>409.61207118</v>
+        <v>365.66629953</v>
       </c>
       <c r="D12" s="18" t="n">
         <f aca="false">'Debt Schedule'!E13-D11</f>
-        <v>507.322410376218</v>
+        <v>412.987318308036</v>
       </c>
       <c r="E12" s="18" t="n">
         <f aca="false">'Debt Schedule'!F13-E11</f>
-        <v>592.668284634674</v>
+        <v>443.397170514871</v>
       </c>
       <c r="F12" s="18" t="n">
         <f aca="false">'Debt Schedule'!G13-F11</f>
-        <v>683.636527809359</v>
+        <v>474.672010650688</v>
       </c>
       <c r="G12" s="18" t="n">
         <f aca="false">'Debt Schedule'!H13-G11</f>
-        <v>781.766215476526</v>
+        <v>507.991959185735</v>
       </c>
       <c r="H12" s="18" t="n">
         <f aca="false">'Debt Schedule'!I13-H11</f>
-        <v>887.671197265277</v>
+        <v>543.576392557112</v>
       </c>
       <c r="I12" s="18" t="n">
         <f aca="false">'Debt Schedule'!J13-I11</f>
-        <v>1001.95176789805</v>
+        <v>581.600121337629</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/03_Private_Equity/instances/public_home_depot_2023.xlsx
+++ b/03_Private_Equity/instances/public_home_depot_2023.xlsx
@@ -998,7 +998,7 @@
     <t xml:space="preserve">Full input accounting: every candidate cell sourced or declared</t>
   </si>
   <si>
-    <t xml:space="preserve">Sourced annual EBITDA-margin change (C8) from management's own FY2024 operating-margin guidance vs FY2023 actual. Explicitly declared every remaining candidate input cell that has no disclosed value to source, each with a stated reason. NWC/revenue (C11) and existing net debt refinanced (C15) remain deliberately undeclared: both are real Home Depot balance-sheet facts that should be sourced, not declared away.</t>
+    <t xml:space="preserve">Sourced annual EBITDA-margin change (C8) from management's own FY2024 operating-margin guidance vs FY2023 actual. Reclassified every remaining candidate input as a typed driver rather than an 'illustrative' hardcode: each names its driver_type and rationale, and carries an empty basis until its range is grounded in real comparable data. Ungrounded drivers earn no coverage credit by design.</t>
   </si>
   <si>
     <t xml:space="preserve">External historical case; human stakeholder approval remains pending</t>
